--- a/N5.xlsx
+++ b/N5.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\新增資料夾 (3)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="1015">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="1017">
   <si>
     <t>東京</t>
   </si>
@@ -3064,6 +3064,14 @@
   </si>
   <si>
     <t>Hiragana</t>
+  </si>
+  <si>
+    <t>10分</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>じゅっぷん</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -5343,10 +5351,10 @@
         <v>3</v>
       </c>
       <c r="B96" t="s">
-        <v>244</v>
+        <v>1016</v>
       </c>
       <c r="C96" t="s">
-        <v>243</v>
+        <v>1015</v>
       </c>
       <c r="D96" t="s">
         <v>245</v>
@@ -9499,5 +9507,6 @@
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/N5.xlsx
+++ b/N5.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sunsh\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25507703-D9FA-4626-B041-1AE6463DA5E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -237,12 +238,6 @@
     <t>ぎゅうにく</t>
   </si>
   <si>
-    <t>化学</t>
-  </si>
-  <si>
-    <t>化學</t>
-  </si>
-  <si>
     <t>購物</t>
   </si>
   <si>
@@ -1558,9 +1553,6 @@
   </si>
   <si>
     <t>毎月</t>
-  </si>
-  <si>
-    <t>まいつき／まいげつ</t>
   </si>
   <si>
     <t>每月</t>
@@ -3071,14 +3063,26 @@
   </si>
   <si>
     <t>じゅっぷん</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>科学</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>科學</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>まいつき</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="19" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3690,13 +3694,13 @@
     <cellStyle name="60% - 輔色5" xfId="36" builtinId="48" customBuiltin="1"/>
     <cellStyle name="60% - 輔色6" xfId="40" builtinId="52" customBuiltin="1"/>
     <cellStyle name="一般" xfId="0" builtinId="0"/>
-    <cellStyle name="一般 2" xfId="41"/>
+    <cellStyle name="一般 2" xfId="41" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
     <cellStyle name="中等" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="合計" xfId="16" builtinId="25" customBuiltin="1"/>
     <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="計算方式" xfId="11" builtinId="22" customBuiltin="1"/>
     <cellStyle name="連結的儲存格" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="備註 2" xfId="42"/>
+    <cellStyle name="備註 2" xfId="42" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
     <cellStyle name="說明文字" xfId="15" builtinId="53" customBuiltin="1"/>
     <cellStyle name="輔色1" xfId="17" builtinId="29" customBuiltin="1"/>
     <cellStyle name="輔色2" xfId="21" builtinId="33" customBuiltin="1"/>
@@ -4012,109 +4016,109 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D392"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="16.5">
       <c r="A1" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1011</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1014</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" t="s">
         <v>89</v>
       </c>
-      <c r="D2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" t="s">
         <v>92</v>
       </c>
-      <c r="D3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" t="s">
         <v>97</v>
       </c>
-      <c r="D5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" t="s">
         <v>100</v>
       </c>
-      <c r="D6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" t="s">
         <v>103</v>
       </c>
-      <c r="D7" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>1</v>
       </c>
@@ -4128,105 +4132,105 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" t="s">
         <v>106</v>
       </c>
-      <c r="D9" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11">
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12">
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C12" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" t="s">
         <v>113</v>
       </c>
-      <c r="D12" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13">
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C13" t="s">
+        <v>114</v>
+      </c>
+      <c r="D13" t="s">
         <v>116</v>
       </c>
-      <c r="D13" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14">
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D14" t="s">
         <v>119</v>
       </c>
-      <c r="D14" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15">
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D15" t="s">
         <v>122</v>
       </c>
-      <c r="D15" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16">
         <v>1</v>
       </c>
@@ -4240,91 +4244,91 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C17" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D17" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C18" t="s">
+        <v>125</v>
+      </c>
+      <c r="D18" t="s">
         <v>127</v>
       </c>
-      <c r="D18" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19">
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C19" t="s">
+        <v>128</v>
+      </c>
+      <c r="D19" t="s">
         <v>130</v>
       </c>
-      <c r="D19" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20">
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C20" t="s">
+        <v>131</v>
+      </c>
+      <c r="D20" t="s">
         <v>133</v>
       </c>
-      <c r="D20" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C21" t="s">
+        <v>134</v>
+      </c>
+      <c r="D21" t="s">
         <v>136</v>
       </c>
-      <c r="D21" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22">
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C22" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D22" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23">
         <v>1</v>
       </c>
@@ -4338,63 +4342,63 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C24" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D24" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25">
         <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C25" t="s">
+        <v>141</v>
+      </c>
+      <c r="D25" t="s">
         <v>143</v>
       </c>
-      <c r="D25" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26">
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C26" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27">
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C27" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D27" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28">
         <v>1</v>
       </c>
@@ -4408,441 +4412,441 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4">
       <c r="A29">
         <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C29" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D29" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30">
         <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C30" t="s">
+        <v>149</v>
+      </c>
+      <c r="D30" t="s">
         <v>151</v>
       </c>
-      <c r="D30" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31">
         <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C31" t="s">
+        <v>152</v>
+      </c>
+      <c r="D31" t="s">
         <v>154</v>
       </c>
-      <c r="D31" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32">
         <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C32" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D32" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33">
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C33" t="s">
+        <v>157</v>
+      </c>
+      <c r="D33" t="s">
         <v>159</v>
       </c>
-      <c r="D33" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34">
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C34" t="s">
+        <v>160</v>
+      </c>
+      <c r="D34" t="s">
         <v>162</v>
       </c>
-      <c r="D34" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:4">
       <c r="A35">
         <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C35" t="s">
+        <v>163</v>
+      </c>
+      <c r="D35" t="s">
         <v>165</v>
       </c>
-      <c r="D35" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:4">
       <c r="A36">
         <v>2</v>
       </c>
       <c r="B36" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C36" t="s">
+        <v>166</v>
+      </c>
+      <c r="D36" t="s">
         <v>168</v>
       </c>
-      <c r="D36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:4">
       <c r="A37">
         <v>2</v>
       </c>
       <c r="B37" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C37" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D37" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
       <c r="A38">
         <v>2</v>
       </c>
       <c r="B38" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C38" t="s">
+        <v>169</v>
+      </c>
+      <c r="D38" t="s">
         <v>171</v>
       </c>
-      <c r="D38" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:4">
       <c r="A39">
         <v>2</v>
       </c>
       <c r="B39" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C39" t="s">
+        <v>172</v>
+      </c>
+      <c r="D39" t="s">
         <v>174</v>
       </c>
-      <c r="D39" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40">
         <v>2</v>
       </c>
       <c r="B40" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C40" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D40" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
       <c r="A41">
         <v>2</v>
       </c>
       <c r="B41" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C41" t="s">
+        <v>177</v>
+      </c>
+      <c r="D41" t="s">
         <v>179</v>
       </c>
-      <c r="D41" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:4">
       <c r="A42">
         <v>2</v>
       </c>
       <c r="B42" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C42" t="s">
+        <v>180</v>
+      </c>
+      <c r="D42" t="s">
         <v>182</v>
       </c>
-      <c r="D42" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:4">
       <c r="A43">
         <v>2</v>
       </c>
       <c r="B43" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C43" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D43" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
       <c r="A44">
         <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C44" t="s">
+        <v>185</v>
+      </c>
+      <c r="D44" t="s">
         <v>187</v>
       </c>
-      <c r="D44" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:4">
       <c r="A45">
         <v>2</v>
       </c>
       <c r="B45" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C45" t="s">
+        <v>188</v>
+      </c>
+      <c r="D45" t="s">
         <v>190</v>
       </c>
-      <c r="D45" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:4">
       <c r="A46">
         <v>2</v>
       </c>
       <c r="B46" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C46" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D46" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
       <c r="A47">
         <v>2</v>
       </c>
       <c r="B47" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C47" t="s">
+        <v>193</v>
+      </c>
+      <c r="D47" t="s">
         <v>195</v>
       </c>
-      <c r="D47" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:4">
       <c r="A48">
         <v>2</v>
       </c>
       <c r="B48" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C48" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D48" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
       <c r="A49">
         <v>2</v>
       </c>
       <c r="B49" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C49" t="s">
+        <v>198</v>
+      </c>
+      <c r="D49" t="s">
         <v>200</v>
       </c>
-      <c r="D49" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:4">
       <c r="A50">
         <v>2</v>
       </c>
       <c r="B50" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C50" t="s">
+        <v>201</v>
+      </c>
+      <c r="D50" t="s">
         <v>203</v>
       </c>
-      <c r="D50" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:4">
       <c r="A51">
         <v>2</v>
       </c>
       <c r="B51" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C51" t="s">
+        <v>204</v>
+      </c>
+      <c r="D51" t="s">
         <v>206</v>
       </c>
-      <c r="D51" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:4">
       <c r="A52">
         <v>2</v>
       </c>
       <c r="B52" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C52" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D52" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
       <c r="A53">
         <v>2</v>
       </c>
       <c r="B53" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C53" t="s">
+        <v>209</v>
+      </c>
+      <c r="D53" t="s">
         <v>211</v>
       </c>
-      <c r="D53" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:4">
       <c r="A54">
         <v>2</v>
       </c>
       <c r="B54" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C54" t="s">
+        <v>212</v>
+      </c>
+      <c r="D54" t="s">
         <v>214</v>
       </c>
-      <c r="D54" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:4">
       <c r="A55">
         <v>2</v>
       </c>
       <c r="B55" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C55" t="s">
+        <v>215</v>
+      </c>
+      <c r="D55" t="s">
         <v>217</v>
       </c>
-      <c r="D55" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:4">
       <c r="A56">
         <v>2</v>
       </c>
       <c r="B56" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C56" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D56" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
       <c r="A57">
         <v>2</v>
       </c>
       <c r="B57" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C57" t="s">
+        <v>220</v>
+      </c>
+      <c r="D57" t="s">
         <v>222</v>
       </c>
-      <c r="D57" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:4">
       <c r="A58">
         <v>2</v>
       </c>
       <c r="B58" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C58" t="s">
+        <v>223</v>
+      </c>
+      <c r="D58" t="s">
         <v>225</v>
       </c>
-      <c r="D58" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:4">
       <c r="A59">
         <v>2</v>
       </c>
       <c r="B59" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C59" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D59" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
       <c r="A60">
         <v>2</v>
       </c>
@@ -4856,371 +4860,371 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4">
       <c r="A61">
         <v>2</v>
       </c>
       <c r="B61" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C61" t="s">
+        <v>228</v>
+      </c>
+      <c r="D61" t="s">
         <v>230</v>
       </c>
-      <c r="D61" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:4">
       <c r="A62">
         <v>2</v>
       </c>
       <c r="B62" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C62" t="s">
+        <v>231</v>
+      </c>
+      <c r="D62" t="s">
         <v>233</v>
       </c>
-      <c r="D62" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:4">
       <c r="A63">
         <v>2</v>
       </c>
       <c r="B63" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C63" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D63" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
       <c r="A64">
         <v>2</v>
       </c>
       <c r="B64" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C64" t="s">
+        <v>236</v>
+      </c>
+      <c r="D64" t="s">
         <v>238</v>
       </c>
-      <c r="D64" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:4">
       <c r="A65">
         <v>2</v>
       </c>
       <c r="B65" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C65" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D65" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
       <c r="A66">
         <v>2</v>
       </c>
       <c r="B66" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C66" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D66" t="s">
         <v>243</v>
       </c>
-      <c r="D66" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:4">
       <c r="A67">
         <v>2</v>
       </c>
       <c r="B67" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C67" t="s">
+        <v>244</v>
+      </c>
+      <c r="D67" t="s">
         <v>246</v>
       </c>
-      <c r="D67" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:4">
       <c r="A68">
         <v>2</v>
       </c>
       <c r="B68" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C68" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D68" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
       <c r="A69">
         <v>2</v>
       </c>
       <c r="B69" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C69" t="s">
+        <v>249</v>
+      </c>
+      <c r="D69" t="s">
         <v>251</v>
       </c>
-      <c r="D69" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:4">
       <c r="A70">
         <v>2</v>
       </c>
       <c r="B70" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C70" t="s">
+        <v>252</v>
+      </c>
+      <c r="D70" t="s">
         <v>254</v>
       </c>
-      <c r="D70" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:4">
       <c r="A71">
         <v>2</v>
       </c>
       <c r="B71" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C71" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D71" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
       <c r="A72">
         <v>3</v>
       </c>
       <c r="B72" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C72" t="s">
+        <v>257</v>
+      </c>
+      <c r="D72" t="s">
         <v>259</v>
       </c>
-      <c r="D72" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:4">
       <c r="A73">
         <v>3</v>
       </c>
       <c r="B73" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C73" t="s">
+        <v>260</v>
+      </c>
+      <c r="D73" t="s">
         <v>262</v>
       </c>
-      <c r="D73" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:4">
       <c r="A74">
         <v>3</v>
       </c>
       <c r="B74" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C74" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
       <c r="A75">
         <v>3</v>
       </c>
       <c r="B75" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C75" t="s">
+        <v>265</v>
+      </c>
+      <c r="D75" t="s">
         <v>267</v>
       </c>
-      <c r="D75" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:4">
       <c r="A76">
         <v>3</v>
       </c>
       <c r="B76" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C76" t="s">
+        <v>268</v>
+      </c>
+      <c r="D76" t="s">
         <v>270</v>
       </c>
-      <c r="D76" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:4">
       <c r="A77">
         <v>3</v>
       </c>
       <c r="B77" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C77" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D77" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
       <c r="A78">
         <v>3</v>
       </c>
       <c r="B78" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C78" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D78" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
       <c r="A79">
         <v>3</v>
       </c>
       <c r="B79" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C79" t="s">
+        <v>275</v>
+      </c>
+      <c r="D79" t="s">
         <v>277</v>
       </c>
-      <c r="D79" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:4">
       <c r="A80">
         <v>3</v>
       </c>
       <c r="B80" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C80" t="s">
+        <v>278</v>
+      </c>
+      <c r="D80" t="s">
         <v>280</v>
       </c>
-      <c r="D80" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:4">
       <c r="A81">
         <v>3</v>
       </c>
       <c r="B81" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C81" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D81" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
       <c r="A82">
         <v>3</v>
       </c>
       <c r="B82" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C82" t="s">
+        <v>283</v>
+      </c>
+      <c r="D82" t="s">
         <v>285</v>
       </c>
-      <c r="D82" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:4">
       <c r="A83">
         <v>3</v>
       </c>
       <c r="B83" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C83" t="s">
+        <v>286</v>
+      </c>
+      <c r="D83" t="s">
         <v>288</v>
       </c>
-      <c r="D83" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="1:4">
       <c r="A84">
         <v>3</v>
       </c>
       <c r="B84" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C84" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D84" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4">
       <c r="A85">
         <v>3</v>
       </c>
       <c r="B85" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C85" t="s">
+        <v>291</v>
+      </c>
+      <c r="D85" t="s">
         <v>293</v>
       </c>
-      <c r="D85" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:4">
       <c r="A86">
         <v>3</v>
       </c>
       <c r="B86" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C86" t="s">
+        <v>294</v>
+      </c>
+      <c r="D86" t="s">
         <v>296</v>
       </c>
-      <c r="D86" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:4">
       <c r="A87">
         <v>3</v>
       </c>
@@ -5234,231 +5238,231 @@
         <v>40</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4">
       <c r="A88">
         <v>3</v>
       </c>
       <c r="B88" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C88" t="s">
+        <v>297</v>
+      </c>
+      <c r="D88" t="s">
         <v>299</v>
       </c>
-      <c r="D88" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="1:4">
       <c r="A89">
         <v>3</v>
       </c>
       <c r="B89" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C89" t="s">
+        <v>300</v>
+      </c>
+      <c r="D89" t="s">
         <v>302</v>
       </c>
-      <c r="D89" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" spans="1:4">
       <c r="A90">
         <v>3</v>
       </c>
       <c r="B90" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C90" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D90" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
       <c r="A91">
         <v>3</v>
       </c>
       <c r="B91" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C91" t="s">
+        <v>305</v>
+      </c>
+      <c r="D91" t="s">
         <v>307</v>
       </c>
-      <c r="D91" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="92" spans="1:4">
       <c r="A92">
         <v>3</v>
       </c>
       <c r="B92" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C92" t="s">
+        <v>308</v>
+      </c>
+      <c r="D92" t="s">
         <v>310</v>
       </c>
-      <c r="D92" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="93" spans="1:4">
       <c r="A93">
         <v>3</v>
       </c>
       <c r="B93" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C93" t="s">
+        <v>311</v>
+      </c>
+      <c r="D93" t="s">
         <v>313</v>
       </c>
-      <c r="D93" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:4">
       <c r="A94">
         <v>3</v>
       </c>
       <c r="B94" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C94" t="s">
+        <v>314</v>
+      </c>
+      <c r="D94" t="s">
         <v>316</v>
       </c>
-      <c r="D94" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:4">
       <c r="A95">
         <v>3</v>
       </c>
       <c r="B95" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C95" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D95" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
       <c r="A96">
         <v>3</v>
       </c>
       <c r="B96" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="C96" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D96" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
       <c r="A97">
         <v>3</v>
       </c>
       <c r="B97" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C97" t="s">
+        <v>319</v>
+      </c>
+      <c r="D97" t="s">
         <v>321</v>
       </c>
-      <c r="D97" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:4">
       <c r="A98">
         <v>3</v>
       </c>
       <c r="B98" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C98" t="s">
+        <v>322</v>
+      </c>
+      <c r="D98" t="s">
         <v>324</v>
       </c>
-      <c r="D98" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:4">
       <c r="A99">
         <v>3</v>
       </c>
       <c r="B99" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C99" t="s">
+        <v>325</v>
+      </c>
+      <c r="D99" t="s">
         <v>327</v>
       </c>
-      <c r="D99" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="100" spans="1:4">
       <c r="A100">
         <v>3</v>
       </c>
       <c r="B100" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C100" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D100" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
       <c r="A101">
         <v>3</v>
       </c>
       <c r="B101" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C101" t="s">
+        <v>330</v>
+      </c>
+      <c r="D101" t="s">
         <v>332</v>
       </c>
-      <c r="D101" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="102" spans="1:4">
       <c r="A102">
         <v>3</v>
       </c>
       <c r="B102" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C102" t="s">
+        <v>333</v>
+      </c>
+      <c r="D102" t="s">
         <v>335</v>
       </c>
-      <c r="D102" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="103" spans="1:4">
       <c r="A103">
         <v>3</v>
       </c>
       <c r="B103" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C103" t="s">
+        <v>336</v>
+      </c>
+      <c r="D103" t="s">
         <v>338</v>
       </c>
-      <c r="D103" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="104" spans="1:4">
       <c r="A104">
         <v>3</v>
       </c>
@@ -5472,203 +5476,203 @@
         <v>30</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4">
       <c r="A105">
         <v>3</v>
       </c>
       <c r="B105" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C105" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D105" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
       <c r="A106">
         <v>3</v>
       </c>
       <c r="B106" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C106" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D106" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
       <c r="A107">
         <v>3</v>
       </c>
       <c r="B107" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C107" t="s">
+        <v>343</v>
+      </c>
+      <c r="D107" t="s">
         <v>345</v>
       </c>
-      <c r="D107" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="108" spans="1:4">
       <c r="A108">
         <v>3</v>
       </c>
       <c r="B108" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C108" t="s">
+        <v>346</v>
+      </c>
+      <c r="D108" t="s">
         <v>348</v>
       </c>
-      <c r="D108" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="109" spans="1:4">
       <c r="A109">
         <v>3</v>
       </c>
       <c r="B109" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C109" t="s">
+        <v>349</v>
+      </c>
+      <c r="D109" t="s">
         <v>351</v>
       </c>
-      <c r="D109" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="110" spans="1:4">
       <c r="A110">
         <v>3</v>
       </c>
       <c r="B110" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C110" t="s">
+        <v>352</v>
+      </c>
+      <c r="D110" t="s">
         <v>354</v>
       </c>
-      <c r="D110" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="111" spans="1:4">
       <c r="A111">
         <v>4</v>
       </c>
       <c r="B111" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C111" t="s">
+        <v>355</v>
+      </c>
+      <c r="D111" t="s">
         <v>357</v>
       </c>
-      <c r="D111" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="112" spans="1:4">
       <c r="A112">
         <v>4</v>
       </c>
       <c r="B112" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C112" t="s">
+        <v>358</v>
+      </c>
+      <c r="D112" t="s">
         <v>360</v>
       </c>
-      <c r="D112" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="113" spans="1:4">
       <c r="A113">
         <v>4</v>
       </c>
       <c r="B113" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C113" t="s">
+        <v>361</v>
+      </c>
+      <c r="D113" t="s">
         <v>363</v>
       </c>
-      <c r="D113" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="114" spans="1:4">
       <c r="A114">
         <v>4</v>
       </c>
       <c r="B114" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C114" t="s">
+        <v>364</v>
+      </c>
+      <c r="D114" t="s">
         <v>366</v>
       </c>
-      <c r="D114" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="115" spans="1:4">
       <c r="A115">
         <v>4</v>
       </c>
       <c r="B115" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C115" t="s">
+        <v>367</v>
+      </c>
+      <c r="D115" t="s">
         <v>369</v>
       </c>
-      <c r="D115" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="116" spans="1:4">
       <c r="A116">
         <v>4</v>
       </c>
       <c r="B116" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C116" t="s">
+        <v>370</v>
+      </c>
+      <c r="D116" t="s">
         <v>372</v>
       </c>
-      <c r="D116" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="117" spans="1:4">
       <c r="A117">
         <v>4</v>
       </c>
       <c r="B117" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C117" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D117" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
       <c r="A118">
         <v>4</v>
       </c>
       <c r="B118" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C118" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D118" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
       <c r="A119">
         <v>4</v>
       </c>
@@ -5682,259 +5686,259 @@
         <v>44</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4">
       <c r="A120">
         <v>4</v>
       </c>
       <c r="B120" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C120" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D120" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
       <c r="A121">
         <v>4</v>
       </c>
       <c r="B121" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C121" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D121" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
       <c r="A122">
         <v>4</v>
       </c>
       <c r="B122" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C122" t="s">
+        <v>381</v>
+      </c>
+      <c r="D122" t="s">
         <v>383</v>
       </c>
-      <c r="D122" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="123" spans="1:4">
       <c r="A123">
         <v>4</v>
       </c>
       <c r="B123" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C123" t="s">
+        <v>384</v>
+      </c>
+      <c r="D123" t="s">
         <v>386</v>
       </c>
-      <c r="D123" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="124" spans="1:4">
       <c r="A124">
         <v>4</v>
       </c>
       <c r="B124" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C124" t="s">
+        <v>387</v>
+      </c>
+      <c r="D124" t="s">
         <v>389</v>
       </c>
-      <c r="D124" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="125" spans="1:4">
       <c r="A125">
         <v>4</v>
       </c>
       <c r="B125" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C125" t="s">
+        <v>390</v>
+      </c>
+      <c r="D125" t="s">
         <v>392</v>
       </c>
-      <c r="D125" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="126" spans="1:4">
       <c r="A126">
         <v>4</v>
       </c>
       <c r="B126" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C126" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D126" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
       <c r="A127">
         <v>4</v>
       </c>
       <c r="B127" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C127" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D127" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
       <c r="A128">
         <v>4</v>
       </c>
       <c r="B128" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C128" t="s">
+        <v>397</v>
+      </c>
+      <c r="D128" t="s">
         <v>399</v>
       </c>
-      <c r="D128" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="129" spans="1:4">
       <c r="A129">
         <v>4</v>
       </c>
       <c r="B129" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C129" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D129" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
       <c r="A130">
         <v>4</v>
       </c>
       <c r="B130" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C130" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D130" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
       <c r="A131">
         <v>4</v>
       </c>
       <c r="B131" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C131" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D131" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
       <c r="A132">
         <v>4</v>
       </c>
       <c r="B132" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C132" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D132" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
       <c r="A133">
         <v>4</v>
       </c>
       <c r="B133" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C133" t="s">
+        <v>407</v>
+      </c>
+      <c r="D133" t="s">
         <v>409</v>
       </c>
-      <c r="D133" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="134" spans="1:4">
       <c r="A134">
         <v>4</v>
       </c>
       <c r="B134" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C134" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D134" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
       <c r="A135">
         <v>4</v>
       </c>
       <c r="B135" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C135" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D135" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
       <c r="A136">
         <v>4</v>
       </c>
       <c r="B136" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C136" t="s">
+        <v>414</v>
+      </c>
+      <c r="D136" t="s">
         <v>416</v>
       </c>
-      <c r="D136" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="137" spans="1:4">
       <c r="A137">
         <v>4</v>
       </c>
       <c r="B137" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C137" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D137" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
       <c r="A138">
         <v>4</v>
       </c>
@@ -5945,94 +5949,94 @@
         <v>47</v>
       </c>
       <c r="D138" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
       <c r="A139">
         <v>4</v>
       </c>
       <c r="B139" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C139" t="s">
+        <v>420</v>
+      </c>
+      <c r="D139" t="s">
         <v>422</v>
       </c>
-      <c r="D139" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="140" spans="1:4">
       <c r="A140">
         <v>4</v>
       </c>
       <c r="B140" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C140" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D140" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
       <c r="A141">
         <v>4</v>
       </c>
       <c r="B141" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C141" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D141" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
       <c r="A142">
         <v>4</v>
       </c>
       <c r="B142" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C142" t="s">
+        <v>427</v>
+      </c>
+      <c r="D142" t="s">
         <v>429</v>
       </c>
-      <c r="D142" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="143" spans="1:4">
       <c r="A143">
         <v>4</v>
       </c>
       <c r="B143" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C143" t="s">
+        <v>430</v>
+      </c>
+      <c r="D143" t="s">
         <v>432</v>
       </c>
-      <c r="D143" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="144" spans="1:4">
       <c r="A144">
         <v>4</v>
       </c>
       <c r="B144" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C144" t="s">
+        <v>433</v>
+      </c>
+      <c r="D144" t="s">
         <v>435</v>
       </c>
-      <c r="D144" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="145" spans="1:4">
       <c r="A145">
         <v>4</v>
       </c>
@@ -6046,175 +6050,175 @@
         <v>4</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4">
       <c r="A146">
         <v>4</v>
       </c>
       <c r="B146" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C146" t="s">
+        <v>436</v>
+      </c>
+      <c r="D146" t="s">
         <v>438</v>
       </c>
-      <c r="D146" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="147" spans="1:4">
       <c r="A147">
         <v>4</v>
       </c>
       <c r="B147" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C147" t="s">
+        <v>439</v>
+      </c>
+      <c r="D147" t="s">
         <v>441</v>
       </c>
-      <c r="D147" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="148" spans="1:4">
       <c r="A148">
         <v>5</v>
       </c>
       <c r="B148" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C148" t="s">
+        <v>442</v>
+      </c>
+      <c r="D148" t="s">
         <v>444</v>
       </c>
-      <c r="D148" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="149" spans="1:4">
       <c r="A149">
         <v>5</v>
       </c>
       <c r="B149" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C149" t="s">
+        <v>445</v>
+      </c>
+      <c r="D149" t="s">
         <v>447</v>
       </c>
-      <c r="D149" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="150" spans="1:4">
       <c r="A150">
         <v>5</v>
       </c>
       <c r="B150" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C150" t="s">
+        <v>448</v>
+      </c>
+      <c r="D150" t="s">
         <v>450</v>
       </c>
-      <c r="D150" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="151" spans="1:4">
       <c r="A151">
         <v>5</v>
       </c>
       <c r="B151" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C151" t="s">
+        <v>451</v>
+      </c>
+      <c r="D151" t="s">
         <v>453</v>
       </c>
-      <c r="D151" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="152" spans="1:4">
       <c r="A152">
         <v>5</v>
       </c>
       <c r="B152" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C152" t="s">
+        <v>454</v>
+      </c>
+      <c r="D152" t="s">
         <v>456</v>
       </c>
-      <c r="D152" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="153" spans="1:4">
       <c r="A153">
         <v>5</v>
       </c>
       <c r="B153" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C153" t="s">
+        <v>457</v>
+      </c>
+      <c r="D153" t="s">
         <v>459</v>
       </c>
-      <c r="D153" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="154" spans="1:4">
       <c r="A154">
         <v>5</v>
       </c>
       <c r="B154" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C154" t="s">
+        <v>460</v>
+      </c>
+      <c r="D154" t="s">
         <v>462</v>
       </c>
-      <c r="D154" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="155" spans="1:4">
       <c r="A155">
         <v>5</v>
       </c>
       <c r="B155" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C155" t="s">
+        <v>463</v>
+      </c>
+      <c r="D155" t="s">
         <v>465</v>
       </c>
-      <c r="D155" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="156" spans="1:4">
       <c r="A156">
         <v>5</v>
       </c>
       <c r="B156" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C156" t="s">
+        <v>466</v>
+      </c>
+      <c r="D156" t="s">
         <v>468</v>
       </c>
-      <c r="D156" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="157" spans="1:4">
       <c r="A157">
         <v>5</v>
       </c>
       <c r="B157" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C157" t="s">
+        <v>469</v>
+      </c>
+      <c r="D157" t="s">
         <v>471</v>
       </c>
-      <c r="D157" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="158" spans="1:4">
       <c r="A158">
         <v>5</v>
       </c>
@@ -6222,139 +6226,139 @@
         <v>49</v>
       </c>
       <c r="C158" t="s">
-        <v>72</v>
+        <v>1014</v>
       </c>
       <c r="D158" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
       <c r="A159">
         <v>5</v>
       </c>
       <c r="B159" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C159" t="s">
+        <v>472</v>
+      </c>
+      <c r="D159" t="s">
         <v>474</v>
       </c>
-      <c r="D159" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="160" spans="1:4">
       <c r="A160">
         <v>5</v>
       </c>
       <c r="B160" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C160" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D160" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
       <c r="A161">
         <v>5</v>
       </c>
       <c r="B161" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C161" t="s">
+        <v>477</v>
+      </c>
+      <c r="D161" t="s">
         <v>479</v>
       </c>
-      <c r="D161" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="162" spans="1:4">
       <c r="A162">
         <v>5</v>
       </c>
       <c r="B162" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C162" t="s">
+        <v>480</v>
+      </c>
+      <c r="D162" t="s">
         <v>482</v>
       </c>
-      <c r="D162" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="163" spans="1:4">
       <c r="A163">
         <v>5</v>
       </c>
       <c r="B163" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C163" t="s">
+        <v>483</v>
+      </c>
+      <c r="D163" t="s">
         <v>485</v>
       </c>
-      <c r="D163" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="164" spans="1:4">
       <c r="A164">
         <v>5</v>
       </c>
       <c r="B164" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C164" t="s">
+        <v>486</v>
+      </c>
+      <c r="D164" t="s">
         <v>488</v>
       </c>
-      <c r="D164" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="165" spans="1:4">
       <c r="A165">
         <v>5</v>
       </c>
       <c r="B165" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C165" t="s">
+        <v>489</v>
+      </c>
+      <c r="D165" t="s">
         <v>491</v>
       </c>
-      <c r="D165" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="166" spans="1:4">
       <c r="A166">
         <v>5</v>
       </c>
       <c r="B166" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C166" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D166" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
       <c r="A167">
         <v>5</v>
       </c>
       <c r="B167" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C167" t="s">
+        <v>492</v>
+      </c>
+      <c r="D167" t="s">
         <v>494</v>
       </c>
-      <c r="D167" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="168" spans="1:4">
       <c r="A168">
         <v>5</v>
       </c>
@@ -6368,175 +6372,175 @@
         <v>18</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4">
       <c r="A169">
         <v>5</v>
       </c>
       <c r="B169" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C169" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D169" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4">
       <c r="A170">
         <v>5</v>
       </c>
       <c r="B170" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C170" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D170" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4">
       <c r="A171">
         <v>5</v>
       </c>
       <c r="B171" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C171" t="s">
+        <v>499</v>
+      </c>
+      <c r="D171" t="s">
         <v>501</v>
       </c>
-      <c r="D171" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="172" spans="1:4">
       <c r="A172">
         <v>5</v>
       </c>
       <c r="B172" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C172" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D172" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
       <c r="A173">
         <v>5</v>
       </c>
       <c r="B173" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C173" t="s">
+        <v>504</v>
+      </c>
+      <c r="D173" t="s">
         <v>506</v>
       </c>
-      <c r="D173" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="174" spans="1:4">
       <c r="A174">
         <v>5</v>
       </c>
       <c r="B174" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C174" t="s">
+        <v>507</v>
+      </c>
+      <c r="D174" t="s">
         <v>509</v>
       </c>
-      <c r="D174" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="175" spans="1:4">
       <c r="A175">
         <v>5</v>
       </c>
       <c r="B175" t="s">
-        <v>513</v>
+        <v>1016</v>
       </c>
       <c r="C175" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D175" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4">
       <c r="A176">
         <v>5</v>
       </c>
       <c r="B176" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C176" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D176" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4">
       <c r="A177">
         <v>5</v>
       </c>
       <c r="B177" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C177" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D177" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4">
       <c r="A178">
         <v>5</v>
       </c>
       <c r="B178" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C178" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D178" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4">
       <c r="A179">
         <v>5</v>
       </c>
       <c r="B179" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="C179" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D179" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4">
       <c r="A180">
         <v>5</v>
       </c>
       <c r="B180" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C180" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D180" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4">
       <c r="A181">
         <v>5</v>
       </c>
@@ -6550,147 +6554,147 @@
         <v>66</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4">
       <c r="A182">
         <v>5</v>
       </c>
       <c r="B182" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C182" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D182" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
       <c r="A183">
         <v>5</v>
       </c>
       <c r="B183" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C183" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D183" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4">
       <c r="A184">
         <v>5</v>
       </c>
       <c r="B184" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="C184" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="D184" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4">
       <c r="A185">
         <v>6</v>
       </c>
       <c r="B185" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C185" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D185" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4">
       <c r="A186">
         <v>6</v>
       </c>
       <c r="B186" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C186" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D186" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4">
       <c r="A187">
         <v>6</v>
       </c>
       <c r="B187" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C187" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D187" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4">
       <c r="A188">
         <v>6</v>
       </c>
       <c r="B188" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C188" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="D188" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4">
       <c r="A189">
         <v>6</v>
       </c>
       <c r="B189" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C189" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D189" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
       <c r="A190">
         <v>6</v>
       </c>
       <c r="B190" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C190" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D190" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4">
       <c r="A191">
         <v>6</v>
       </c>
       <c r="B191" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C191" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D191" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4">
       <c r="A192">
         <v>6</v>
       </c>
@@ -6704,287 +6708,287 @@
         <v>24</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4">
       <c r="A193">
         <v>6</v>
       </c>
       <c r="B193" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C193" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D193" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
       <c r="A194">
         <v>6</v>
       </c>
       <c r="B194" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="C194" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="D194" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
       <c r="A195">
         <v>6</v>
       </c>
       <c r="B195" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C195" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D195" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
       <c r="A196">
         <v>6</v>
       </c>
       <c r="B196" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C196" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D196" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
       <c r="A197">
         <v>6</v>
       </c>
       <c r="B197" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C197" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="D197" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
       <c r="A198">
         <v>6</v>
       </c>
       <c r="B198" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C198" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="D198" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
       <c r="A199">
         <v>6</v>
       </c>
       <c r="B199" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C199" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="D199" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
       <c r="A200">
         <v>6</v>
       </c>
       <c r="B200" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C200" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D200" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
       <c r="A201">
         <v>6</v>
       </c>
       <c r="B201" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="C201" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="D201" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
       <c r="A202">
         <v>6</v>
       </c>
       <c r="B202" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C202" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="D202" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
       <c r="A203">
         <v>6</v>
       </c>
       <c r="B203" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C203" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="D203" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
       <c r="A204">
         <v>6</v>
       </c>
       <c r="B204" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C204" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="D204" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
       <c r="A205">
         <v>6</v>
       </c>
       <c r="B205" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="C205" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="D205" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
       <c r="A206">
         <v>6</v>
       </c>
       <c r="B206" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C206" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="D206" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
       <c r="A207">
         <v>6</v>
       </c>
       <c r="B207" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C207" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="D207" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
       <c r="A208">
         <v>6</v>
       </c>
       <c r="B208" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="C208" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D208" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
       <c r="A209">
         <v>6</v>
       </c>
       <c r="B209" t="s">
+        <v>592</v>
+      </c>
+      <c r="C209" t="s">
+        <v>594</v>
+      </c>
+      <c r="D209" t="s">
         <v>595</v>
       </c>
-      <c r="C209" t="s">
-        <v>597</v>
-      </c>
-      <c r="D209" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="210" spans="1:4">
       <c r="A210">
         <v>6</v>
       </c>
       <c r="B210" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="C210" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="D210" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
       <c r="A211">
         <v>6</v>
       </c>
       <c r="B211" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="C211" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D211" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
       <c r="A212">
         <v>6</v>
       </c>
       <c r="B212" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="C212" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="D212" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
       <c r="A213">
         <v>6</v>
       </c>
@@ -6998,35 +7002,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4">
       <c r="A214">
         <v>6</v>
       </c>
       <c r="B214" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="C214" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="D214" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
       <c r="A215">
         <v>6</v>
       </c>
       <c r="B215" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C215" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D215" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
       <c r="A216">
         <v>6</v>
       </c>
@@ -7037,52 +7041,52 @@
         <v>31</v>
       </c>
       <c r="D216" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
       <c r="A217">
         <v>6</v>
       </c>
       <c r="B217" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C217" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="D217" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
       <c r="A218">
         <v>6</v>
       </c>
       <c r="B218" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="C218" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="D218" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
       <c r="A219">
         <v>6</v>
       </c>
       <c r="B219" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C219" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="D219" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
       <c r="A220">
         <v>6</v>
       </c>
@@ -7096,161 +7100,161 @@
         <v>33</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4">
       <c r="A221">
         <v>7</v>
       </c>
       <c r="B221" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C221" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="D221" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
       <c r="A222">
         <v>7</v>
       </c>
       <c r="B222" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="C222" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="D222" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
       <c r="A223">
         <v>7</v>
       </c>
       <c r="B223" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C223" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="D223" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
       <c r="A224">
         <v>7</v>
       </c>
       <c r="B224" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C224" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="D224" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
       <c r="A225">
         <v>7</v>
       </c>
       <c r="B225" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="C225" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="D225" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
       <c r="A226">
         <v>7</v>
       </c>
       <c r="B226" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C226" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="D226" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
       <c r="A227">
         <v>7</v>
       </c>
       <c r="B227" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C227" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="D227" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
       <c r="A228">
         <v>7</v>
       </c>
       <c r="B228" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C228" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="D228" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
       <c r="A229">
         <v>7</v>
       </c>
       <c r="B229" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C229" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D229" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
       <c r="A230">
         <v>7</v>
       </c>
       <c r="B230" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C230" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D230" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
       <c r="A231">
         <v>7</v>
       </c>
       <c r="B231" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C231" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="D231" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
       <c r="A232">
         <v>7</v>
       </c>
@@ -7264,21 +7268,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:4">
       <c r="A233">
         <v>7</v>
       </c>
       <c r="B233" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C233" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="D233" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
       <c r="A234">
         <v>7</v>
       </c>
@@ -7292,49 +7296,49 @@
         <v>61</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:4">
       <c r="A235">
         <v>7</v>
       </c>
       <c r="B235" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C235" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="D235" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
       <c r="A236">
         <v>7</v>
       </c>
       <c r="B236" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="C236" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="D236" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
       <c r="A237">
         <v>7</v>
       </c>
       <c r="B237" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C237" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="D237" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
       <c r="A238">
         <v>7</v>
       </c>
@@ -7348,315 +7352,315 @@
         <v>70</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:4">
       <c r="A239">
         <v>7</v>
       </c>
       <c r="B239" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C239" t="s">
+        <v>75</v>
+      </c>
+      <c r="D239" t="s">
         <v>77</v>
       </c>
-      <c r="D239" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="240" spans="1:4">
       <c r="A240">
         <v>7</v>
       </c>
       <c r="B240" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C240" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="D240" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
       <c r="A241">
         <v>7</v>
       </c>
       <c r="B241" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="C241" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D241" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
       <c r="A242">
         <v>7</v>
       </c>
       <c r="B242" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="C242" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="D242" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
       <c r="A243">
         <v>7</v>
       </c>
       <c r="B243" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="C243" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="D243" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
       <c r="A244">
         <v>7</v>
       </c>
       <c r="B244" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="C244" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="D244" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
       <c r="A245">
         <v>7</v>
       </c>
       <c r="B245" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="C245" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="D245" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
       <c r="A246">
         <v>7</v>
       </c>
       <c r="B246" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="C246" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="D246" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
       <c r="A247">
         <v>7</v>
       </c>
       <c r="B247" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="C247" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D247" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
       <c r="A248">
         <v>7</v>
       </c>
       <c r="B248" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C248" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="D248" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
       <c r="A249">
         <v>7</v>
       </c>
       <c r="B249" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="C249" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="D249" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
       <c r="A250">
         <v>7</v>
       </c>
       <c r="B250" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="C250" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="D250" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
       <c r="A251">
         <v>8</v>
       </c>
       <c r="B251" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="C251" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="D251" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
       <c r="A252">
         <v>8</v>
       </c>
       <c r="B252" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="C252" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="D252" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
       <c r="A253">
         <v>8</v>
       </c>
       <c r="B253" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C253" t="s">
+        <v>308</v>
+      </c>
+      <c r="D253" t="s">
         <v>310</v>
       </c>
-      <c r="D253" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="254" spans="1:4">
       <c r="A254">
         <v>8</v>
       </c>
       <c r="B254" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C254" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="D254" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
       <c r="A255">
         <v>8</v>
       </c>
       <c r="B255" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="C255" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="D255" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
       <c r="A256">
         <v>8</v>
       </c>
       <c r="B256" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="C256" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D256" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
       <c r="A257">
         <v>8</v>
       </c>
       <c r="B257" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="C257" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="D257" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
       <c r="A258">
         <v>8</v>
       </c>
       <c r="B258" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="C258" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="D258" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
       <c r="A259">
         <v>8</v>
       </c>
       <c r="B259" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C259" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="D259" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
       <c r="A260">
         <v>8</v>
       </c>
       <c r="B260" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C260" t="s">
+        <v>477</v>
+      </c>
+      <c r="D260" t="s">
         <v>479</v>
       </c>
-      <c r="D260" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="261" spans="1:4">
       <c r="A261">
         <v>8</v>
       </c>
@@ -7670,49 +7674,49 @@
         <v>65</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:4">
       <c r="A262">
         <v>8</v>
       </c>
       <c r="B262" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="C262" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="D262" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
       <c r="A263">
         <v>8</v>
       </c>
       <c r="B263" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="C263" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="D263" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
       <c r="A264">
         <v>8</v>
       </c>
       <c r="B264" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="C264" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="D264" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
       <c r="A265">
         <v>8</v>
       </c>
@@ -7723,682 +7727,682 @@
         <v>45</v>
       </c>
       <c r="D265" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
       <c r="A266">
         <v>8</v>
       </c>
       <c r="B266" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="C266" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D266" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
       <c r="A267">
         <v>8</v>
       </c>
       <c r="B267" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C267" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D267" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
       <c r="A268">
         <v>8</v>
       </c>
       <c r="B268" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="C268" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="D268" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
       <c r="A269">
         <v>8</v>
       </c>
       <c r="B269" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="C269" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D269" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
       <c r="A270">
         <v>8</v>
       </c>
       <c r="B270" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="C270" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D270" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
       <c r="A271">
         <v>8</v>
       </c>
       <c r="B271" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="C271" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="D271" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
       <c r="A272">
         <v>8</v>
       </c>
       <c r="B272" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="C272" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="D272" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
       <c r="A273">
         <v>8</v>
       </c>
       <c r="B273" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="C273" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="D273" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
       <c r="A274">
         <v>8</v>
       </c>
       <c r="B274" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="C274" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="D274" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
       <c r="A275">
         <v>8</v>
       </c>
       <c r="B275" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="C275" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="D275" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
       <c r="A276">
         <v>8</v>
       </c>
       <c r="B276" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="C276" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="D276" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
       <c r="A277">
         <v>8</v>
       </c>
       <c r="B277" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C277" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="D277" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
       <c r="A278">
         <v>8</v>
       </c>
       <c r="B278" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="C278" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="D278" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
       <c r="A279">
         <v>8</v>
       </c>
       <c r="B279" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="C279" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="D279" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
       <c r="A280">
         <v>8</v>
       </c>
       <c r="B280" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="C280" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="D280" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
       <c r="A281">
         <v>8</v>
       </c>
       <c r="B281" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="C281" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="D281" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
       <c r="A282">
         <v>8</v>
       </c>
       <c r="B282" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="C282" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="D282" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
       <c r="A283">
         <v>8</v>
       </c>
       <c r="B283" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="C283" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="D283" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
       <c r="A284">
         <v>9</v>
       </c>
       <c r="B284" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="C284" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="D284" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
       <c r="A285">
         <v>9</v>
       </c>
       <c r="B285" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="C285" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="D285" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
       <c r="A286">
         <v>9</v>
       </c>
       <c r="B286" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="C286" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="D286" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
       <c r="A287">
         <v>9</v>
       </c>
       <c r="B287" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="C287" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="D287" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
       <c r="A288">
         <v>9</v>
       </c>
       <c r="B288" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="C288" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="D288" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
       <c r="A289">
         <v>9</v>
       </c>
       <c r="B289" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C289" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D289" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
       <c r="A290">
         <v>9</v>
       </c>
       <c r="B290" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="C290" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="D290" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
       <c r="A291">
         <v>9</v>
       </c>
       <c r="B291" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="C291" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="D291" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
       <c r="A292">
         <v>9</v>
       </c>
       <c r="B292" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="C292" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="D292" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
       <c r="A293">
         <v>9</v>
       </c>
       <c r="B293" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C293" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D293" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
       <c r="A294">
         <v>9</v>
       </c>
       <c r="B294" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="C294" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="D294" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
       <c r="A295">
         <v>9</v>
       </c>
       <c r="B295" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="C295" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="D295" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
       <c r="A296">
         <v>9</v>
       </c>
       <c r="B296" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C296" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="D296" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
       <c r="A297">
         <v>9</v>
       </c>
       <c r="B297" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="C297" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="D297" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
       <c r="A298">
         <v>9</v>
       </c>
       <c r="B298" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C298" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D298" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
       <c r="A299">
         <v>9</v>
       </c>
       <c r="B299" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="C299" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="D299" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
       <c r="A300">
         <v>9</v>
       </c>
       <c r="B300" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="C300" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="D300" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
       <c r="A301">
         <v>9</v>
       </c>
       <c r="B301" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C301" t="s">
+        <v>343</v>
+      </c>
+      <c r="D301" t="s">
         <v>345</v>
       </c>
-      <c r="D301" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="302" spans="1:4">
       <c r="A302">
         <v>9</v>
       </c>
       <c r="B302" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="C302" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="D302" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
       <c r="A303">
         <v>9</v>
       </c>
       <c r="B303" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="C303" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="D303" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
       <c r="A304">
         <v>9</v>
       </c>
       <c r="B304" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="C304" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="D304" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4">
       <c r="A305">
         <v>9</v>
       </c>
       <c r="B305" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="C305" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="D305" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4">
       <c r="A306">
         <v>9</v>
       </c>
       <c r="B306" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C306" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="D306" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
       <c r="A307">
         <v>9</v>
       </c>
       <c r="B307" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="C307" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="D307" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
       <c r="A308">
         <v>9</v>
       </c>
       <c r="B308" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C308" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="D308" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
       <c r="A309">
         <v>9</v>
       </c>
       <c r="B309" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="C309" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="D309" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
       <c r="A310">
         <v>9</v>
       </c>
       <c r="B310" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="C310" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="D310" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
       <c r="A311">
         <v>9</v>
       </c>
       <c r="B311" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C311" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="D311" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4">
       <c r="A312">
         <v>9</v>
       </c>
       <c r="B312" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="C312" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="D312" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
       <c r="A313">
         <v>9</v>
       </c>
       <c r="B313" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="C313" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="D313" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4">
       <c r="A314">
         <v>9</v>
       </c>
@@ -8412,35 +8416,35 @@
         <v>22</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:4">
       <c r="A315">
         <v>9</v>
       </c>
       <c r="B315" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="C315" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="D315" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
       <c r="A316">
         <v>9</v>
       </c>
       <c r="B316" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C316" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D316" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4">
       <c r="A317">
         <v>9</v>
       </c>
@@ -8451,220 +8455,220 @@
         <v>68</v>
       </c>
       <c r="D317" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
       <c r="A318">
         <v>9</v>
       </c>
       <c r="B318" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="C318" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D318" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
       <c r="A319">
         <v>9</v>
       </c>
       <c r="B319" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="C319" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="D319" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
       <c r="A320">
         <v>9</v>
       </c>
       <c r="B320" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="C320" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="D320" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
       <c r="A321">
         <v>10</v>
       </c>
       <c r="B321" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="C321" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="D321" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
       <c r="A322">
         <v>10</v>
       </c>
       <c r="B322" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="C322" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="D322" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
       <c r="A323">
         <v>10</v>
       </c>
       <c r="B323" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="C323" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="D323" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
       <c r="A324">
         <v>10</v>
       </c>
       <c r="B324" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="C324" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="D324" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4">
       <c r="A325">
         <v>10</v>
       </c>
       <c r="B325" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="C325" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="D325" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
       <c r="A326">
         <v>10</v>
       </c>
       <c r="B326" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="C326" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="D326" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4">
       <c r="A327">
         <v>10</v>
       </c>
       <c r="B327" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="C327" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="D327" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4">
       <c r="A328">
         <v>10</v>
       </c>
       <c r="B328" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C328" t="s">
+        <v>98</v>
+      </c>
+      <c r="D328" t="s">
         <v>100</v>
       </c>
-      <c r="D328" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="329" spans="1:4">
       <c r="A329">
         <v>10</v>
       </c>
       <c r="B329" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="C329" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="D329" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4">
       <c r="A330">
         <v>10</v>
       </c>
       <c r="B330" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="C330" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="D330" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4">
       <c r="A331">
         <v>10</v>
       </c>
       <c r="B331" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="C331" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="D331" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4">
       <c r="A332">
         <v>10</v>
       </c>
       <c r="B332" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="C332" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="D332" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4">
       <c r="A333">
         <v>10</v>
       </c>
@@ -8678,63 +8682,63 @@
         <v>39</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:4">
       <c r="A334">
         <v>10</v>
       </c>
       <c r="B334" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="C334" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="D334" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4">
       <c r="A335">
         <v>10</v>
       </c>
       <c r="B335" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="C335" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="D335" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
       <c r="A336">
         <v>10</v>
       </c>
       <c r="B336" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="C336" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="D336" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4">
       <c r="A337">
         <v>10</v>
       </c>
       <c r="B337" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="C337" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="D337" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4">
       <c r="A338">
         <v>10</v>
       </c>
@@ -8748,455 +8752,455 @@
         <v>55</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:4">
       <c r="A339">
         <v>10</v>
       </c>
       <c r="B339" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="C339" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="D339" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4">
       <c r="A340">
         <v>10</v>
       </c>
       <c r="B340" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="C340" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="D340" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4">
       <c r="A341">
         <v>10</v>
       </c>
       <c r="B341" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="C341" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="D341" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4">
       <c r="A342">
         <v>10</v>
       </c>
       <c r="B342" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C342" t="s">
+        <v>141</v>
+      </c>
+      <c r="D342" t="s">
         <v>143</v>
       </c>
-      <c r="D342" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="343" spans="1:4">
       <c r="A343">
         <v>10</v>
       </c>
       <c r="B343" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="C343" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="D343" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4">
       <c r="A344">
         <v>10</v>
       </c>
       <c r="B344" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="C344" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="D344" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4">
       <c r="A345">
         <v>10</v>
       </c>
       <c r="B345" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="C345" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="D345" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4">
       <c r="A346">
         <v>10</v>
       </c>
       <c r="B346" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="C346" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="D346" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4">
       <c r="A347">
         <v>10</v>
       </c>
       <c r="B347" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C347" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="D347" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4">
       <c r="A348">
         <v>10</v>
       </c>
       <c r="B348" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="C348" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="D348" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4">
       <c r="A349">
         <v>10</v>
       </c>
       <c r="B349" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C349" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="D349" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4">
       <c r="A350">
         <v>10</v>
       </c>
       <c r="B350" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="C350" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="D350" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.3">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4">
       <c r="A351">
         <v>10</v>
       </c>
       <c r="B351" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="C351" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="D351" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.3">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4">
       <c r="A352">
         <v>10</v>
       </c>
       <c r="B352" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="C352" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="D352" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4">
       <c r="A353">
         <v>10</v>
       </c>
       <c r="B353" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="C353" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="D353" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4">
       <c r="A354">
         <v>10</v>
       </c>
       <c r="B354" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C354" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D354" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4">
       <c r="A355">
         <v>10</v>
       </c>
       <c r="B355" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="C355" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D355" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4">
       <c r="A356">
         <v>11</v>
       </c>
       <c r="B356" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="C356" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="D356" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4">
       <c r="A357">
         <v>11</v>
       </c>
       <c r="B357" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="C357" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="D357" t="s">
-        <v>937</v>
-      </c>
-    </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4">
       <c r="A358">
         <v>11</v>
       </c>
       <c r="B358" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="C358" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="D358" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4">
       <c r="A359">
         <v>11</v>
       </c>
       <c r="B359" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="C359" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="D359" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4">
       <c r="A360">
         <v>11</v>
       </c>
       <c r="B360" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C360" t="s">
+        <v>95</v>
+      </c>
+      <c r="D360" t="s">
         <v>97</v>
       </c>
-      <c r="D360" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="361" spans="1:4">
       <c r="A361">
         <v>11</v>
       </c>
       <c r="B361" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="C361" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="D361" t="s">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4">
       <c r="A362">
         <v>11</v>
       </c>
       <c r="B362" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="C362" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="D362" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4">
       <c r="A363">
         <v>11</v>
       </c>
       <c r="B363" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="C363" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="D363" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4">
       <c r="A364">
         <v>11</v>
       </c>
       <c r="B364" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="C364" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="D364" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4">
       <c r="A365">
         <v>11</v>
       </c>
       <c r="B365" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="C365" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="D365" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4">
       <c r="A366">
         <v>11</v>
       </c>
       <c r="B366" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="C366" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="D366" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4">
       <c r="A367">
         <v>11</v>
       </c>
       <c r="B367" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C367" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D367" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4">
       <c r="A368">
         <v>11</v>
       </c>
       <c r="B368" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C368" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="D368" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4">
       <c r="A369">
         <v>11</v>
       </c>
       <c r="B369" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="C369" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="D369" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4">
       <c r="A370">
         <v>11</v>
       </c>
       <c r="B370" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="C370" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="D370" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4">
       <c r="A371">
         <v>11</v>
       </c>
@@ -9210,49 +9214,49 @@
         <v>14</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:4">
       <c r="A372">
         <v>11</v>
       </c>
       <c r="B372" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="C372" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="D372" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4">
       <c r="A373">
         <v>11</v>
       </c>
       <c r="B373" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="C373" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="D373" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4">
       <c r="A374">
         <v>11</v>
       </c>
       <c r="B374" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="C374" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="D374" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4">
       <c r="A375">
         <v>11</v>
       </c>
@@ -9266,161 +9270,161 @@
         <v>10</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:4">
       <c r="A376">
         <v>11</v>
       </c>
       <c r="B376" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="C376" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="D376" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4">
       <c r="A377">
         <v>11</v>
       </c>
       <c r="B377" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="C377" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="D377" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4">
       <c r="A378">
         <v>11</v>
       </c>
       <c r="B378" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="C378" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="D378" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4">
       <c r="A379">
         <v>11</v>
       </c>
       <c r="B379" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="C379" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="D379" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4">
       <c r="A380">
         <v>11</v>
       </c>
       <c r="B380" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="C380" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="D380" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4">
       <c r="A381">
         <v>11</v>
       </c>
       <c r="B381" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="C381" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="D381" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4">
       <c r="A382">
         <v>11</v>
       </c>
       <c r="B382" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="C382" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="D382" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4">
       <c r="A383">
         <v>11</v>
       </c>
       <c r="B383" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="C383" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="D383" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4">
       <c r="A384">
         <v>11</v>
       </c>
       <c r="B384" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="C384" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="D384" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4">
       <c r="A385">
         <v>11</v>
       </c>
       <c r="B385" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="C385" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="D385" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4">
       <c r="A386">
         <v>11</v>
       </c>
       <c r="B386" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="C386" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="D386" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4">
       <c r="A387">
         <v>11</v>
       </c>
@@ -9434,74 +9438,74 @@
         <v>35</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:4">
       <c r="A388">
         <v>11</v>
       </c>
       <c r="B388" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="C388" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D388" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4">
       <c r="A389">
         <v>11</v>
       </c>
       <c r="B389" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="C389" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D389" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4">
       <c r="A390">
         <v>11</v>
       </c>
       <c r="B390" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="C390" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="D390" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4">
       <c r="A391">
         <v>11</v>
       </c>
       <c r="B391" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="C391" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="D391" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4">
       <c r="A392">
         <v>11</v>
       </c>
       <c r="B392" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="C392" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="D392" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
     </row>
   </sheetData>

--- a/N5.xlsx
+++ b/N5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sunsh\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25507703-D9FA-4626-B041-1AE6463DA5E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DDD6713-361A-4430-A021-3F2CF8BEBA93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="1017">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="1018">
   <si>
     <t>東京</t>
   </si>
@@ -1799,9 +1799,6 @@
   </si>
   <si>
     <t>うしろ</t>
-  </si>
-  <si>
-    <t>後面</t>
   </si>
   <si>
     <t>後ろ</t>
@@ -3075,6 +3072,14 @@
   </si>
   <si>
     <t>まいつき</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>あと</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>之後、等一下、剩下</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -3082,7 +3087,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3239,6 +3244,11 @@
       <name val="新細明體"/>
       <family val="3"/>
       <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="新細明體"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -3668,11 +3678,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="41">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - 輔色1" xfId="18" builtinId="30" customBuiltin="1"/>
@@ -4022,16 +4033,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="16.5">
       <c r="A1" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1008</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1009</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -4938,7 +4949,7 @@
         <v>242</v>
       </c>
       <c r="C66" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="D66" t="s">
         <v>243</v>
@@ -5355,10 +5366,10 @@
         <v>3</v>
       </c>
       <c r="B96" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C96" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="D96" t="s">
         <v>243</v>
@@ -6226,10 +6237,10 @@
         <v>49</v>
       </c>
       <c r="C158" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D158" t="s">
         <v>1014</v>
-      </c>
-      <c r="D158" t="s">
-        <v>1015</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -6461,7 +6472,7 @@
         <v>5</v>
       </c>
       <c r="B175" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="C175" t="s">
         <v>510</v>
@@ -6923,13 +6934,13 @@
         <v>6</v>
       </c>
       <c r="B208" t="s">
-        <v>592</v>
+        <v>1016</v>
       </c>
       <c r="C208" t="s">
         <v>591</v>
       </c>
-      <c r="D208" t="s">
-        <v>593</v>
+      <c r="D208" s="2" t="s">
+        <v>1017</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -6940,10 +6951,10 @@
         <v>592</v>
       </c>
       <c r="C209" t="s">
+        <v>593</v>
+      </c>
+      <c r="D209" t="s">
         <v>594</v>
-      </c>
-      <c r="D209" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -6951,13 +6962,13 @@
         <v>6</v>
       </c>
       <c r="B210" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C210" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D210" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -6965,13 +6976,13 @@
         <v>6</v>
       </c>
       <c r="B211" t="s">
+        <v>598</v>
+      </c>
+      <c r="C211" t="s">
+        <v>597</v>
+      </c>
+      <c r="D211" t="s">
         <v>599</v>
-      </c>
-      <c r="C211" t="s">
-        <v>598</v>
-      </c>
-      <c r="D211" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -6979,13 +6990,13 @@
         <v>6</v>
       </c>
       <c r="B212" t="s">
+        <v>601</v>
+      </c>
+      <c r="C212" t="s">
+        <v>600</v>
+      </c>
+      <c r="D212" t="s">
         <v>602</v>
-      </c>
-      <c r="C212" t="s">
-        <v>601</v>
-      </c>
-      <c r="D212" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -7007,13 +7018,13 @@
         <v>6</v>
       </c>
       <c r="B214" t="s">
+        <v>604</v>
+      </c>
+      <c r="C214" t="s">
+        <v>603</v>
+      </c>
+      <c r="D214" t="s">
         <v>605</v>
-      </c>
-      <c r="C214" t="s">
-        <v>604</v>
-      </c>
-      <c r="D214" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -7021,13 +7032,13 @@
         <v>6</v>
       </c>
       <c r="B215" t="s">
+        <v>607</v>
+      </c>
+      <c r="C215" t="s">
+        <v>606</v>
+      </c>
+      <c r="D215" t="s">
         <v>608</v>
-      </c>
-      <c r="C215" t="s">
-        <v>607</v>
-      </c>
-      <c r="D215" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -7041,7 +7052,7 @@
         <v>31</v>
       </c>
       <c r="D216" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -7049,13 +7060,13 @@
         <v>6</v>
       </c>
       <c r="B217" t="s">
+        <v>611</v>
+      </c>
+      <c r="C217" t="s">
+        <v>610</v>
+      </c>
+      <c r="D217" t="s">
         <v>612</v>
-      </c>
-      <c r="C217" t="s">
-        <v>611</v>
-      </c>
-      <c r="D217" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -7063,13 +7074,13 @@
         <v>6</v>
       </c>
       <c r="B218" t="s">
+        <v>614</v>
+      </c>
+      <c r="C218" t="s">
+        <v>613</v>
+      </c>
+      <c r="D218" t="s">
         <v>615</v>
-      </c>
-      <c r="C218" t="s">
-        <v>614</v>
-      </c>
-      <c r="D218" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -7077,13 +7088,13 @@
         <v>6</v>
       </c>
       <c r="B219" t="s">
+        <v>617</v>
+      </c>
+      <c r="C219" t="s">
+        <v>616</v>
+      </c>
+      <c r="D219" t="s">
         <v>618</v>
-      </c>
-      <c r="C219" t="s">
-        <v>617</v>
-      </c>
-      <c r="D219" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -7105,13 +7116,13 @@
         <v>7</v>
       </c>
       <c r="B221" t="s">
+        <v>620</v>
+      </c>
+      <c r="C221" t="s">
+        <v>619</v>
+      </c>
+      <c r="D221" t="s">
         <v>621</v>
-      </c>
-      <c r="C221" t="s">
-        <v>620</v>
-      </c>
-      <c r="D221" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -7119,13 +7130,13 @@
         <v>7</v>
       </c>
       <c r="B222" t="s">
+        <v>623</v>
+      </c>
+      <c r="C222" t="s">
+        <v>622</v>
+      </c>
+      <c r="D222" t="s">
         <v>624</v>
-      </c>
-      <c r="C222" t="s">
-        <v>623</v>
-      </c>
-      <c r="D222" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -7133,13 +7144,13 @@
         <v>7</v>
       </c>
       <c r="B223" t="s">
+        <v>626</v>
+      </c>
+      <c r="C223" t="s">
+        <v>625</v>
+      </c>
+      <c r="D223" t="s">
         <v>627</v>
-      </c>
-      <c r="C223" t="s">
-        <v>626</v>
-      </c>
-      <c r="D223" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -7147,13 +7158,13 @@
         <v>7</v>
       </c>
       <c r="B224" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C224" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D224" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -7161,13 +7172,13 @@
         <v>7</v>
       </c>
       <c r="B225" t="s">
+        <v>631</v>
+      </c>
+      <c r="C225" t="s">
+        <v>630</v>
+      </c>
+      <c r="D225" t="s">
         <v>632</v>
-      </c>
-      <c r="C225" t="s">
-        <v>631</v>
-      </c>
-      <c r="D225" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -7175,13 +7186,13 @@
         <v>7</v>
       </c>
       <c r="B226" t="s">
+        <v>634</v>
+      </c>
+      <c r="C226" t="s">
+        <v>633</v>
+      </c>
+      <c r="D226" t="s">
         <v>635</v>
-      </c>
-      <c r="C226" t="s">
-        <v>634</v>
-      </c>
-      <c r="D226" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -7189,13 +7200,13 @@
         <v>7</v>
       </c>
       <c r="B227" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C227" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D227" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -7203,13 +7214,13 @@
         <v>7</v>
       </c>
       <c r="B228" t="s">
+        <v>639</v>
+      </c>
+      <c r="C228" t="s">
+        <v>638</v>
+      </c>
+      <c r="D228" t="s">
         <v>640</v>
-      </c>
-      <c r="C228" t="s">
-        <v>639</v>
-      </c>
-      <c r="D228" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -7217,13 +7228,13 @@
         <v>7</v>
       </c>
       <c r="B229" t="s">
+        <v>642</v>
+      </c>
+      <c r="C229" t="s">
+        <v>641</v>
+      </c>
+      <c r="D229" t="s">
         <v>643</v>
-      </c>
-      <c r="C229" t="s">
-        <v>642</v>
-      </c>
-      <c r="D229" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -7231,13 +7242,13 @@
         <v>7</v>
       </c>
       <c r="B230" t="s">
+        <v>645</v>
+      </c>
+      <c r="C230" t="s">
+        <v>644</v>
+      </c>
+      <c r="D230" t="s">
         <v>646</v>
-      </c>
-      <c r="C230" t="s">
-        <v>645</v>
-      </c>
-      <c r="D230" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -7245,13 +7256,13 @@
         <v>7</v>
       </c>
       <c r="B231" t="s">
+        <v>648</v>
+      </c>
+      <c r="C231" t="s">
+        <v>647</v>
+      </c>
+      <c r="D231" t="s">
         <v>649</v>
-      </c>
-      <c r="C231" t="s">
-        <v>648</v>
-      </c>
-      <c r="D231" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -7273,13 +7284,13 @@
         <v>7</v>
       </c>
       <c r="B233" t="s">
+        <v>651</v>
+      </c>
+      <c r="C233" t="s">
+        <v>650</v>
+      </c>
+      <c r="D233" t="s">
         <v>652</v>
-      </c>
-      <c r="C233" t="s">
-        <v>651</v>
-      </c>
-      <c r="D233" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -7301,13 +7312,13 @@
         <v>7</v>
       </c>
       <c r="B235" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C235" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D235" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -7315,13 +7326,13 @@
         <v>7</v>
       </c>
       <c r="B236" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C236" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D236" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -7329,13 +7340,13 @@
         <v>7</v>
       </c>
       <c r="B237" t="s">
+        <v>658</v>
+      </c>
+      <c r="C237" t="s">
+        <v>657</v>
+      </c>
+      <c r="D237" t="s">
         <v>659</v>
-      </c>
-      <c r="C237" t="s">
-        <v>658</v>
-      </c>
-      <c r="D237" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -7371,13 +7382,13 @@
         <v>7</v>
       </c>
       <c r="B240" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C240" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D240" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -7385,13 +7396,13 @@
         <v>7</v>
       </c>
       <c r="B241" t="s">
+        <v>663</v>
+      </c>
+      <c r="C241" t="s">
+        <v>662</v>
+      </c>
+      <c r="D241" t="s">
         <v>664</v>
-      </c>
-      <c r="C241" t="s">
-        <v>663</v>
-      </c>
-      <c r="D241" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -7399,13 +7410,13 @@
         <v>7</v>
       </c>
       <c r="B242" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C242" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D242" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -7413,13 +7424,13 @@
         <v>7</v>
       </c>
       <c r="B243" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C243" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D243" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -7427,13 +7438,13 @@
         <v>7</v>
       </c>
       <c r="B244" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C244" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D244" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -7441,13 +7452,13 @@
         <v>7</v>
       </c>
       <c r="B245" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C245" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D245" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -7455,13 +7466,13 @@
         <v>7</v>
       </c>
       <c r="B246" t="s">
+        <v>674</v>
+      </c>
+      <c r="C246" t="s">
+        <v>673</v>
+      </c>
+      <c r="D246" t="s">
         <v>675</v>
-      </c>
-      <c r="C246" t="s">
-        <v>674</v>
-      </c>
-      <c r="D246" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -7469,13 +7480,13 @@
         <v>7</v>
       </c>
       <c r="B247" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C247" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D247" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -7483,13 +7494,13 @@
         <v>7</v>
       </c>
       <c r="B248" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C248" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D248" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -7497,13 +7508,13 @@
         <v>7</v>
       </c>
       <c r="B249" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C249" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D249" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -7511,13 +7522,13 @@
         <v>7</v>
       </c>
       <c r="B250" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C250" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D250" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -7525,13 +7536,13 @@
         <v>8</v>
       </c>
       <c r="B251" t="s">
+        <v>685</v>
+      </c>
+      <c r="C251" t="s">
+        <v>684</v>
+      </c>
+      <c r="D251" t="s">
         <v>686</v>
-      </c>
-      <c r="C251" t="s">
-        <v>685</v>
-      </c>
-      <c r="D251" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -7539,13 +7550,13 @@
         <v>8</v>
       </c>
       <c r="B252" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C252" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D252" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -7567,13 +7578,13 @@
         <v>8</v>
       </c>
       <c r="B254" t="s">
+        <v>690</v>
+      </c>
+      <c r="C254" t="s">
+        <v>689</v>
+      </c>
+      <c r="D254" t="s">
         <v>691</v>
-      </c>
-      <c r="C254" t="s">
-        <v>690</v>
-      </c>
-      <c r="D254" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -7581,13 +7592,13 @@
         <v>8</v>
       </c>
       <c r="B255" t="s">
+        <v>693</v>
+      </c>
+      <c r="C255" t="s">
+        <v>692</v>
+      </c>
+      <c r="D255" t="s">
         <v>694</v>
-      </c>
-      <c r="C255" t="s">
-        <v>693</v>
-      </c>
-      <c r="D255" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -7595,13 +7606,13 @@
         <v>8</v>
       </c>
       <c r="B256" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C256" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D256" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -7609,13 +7620,13 @@
         <v>8</v>
       </c>
       <c r="B257" t="s">
+        <v>698</v>
+      </c>
+      <c r="C257" t="s">
+        <v>697</v>
+      </c>
+      <c r="D257" t="s">
         <v>699</v>
-      </c>
-      <c r="C257" t="s">
-        <v>698</v>
-      </c>
-      <c r="D257" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -7623,13 +7634,13 @@
         <v>8</v>
       </c>
       <c r="B258" t="s">
+        <v>701</v>
+      </c>
+      <c r="C258" t="s">
+        <v>700</v>
+      </c>
+      <c r="D258" t="s">
         <v>702</v>
-      </c>
-      <c r="C258" t="s">
-        <v>701</v>
-      </c>
-      <c r="D258" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -7637,13 +7648,13 @@
         <v>8</v>
       </c>
       <c r="B259" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C259" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D259" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -7679,13 +7690,13 @@
         <v>8</v>
       </c>
       <c r="B262" t="s">
+        <v>706</v>
+      </c>
+      <c r="C262" t="s">
+        <v>705</v>
+      </c>
+      <c r="D262" t="s">
         <v>707</v>
-      </c>
-      <c r="C262" t="s">
-        <v>706</v>
-      </c>
-      <c r="D262" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -7693,13 +7704,13 @@
         <v>8</v>
       </c>
       <c r="B263" t="s">
+        <v>709</v>
+      </c>
+      <c r="C263" t="s">
+        <v>708</v>
+      </c>
+      <c r="D263" t="s">
         <v>710</v>
-      </c>
-      <c r="C263" t="s">
-        <v>709</v>
-      </c>
-      <c r="D263" t="s">
-        <v>711</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -7707,13 +7718,13 @@
         <v>8</v>
       </c>
       <c r="B264" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C264" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D264" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -7727,7 +7738,7 @@
         <v>45</v>
       </c>
       <c r="D265" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -7735,13 +7746,13 @@
         <v>8</v>
       </c>
       <c r="B266" t="s">
+        <v>715</v>
+      </c>
+      <c r="C266" t="s">
+        <v>714</v>
+      </c>
+      <c r="D266" t="s">
         <v>716</v>
-      </c>
-      <c r="C266" t="s">
-        <v>715</v>
-      </c>
-      <c r="D266" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -7755,7 +7766,7 @@
         <v>486</v>
       </c>
       <c r="D267" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -7763,13 +7774,13 @@
         <v>8</v>
       </c>
       <c r="B268" t="s">
+        <v>719</v>
+      </c>
+      <c r="C268" t="s">
+        <v>718</v>
+      </c>
+      <c r="D268" t="s">
         <v>720</v>
-      </c>
-      <c r="C268" t="s">
-        <v>719</v>
-      </c>
-      <c r="D268" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -7777,13 +7788,13 @@
         <v>8</v>
       </c>
       <c r="B269" t="s">
+        <v>722</v>
+      </c>
+      <c r="C269" t="s">
+        <v>721</v>
+      </c>
+      <c r="D269" t="s">
         <v>723</v>
-      </c>
-      <c r="C269" t="s">
-        <v>722</v>
-      </c>
-      <c r="D269" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -7791,13 +7802,13 @@
         <v>8</v>
       </c>
       <c r="B270" t="s">
+        <v>725</v>
+      </c>
+      <c r="C270" t="s">
+        <v>724</v>
+      </c>
+      <c r="D270" t="s">
         <v>726</v>
-      </c>
-      <c r="C270" t="s">
-        <v>725</v>
-      </c>
-      <c r="D270" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -7805,13 +7816,13 @@
         <v>8</v>
       </c>
       <c r="B271" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C271" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D271" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -7819,13 +7830,13 @@
         <v>8</v>
       </c>
       <c r="B272" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C272" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D272" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -7833,13 +7844,13 @@
         <v>8</v>
       </c>
       <c r="B273" t="s">
+        <v>732</v>
+      </c>
+      <c r="C273" t="s">
+        <v>731</v>
+      </c>
+      <c r="D273" t="s">
         <v>733</v>
-      </c>
-      <c r="C273" t="s">
-        <v>732</v>
-      </c>
-      <c r="D273" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -7847,13 +7858,13 @@
         <v>8</v>
       </c>
       <c r="B274" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C274" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D274" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -7861,13 +7872,13 @@
         <v>8</v>
       </c>
       <c r="B275" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C275" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D275" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -7875,10 +7886,10 @@
         <v>8</v>
       </c>
       <c r="B276" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C276" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D276" t="s">
         <v>82</v>
@@ -7889,13 +7900,13 @@
         <v>8</v>
       </c>
       <c r="B277" t="s">
+        <v>741</v>
+      </c>
+      <c r="C277" t="s">
+        <v>740</v>
+      </c>
+      <c r="D277" t="s">
         <v>742</v>
-      </c>
-      <c r="C277" t="s">
-        <v>741</v>
-      </c>
-      <c r="D277" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -7903,13 +7914,13 @@
         <v>8</v>
       </c>
       <c r="B278" t="s">
+        <v>744</v>
+      </c>
+      <c r="C278" t="s">
+        <v>743</v>
+      </c>
+      <c r="D278" t="s">
         <v>745</v>
-      </c>
-      <c r="C278" t="s">
-        <v>744</v>
-      </c>
-      <c r="D278" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -7917,13 +7928,13 @@
         <v>8</v>
       </c>
       <c r="B279" t="s">
+        <v>747</v>
+      </c>
+      <c r="C279" t="s">
+        <v>746</v>
+      </c>
+      <c r="D279" t="s">
         <v>748</v>
-      </c>
-      <c r="C279" t="s">
-        <v>747</v>
-      </c>
-      <c r="D279" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -7931,13 +7942,13 @@
         <v>8</v>
       </c>
       <c r="B280" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C280" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D280" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -7945,13 +7956,13 @@
         <v>8</v>
       </c>
       <c r="B281" t="s">
+        <v>752</v>
+      </c>
+      <c r="C281" t="s">
+        <v>751</v>
+      </c>
+      <c r="D281" t="s">
         <v>753</v>
-      </c>
-      <c r="C281" t="s">
-        <v>752</v>
-      </c>
-      <c r="D281" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -7959,13 +7970,13 @@
         <v>8</v>
       </c>
       <c r="B282" t="s">
+        <v>755</v>
+      </c>
+      <c r="C282" t="s">
+        <v>754</v>
+      </c>
+      <c r="D282" t="s">
         <v>756</v>
-      </c>
-      <c r="C282" t="s">
-        <v>755</v>
-      </c>
-      <c r="D282" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -7973,13 +7984,13 @@
         <v>8</v>
       </c>
       <c r="B283" t="s">
+        <v>758</v>
+      </c>
+      <c r="C283" t="s">
+        <v>757</v>
+      </c>
+      <c r="D283" t="s">
         <v>759</v>
-      </c>
-      <c r="C283" t="s">
-        <v>758</v>
-      </c>
-      <c r="D283" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -7987,13 +7998,13 @@
         <v>9</v>
       </c>
       <c r="B284" t="s">
+        <v>761</v>
+      </c>
+      <c r="C284" t="s">
+        <v>760</v>
+      </c>
+      <c r="D284" t="s">
         <v>762</v>
-      </c>
-      <c r="C284" t="s">
-        <v>761</v>
-      </c>
-      <c r="D284" t="s">
-        <v>763</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -8001,13 +8012,13 @@
         <v>9</v>
       </c>
       <c r="B285" t="s">
+        <v>764</v>
+      </c>
+      <c r="C285" t="s">
+        <v>763</v>
+      </c>
+      <c r="D285" t="s">
         <v>765</v>
-      </c>
-      <c r="C285" t="s">
-        <v>764</v>
-      </c>
-      <c r="D285" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -8015,13 +8026,13 @@
         <v>9</v>
       </c>
       <c r="B286" t="s">
+        <v>767</v>
+      </c>
+      <c r="C286" t="s">
+        <v>766</v>
+      </c>
+      <c r="D286" t="s">
         <v>768</v>
-      </c>
-      <c r="C286" t="s">
-        <v>767</v>
-      </c>
-      <c r="D286" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -8029,13 +8040,13 @@
         <v>9</v>
       </c>
       <c r="B287" t="s">
+        <v>770</v>
+      </c>
+      <c r="C287" t="s">
+        <v>769</v>
+      </c>
+      <c r="D287" t="s">
         <v>771</v>
-      </c>
-      <c r="C287" t="s">
-        <v>770</v>
-      </c>
-      <c r="D287" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -8043,13 +8054,13 @@
         <v>9</v>
       </c>
       <c r="B288" t="s">
+        <v>773</v>
+      </c>
+      <c r="C288" t="s">
+        <v>772</v>
+      </c>
+      <c r="D288" t="s">
         <v>774</v>
-      </c>
-      <c r="C288" t="s">
-        <v>773</v>
-      </c>
-      <c r="D288" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -8071,13 +8082,13 @@
         <v>9</v>
       </c>
       <c r="B290" t="s">
+        <v>776</v>
+      </c>
+      <c r="C290" t="s">
+        <v>775</v>
+      </c>
+      <c r="D290" t="s">
         <v>777</v>
-      </c>
-      <c r="C290" t="s">
-        <v>776</v>
-      </c>
-      <c r="D290" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -8085,13 +8096,13 @@
         <v>9</v>
       </c>
       <c r="B291" t="s">
+        <v>779</v>
+      </c>
+      <c r="C291" t="s">
+        <v>778</v>
+      </c>
+      <c r="D291" t="s">
         <v>780</v>
-      </c>
-      <c r="C291" t="s">
-        <v>779</v>
-      </c>
-      <c r="D291" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -8099,13 +8110,13 @@
         <v>9</v>
       </c>
       <c r="B292" t="s">
+        <v>782</v>
+      </c>
+      <c r="C292" t="s">
+        <v>781</v>
+      </c>
+      <c r="D292" t="s">
         <v>783</v>
-      </c>
-      <c r="C292" t="s">
-        <v>782</v>
-      </c>
-      <c r="D292" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -8127,13 +8138,13 @@
         <v>9</v>
       </c>
       <c r="B294" t="s">
+        <v>785</v>
+      </c>
+      <c r="C294" t="s">
+        <v>784</v>
+      </c>
+      <c r="D294" t="s">
         <v>786</v>
-      </c>
-      <c r="C294" t="s">
-        <v>785</v>
-      </c>
-      <c r="D294" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -8141,13 +8152,13 @@
         <v>9</v>
       </c>
       <c r="B295" t="s">
+        <v>788</v>
+      </c>
+      <c r="C295" t="s">
+        <v>787</v>
+      </c>
+      <c r="D295" t="s">
         <v>789</v>
-      </c>
-      <c r="C295" t="s">
-        <v>788</v>
-      </c>
-      <c r="D295" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -8155,13 +8166,13 @@
         <v>9</v>
       </c>
       <c r="B296" t="s">
+        <v>791</v>
+      </c>
+      <c r="C296" t="s">
+        <v>790</v>
+      </c>
+      <c r="D296" t="s">
         <v>792</v>
-      </c>
-      <c r="C296" t="s">
-        <v>791</v>
-      </c>
-      <c r="D296" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -8169,13 +8180,13 @@
         <v>9</v>
       </c>
       <c r="B297" t="s">
+        <v>794</v>
+      </c>
+      <c r="C297" t="s">
+        <v>793</v>
+      </c>
+      <c r="D297" t="s">
         <v>795</v>
-      </c>
-      <c r="C297" t="s">
-        <v>794</v>
-      </c>
-      <c r="D297" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -8197,13 +8208,13 @@
         <v>9</v>
       </c>
       <c r="B299" t="s">
+        <v>797</v>
+      </c>
+      <c r="C299" t="s">
+        <v>796</v>
+      </c>
+      <c r="D299" t="s">
         <v>798</v>
-      </c>
-      <c r="C299" t="s">
-        <v>797</v>
-      </c>
-      <c r="D299" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -8211,13 +8222,13 @@
         <v>9</v>
       </c>
       <c r="B300" t="s">
+        <v>800</v>
+      </c>
+      <c r="C300" t="s">
+        <v>799</v>
+      </c>
+      <c r="D300" t="s">
         <v>801</v>
-      </c>
-      <c r="C300" t="s">
-        <v>800</v>
-      </c>
-      <c r="D300" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -8239,13 +8250,13 @@
         <v>9</v>
       </c>
       <c r="B302" t="s">
+        <v>803</v>
+      </c>
+      <c r="C302" t="s">
+        <v>802</v>
+      </c>
+      <c r="D302" t="s">
         <v>804</v>
-      </c>
-      <c r="C302" t="s">
-        <v>803</v>
-      </c>
-      <c r="D302" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -8253,13 +8264,13 @@
         <v>9</v>
       </c>
       <c r="B303" t="s">
+        <v>806</v>
+      </c>
+      <c r="C303" t="s">
+        <v>805</v>
+      </c>
+      <c r="D303" t="s">
         <v>807</v>
-      </c>
-      <c r="C303" t="s">
-        <v>806</v>
-      </c>
-      <c r="D303" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -8267,13 +8278,13 @@
         <v>9</v>
       </c>
       <c r="B304" t="s">
+        <v>809</v>
+      </c>
+      <c r="C304" t="s">
+        <v>808</v>
+      </c>
+      <c r="D304" t="s">
         <v>810</v>
-      </c>
-      <c r="C304" t="s">
-        <v>809</v>
-      </c>
-      <c r="D304" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -8281,13 +8292,13 @@
         <v>9</v>
       </c>
       <c r="B305" t="s">
+        <v>812</v>
+      </c>
+      <c r="C305" t="s">
+        <v>811</v>
+      </c>
+      <c r="D305" t="s">
         <v>813</v>
-      </c>
-      <c r="C305" t="s">
-        <v>812</v>
-      </c>
-      <c r="D305" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -8295,13 +8306,13 @@
         <v>9</v>
       </c>
       <c r="B306" t="s">
+        <v>815</v>
+      </c>
+      <c r="C306" t="s">
+        <v>814</v>
+      </c>
+      <c r="D306" t="s">
         <v>816</v>
-      </c>
-      <c r="C306" t="s">
-        <v>815</v>
-      </c>
-      <c r="D306" t="s">
-        <v>817</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -8309,13 +8320,13 @@
         <v>9</v>
       </c>
       <c r="B307" t="s">
+        <v>818</v>
+      </c>
+      <c r="C307" t="s">
+        <v>817</v>
+      </c>
+      <c r="D307" t="s">
         <v>819</v>
-      </c>
-      <c r="C307" t="s">
-        <v>818</v>
-      </c>
-      <c r="D307" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -8323,13 +8334,13 @@
         <v>9</v>
       </c>
       <c r="B308" t="s">
+        <v>821</v>
+      </c>
+      <c r="C308" t="s">
+        <v>820</v>
+      </c>
+      <c r="D308" t="s">
         <v>822</v>
-      </c>
-      <c r="C308" t="s">
-        <v>821</v>
-      </c>
-      <c r="D308" t="s">
-        <v>823</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -8337,13 +8348,13 @@
         <v>9</v>
       </c>
       <c r="B309" t="s">
+        <v>824</v>
+      </c>
+      <c r="C309" t="s">
+        <v>823</v>
+      </c>
+      <c r="D309" t="s">
         <v>825</v>
-      </c>
-      <c r="C309" t="s">
-        <v>824</v>
-      </c>
-      <c r="D309" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -8351,13 +8362,13 @@
         <v>9</v>
       </c>
       <c r="B310" t="s">
+        <v>827</v>
+      </c>
+      <c r="C310" t="s">
+        <v>826</v>
+      </c>
+      <c r="D310" t="s">
         <v>828</v>
-      </c>
-      <c r="C310" t="s">
-        <v>827</v>
-      </c>
-      <c r="D310" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -8365,13 +8376,13 @@
         <v>9</v>
       </c>
       <c r="B311" t="s">
+        <v>830</v>
+      </c>
+      <c r="C311" t="s">
+        <v>829</v>
+      </c>
+      <c r="D311" t="s">
         <v>831</v>
-      </c>
-      <c r="C311" t="s">
-        <v>830</v>
-      </c>
-      <c r="D311" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -8379,13 +8390,13 @@
         <v>9</v>
       </c>
       <c r="B312" t="s">
+        <v>833</v>
+      </c>
+      <c r="C312" t="s">
+        <v>832</v>
+      </c>
+      <c r="D312" t="s">
         <v>834</v>
-      </c>
-      <c r="C312" t="s">
-        <v>833</v>
-      </c>
-      <c r="D312" t="s">
-        <v>835</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -8393,13 +8404,13 @@
         <v>9</v>
       </c>
       <c r="B313" t="s">
+        <v>836</v>
+      </c>
+      <c r="C313" t="s">
+        <v>835</v>
+      </c>
+      <c r="D313" t="s">
         <v>837</v>
-      </c>
-      <c r="C313" t="s">
-        <v>836</v>
-      </c>
-      <c r="D313" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -8421,13 +8432,13 @@
         <v>9</v>
       </c>
       <c r="B315" t="s">
+        <v>839</v>
+      </c>
+      <c r="C315" t="s">
+        <v>838</v>
+      </c>
+      <c r="D315" t="s">
         <v>840</v>
-      </c>
-      <c r="C315" t="s">
-        <v>839</v>
-      </c>
-      <c r="D315" t="s">
-        <v>841</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -8455,7 +8466,7 @@
         <v>68</v>
       </c>
       <c r="D317" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -8463,13 +8474,13 @@
         <v>9</v>
       </c>
       <c r="B318" t="s">
+        <v>843</v>
+      </c>
+      <c r="C318" t="s">
+        <v>842</v>
+      </c>
+      <c r="D318" t="s">
         <v>844</v>
-      </c>
-      <c r="C318" t="s">
-        <v>843</v>
-      </c>
-      <c r="D318" t="s">
-        <v>845</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -8477,13 +8488,13 @@
         <v>9</v>
       </c>
       <c r="B319" t="s">
+        <v>846</v>
+      </c>
+      <c r="C319" t="s">
+        <v>845</v>
+      </c>
+      <c r="D319" t="s">
         <v>847</v>
-      </c>
-      <c r="C319" t="s">
-        <v>846</v>
-      </c>
-      <c r="D319" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -8491,13 +8502,13 @@
         <v>9</v>
       </c>
       <c r="B320" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C320" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="D320" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -8505,13 +8516,13 @@
         <v>10</v>
       </c>
       <c r="B321" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C321" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="D321" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -8519,13 +8530,13 @@
         <v>10</v>
       </c>
       <c r="B322" t="s">
+        <v>853</v>
+      </c>
+      <c r="C322" t="s">
+        <v>852</v>
+      </c>
+      <c r="D322" t="s">
         <v>854</v>
-      </c>
-      <c r="C322" t="s">
-        <v>853</v>
-      </c>
-      <c r="D322" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -8533,13 +8544,13 @@
         <v>10</v>
       </c>
       <c r="B323" t="s">
+        <v>856</v>
+      </c>
+      <c r="C323" t="s">
+        <v>855</v>
+      </c>
+      <c r="D323" t="s">
         <v>857</v>
-      </c>
-      <c r="C323" t="s">
-        <v>856</v>
-      </c>
-      <c r="D323" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -8547,13 +8558,13 @@
         <v>10</v>
       </c>
       <c r="B324" t="s">
+        <v>859</v>
+      </c>
+      <c r="C324" t="s">
+        <v>858</v>
+      </c>
+      <c r="D324" t="s">
         <v>860</v>
-      </c>
-      <c r="C324" t="s">
-        <v>859</v>
-      </c>
-      <c r="D324" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -8561,13 +8572,13 @@
         <v>10</v>
       </c>
       <c r="B325" t="s">
+        <v>862</v>
+      </c>
+      <c r="C325" t="s">
+        <v>861</v>
+      </c>
+      <c r="D325" t="s">
         <v>863</v>
-      </c>
-      <c r="C325" t="s">
-        <v>862</v>
-      </c>
-      <c r="D325" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -8575,13 +8586,13 @@
         <v>10</v>
       </c>
       <c r="B326" t="s">
+        <v>865</v>
+      </c>
+      <c r="C326" t="s">
+        <v>864</v>
+      </c>
+      <c r="D326" t="s">
         <v>866</v>
-      </c>
-      <c r="C326" t="s">
-        <v>865</v>
-      </c>
-      <c r="D326" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -8589,13 +8600,13 @@
         <v>10</v>
       </c>
       <c r="B327" t="s">
+        <v>868</v>
+      </c>
+      <c r="C327" t="s">
+        <v>867</v>
+      </c>
+      <c r="D327" t="s">
         <v>869</v>
-      </c>
-      <c r="C327" t="s">
-        <v>868</v>
-      </c>
-      <c r="D327" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -8617,13 +8628,13 @@
         <v>10</v>
       </c>
       <c r="B329" t="s">
+        <v>871</v>
+      </c>
+      <c r="C329" t="s">
+        <v>870</v>
+      </c>
+      <c r="D329" t="s">
         <v>872</v>
-      </c>
-      <c r="C329" t="s">
-        <v>871</v>
-      </c>
-      <c r="D329" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -8631,13 +8642,13 @@
         <v>10</v>
       </c>
       <c r="B330" t="s">
+        <v>874</v>
+      </c>
+      <c r="C330" t="s">
+        <v>873</v>
+      </c>
+      <c r="D330" t="s">
         <v>875</v>
-      </c>
-      <c r="C330" t="s">
-        <v>874</v>
-      </c>
-      <c r="D330" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -8645,13 +8656,13 @@
         <v>10</v>
       </c>
       <c r="B331" t="s">
+        <v>877</v>
+      </c>
+      <c r="C331" t="s">
+        <v>876</v>
+      </c>
+      <c r="D331" t="s">
         <v>878</v>
-      </c>
-      <c r="C331" t="s">
-        <v>877</v>
-      </c>
-      <c r="D331" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -8659,13 +8670,13 @@
         <v>10</v>
       </c>
       <c r="B332" t="s">
+        <v>880</v>
+      </c>
+      <c r="C332" t="s">
+        <v>879</v>
+      </c>
+      <c r="D332" t="s">
         <v>881</v>
-      </c>
-      <c r="C332" t="s">
-        <v>880</v>
-      </c>
-      <c r="D332" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -8687,13 +8698,13 @@
         <v>10</v>
       </c>
       <c r="B334" t="s">
+        <v>883</v>
+      </c>
+      <c r="C334" t="s">
+        <v>882</v>
+      </c>
+      <c r="D334" t="s">
         <v>884</v>
-      </c>
-      <c r="C334" t="s">
-        <v>883</v>
-      </c>
-      <c r="D334" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -8701,10 +8712,10 @@
         <v>10</v>
       </c>
       <c r="B335" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C335" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D335" t="s">
         <v>82</v>
@@ -8715,13 +8726,13 @@
         <v>10</v>
       </c>
       <c r="B336" t="s">
+        <v>886</v>
+      </c>
+      <c r="C336" t="s">
+        <v>885</v>
+      </c>
+      <c r="D336" t="s">
         <v>887</v>
-      </c>
-      <c r="C336" t="s">
-        <v>886</v>
-      </c>
-      <c r="D336" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -8729,13 +8740,13 @@
         <v>10</v>
       </c>
       <c r="B337" t="s">
+        <v>889</v>
+      </c>
+      <c r="C337" t="s">
+        <v>888</v>
+      </c>
+      <c r="D337" t="s">
         <v>890</v>
-      </c>
-      <c r="C337" t="s">
-        <v>889</v>
-      </c>
-      <c r="D337" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -8757,13 +8768,13 @@
         <v>10</v>
       </c>
       <c r="B339" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C339" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D339" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -8771,13 +8782,13 @@
         <v>10</v>
       </c>
       <c r="B340" t="s">
+        <v>894</v>
+      </c>
+      <c r="C340" t="s">
+        <v>893</v>
+      </c>
+      <c r="D340" t="s">
         <v>895</v>
-      </c>
-      <c r="C340" t="s">
-        <v>894</v>
-      </c>
-      <c r="D340" t="s">
-        <v>896</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -8785,13 +8796,13 @@
         <v>10</v>
       </c>
       <c r="B341" t="s">
+        <v>803</v>
+      </c>
+      <c r="C341" t="s">
+        <v>802</v>
+      </c>
+      <c r="D341" t="s">
         <v>804</v>
-      </c>
-      <c r="C341" t="s">
-        <v>803</v>
-      </c>
-      <c r="D341" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -8813,13 +8824,13 @@
         <v>10</v>
       </c>
       <c r="B343" t="s">
+        <v>897</v>
+      </c>
+      <c r="C343" t="s">
+        <v>896</v>
+      </c>
+      <c r="D343" t="s">
         <v>898</v>
-      </c>
-      <c r="C343" t="s">
-        <v>897</v>
-      </c>
-      <c r="D343" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -8827,13 +8838,13 @@
         <v>10</v>
       </c>
       <c r="B344" t="s">
+        <v>900</v>
+      </c>
+      <c r="C344" t="s">
+        <v>899</v>
+      </c>
+      <c r="D344" t="s">
         <v>901</v>
-      </c>
-      <c r="C344" t="s">
-        <v>900</v>
-      </c>
-      <c r="D344" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -8841,13 +8852,13 @@
         <v>10</v>
       </c>
       <c r="B345" t="s">
+        <v>903</v>
+      </c>
+      <c r="C345" t="s">
+        <v>902</v>
+      </c>
+      <c r="D345" t="s">
         <v>904</v>
-      </c>
-      <c r="C345" t="s">
-        <v>903</v>
-      </c>
-      <c r="D345" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -8855,13 +8866,13 @@
         <v>10</v>
       </c>
       <c r="B346" t="s">
+        <v>906</v>
+      </c>
+      <c r="C346" t="s">
+        <v>905</v>
+      </c>
+      <c r="D346" t="s">
         <v>907</v>
-      </c>
-      <c r="C346" t="s">
-        <v>906</v>
-      </c>
-      <c r="D346" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -8869,13 +8880,13 @@
         <v>10</v>
       </c>
       <c r="B347" t="s">
+        <v>909</v>
+      </c>
+      <c r="C347" t="s">
+        <v>908</v>
+      </c>
+      <c r="D347" t="s">
         <v>910</v>
-      </c>
-      <c r="C347" t="s">
-        <v>909</v>
-      </c>
-      <c r="D347" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -8883,13 +8894,13 @@
         <v>10</v>
       </c>
       <c r="B348" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C348" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="D348" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -8897,10 +8908,10 @@
         <v>10</v>
       </c>
       <c r="B349" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C349" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="D349" t="s">
         <v>72</v>
@@ -8911,13 +8922,13 @@
         <v>10</v>
       </c>
       <c r="B350" t="s">
+        <v>915</v>
+      </c>
+      <c r="C350" t="s">
+        <v>914</v>
+      </c>
+      <c r="D350" t="s">
         <v>916</v>
-      </c>
-      <c r="C350" t="s">
-        <v>915</v>
-      </c>
-      <c r="D350" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -8925,13 +8936,13 @@
         <v>10</v>
       </c>
       <c r="B351" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C351" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="D351" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -8939,13 +8950,13 @@
         <v>10</v>
       </c>
       <c r="B352" t="s">
+        <v>920</v>
+      </c>
+      <c r="C352" t="s">
+        <v>919</v>
+      </c>
+      <c r="D352" t="s">
         <v>921</v>
-      </c>
-      <c r="C352" t="s">
-        <v>920</v>
-      </c>
-      <c r="D352" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -8953,13 +8964,13 @@
         <v>10</v>
       </c>
       <c r="B353" t="s">
+        <v>923</v>
+      </c>
+      <c r="C353" t="s">
+        <v>922</v>
+      </c>
+      <c r="D353" t="s">
         <v>924</v>
-      </c>
-      <c r="C353" t="s">
-        <v>923</v>
-      </c>
-      <c r="D353" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -8973,7 +8984,7 @@
         <v>83</v>
       </c>
       <c r="D354" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -8981,13 +8992,13 @@
         <v>10</v>
       </c>
       <c r="B355" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="C355" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="D355" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -8995,13 +9006,13 @@
         <v>11</v>
       </c>
       <c r="B356" t="s">
+        <v>929</v>
+      </c>
+      <c r="C356" t="s">
+        <v>928</v>
+      </c>
+      <c r="D356" t="s">
         <v>930</v>
-      </c>
-      <c r="C356" t="s">
-        <v>929</v>
-      </c>
-      <c r="D356" t="s">
-        <v>931</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -9009,13 +9020,13 @@
         <v>11</v>
       </c>
       <c r="B357" t="s">
+        <v>932</v>
+      </c>
+      <c r="C357" t="s">
+        <v>931</v>
+      </c>
+      <c r="D357" t="s">
         <v>933</v>
-      </c>
-      <c r="C357" t="s">
-        <v>932</v>
-      </c>
-      <c r="D357" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -9023,13 +9034,13 @@
         <v>11</v>
       </c>
       <c r="B358" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="C358" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="D358" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -9037,13 +9048,13 @@
         <v>11</v>
       </c>
       <c r="B359" t="s">
+        <v>937</v>
+      </c>
+      <c r="C359" t="s">
+        <v>936</v>
+      </c>
+      <c r="D359" t="s">
         <v>938</v>
-      </c>
-      <c r="C359" t="s">
-        <v>937</v>
-      </c>
-      <c r="D359" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -9065,13 +9076,13 @@
         <v>11</v>
       </c>
       <c r="B361" t="s">
+        <v>940</v>
+      </c>
+      <c r="C361" t="s">
+        <v>939</v>
+      </c>
+      <c r="D361" t="s">
         <v>941</v>
-      </c>
-      <c r="C361" t="s">
-        <v>940</v>
-      </c>
-      <c r="D361" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -9079,13 +9090,13 @@
         <v>11</v>
       </c>
       <c r="B362" t="s">
+        <v>943</v>
+      </c>
+      <c r="C362" t="s">
+        <v>942</v>
+      </c>
+      <c r="D362" t="s">
         <v>944</v>
-      </c>
-      <c r="C362" t="s">
-        <v>943</v>
-      </c>
-      <c r="D362" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -9093,13 +9104,13 @@
         <v>11</v>
       </c>
       <c r="B363" t="s">
+        <v>871</v>
+      </c>
+      <c r="C363" t="s">
+        <v>870</v>
+      </c>
+      <c r="D363" t="s">
         <v>872</v>
-      </c>
-      <c r="C363" t="s">
-        <v>871</v>
-      </c>
-      <c r="D363" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -9107,13 +9118,13 @@
         <v>11</v>
       </c>
       <c r="B364" t="s">
+        <v>946</v>
+      </c>
+      <c r="C364" t="s">
+        <v>945</v>
+      </c>
+      <c r="D364" t="s">
         <v>947</v>
-      </c>
-      <c r="C364" t="s">
-        <v>946</v>
-      </c>
-      <c r="D364" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -9121,13 +9132,13 @@
         <v>11</v>
       </c>
       <c r="B365" t="s">
+        <v>949</v>
+      </c>
+      <c r="C365" t="s">
+        <v>948</v>
+      </c>
+      <c r="D365" t="s">
         <v>950</v>
-      </c>
-      <c r="C365" t="s">
-        <v>949</v>
-      </c>
-      <c r="D365" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -9135,13 +9146,13 @@
         <v>11</v>
       </c>
       <c r="B366" t="s">
+        <v>952</v>
+      </c>
+      <c r="C366" t="s">
+        <v>951</v>
+      </c>
+      <c r="D366" t="s">
         <v>953</v>
-      </c>
-      <c r="C366" t="s">
-        <v>952</v>
-      </c>
-      <c r="D366" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -9155,7 +9166,7 @@
         <v>85</v>
       </c>
       <c r="D367" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -9177,13 +9188,13 @@
         <v>11</v>
       </c>
       <c r="B369" t="s">
+        <v>956</v>
+      </c>
+      <c r="C369" t="s">
+        <v>955</v>
+      </c>
+      <c r="D369" t="s">
         <v>957</v>
-      </c>
-      <c r="C369" t="s">
-        <v>956</v>
-      </c>
-      <c r="D369" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -9191,13 +9202,13 @@
         <v>11</v>
       </c>
       <c r="B370" t="s">
+        <v>959</v>
+      </c>
+      <c r="C370" t="s">
+        <v>958</v>
+      </c>
+      <c r="D370" t="s">
         <v>960</v>
-      </c>
-      <c r="C370" t="s">
-        <v>959</v>
-      </c>
-      <c r="D370" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -9219,13 +9230,13 @@
         <v>11</v>
       </c>
       <c r="B372" t="s">
+        <v>962</v>
+      </c>
+      <c r="C372" t="s">
+        <v>961</v>
+      </c>
+      <c r="D372" t="s">
         <v>963</v>
-      </c>
-      <c r="C372" t="s">
-        <v>962</v>
-      </c>
-      <c r="D372" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -9233,13 +9244,13 @@
         <v>11</v>
       </c>
       <c r="B373" t="s">
+        <v>965</v>
+      </c>
+      <c r="C373" t="s">
+        <v>964</v>
+      </c>
+      <c r="D373" t="s">
         <v>966</v>
-      </c>
-      <c r="C373" t="s">
-        <v>965</v>
-      </c>
-      <c r="D373" t="s">
-        <v>967</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -9247,13 +9258,13 @@
         <v>11</v>
       </c>
       <c r="B374" t="s">
+        <v>968</v>
+      </c>
+      <c r="C374" t="s">
+        <v>967</v>
+      </c>
+      <c r="D374" t="s">
         <v>969</v>
-      </c>
-      <c r="C374" t="s">
-        <v>968</v>
-      </c>
-      <c r="D374" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -9275,13 +9286,13 @@
         <v>11</v>
       </c>
       <c r="B376" t="s">
+        <v>971</v>
+      </c>
+      <c r="C376" t="s">
+        <v>970</v>
+      </c>
+      <c r="D376" t="s">
         <v>972</v>
-      </c>
-      <c r="C376" t="s">
-        <v>971</v>
-      </c>
-      <c r="D376" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -9289,13 +9300,13 @@
         <v>11</v>
       </c>
       <c r="B377" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C377" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D377" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -9303,13 +9314,13 @@
         <v>11</v>
       </c>
       <c r="B378" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C378" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="D378" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -9317,13 +9328,13 @@
         <v>11</v>
       </c>
       <c r="B379" t="s">
+        <v>976</v>
+      </c>
+      <c r="C379" t="s">
+        <v>975</v>
+      </c>
+      <c r="D379" t="s">
         <v>977</v>
-      </c>
-      <c r="C379" t="s">
-        <v>976</v>
-      </c>
-      <c r="D379" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -9331,13 +9342,13 @@
         <v>11</v>
       </c>
       <c r="B380" t="s">
+        <v>979</v>
+      </c>
+      <c r="C380" t="s">
+        <v>978</v>
+      </c>
+      <c r="D380" t="s">
         <v>980</v>
-      </c>
-      <c r="C380" t="s">
-        <v>979</v>
-      </c>
-      <c r="D380" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -9345,13 +9356,13 @@
         <v>11</v>
       </c>
       <c r="B381" t="s">
+        <v>982</v>
+      </c>
+      <c r="C381" t="s">
+        <v>981</v>
+      </c>
+      <c r="D381" t="s">
         <v>983</v>
-      </c>
-      <c r="C381" t="s">
-        <v>982</v>
-      </c>
-      <c r="D381" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -9359,13 +9370,13 @@
         <v>11</v>
       </c>
       <c r="B382" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C382" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="D382" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -9373,13 +9384,13 @@
         <v>11</v>
       </c>
       <c r="B383" t="s">
+        <v>987</v>
+      </c>
+      <c r="C383" t="s">
+        <v>986</v>
+      </c>
+      <c r="D383" t="s">
         <v>988</v>
-      </c>
-      <c r="C383" t="s">
-        <v>987</v>
-      </c>
-      <c r="D383" t="s">
-        <v>989</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -9387,13 +9398,13 @@
         <v>11</v>
       </c>
       <c r="B384" t="s">
+        <v>990</v>
+      </c>
+      <c r="C384" t="s">
+        <v>989</v>
+      </c>
+      <c r="D384" t="s">
         <v>991</v>
-      </c>
-      <c r="C384" t="s">
-        <v>990</v>
-      </c>
-      <c r="D384" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -9401,13 +9412,13 @@
         <v>11</v>
       </c>
       <c r="B385" t="s">
+        <v>993</v>
+      </c>
+      <c r="C385" t="s">
+        <v>992</v>
+      </c>
+      <c r="D385" t="s">
         <v>994</v>
-      </c>
-      <c r="C385" t="s">
-        <v>993</v>
-      </c>
-      <c r="D385" t="s">
-        <v>995</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -9415,13 +9426,13 @@
         <v>11</v>
       </c>
       <c r="B386" t="s">
+        <v>996</v>
+      </c>
+      <c r="C386" t="s">
+        <v>995</v>
+      </c>
+      <c r="D386" t="s">
         <v>997</v>
-      </c>
-      <c r="C386" t="s">
-        <v>996</v>
-      </c>
-      <c r="D386" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -9443,13 +9454,13 @@
         <v>11</v>
       </c>
       <c r="B388" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="C388" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="D388" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -9457,13 +9468,13 @@
         <v>11</v>
       </c>
       <c r="B389" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C389" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D389" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -9471,13 +9482,13 @@
         <v>11</v>
       </c>
       <c r="B390" t="s">
+        <v>999</v>
+      </c>
+      <c r="C390" t="s">
+        <v>998</v>
+      </c>
+      <c r="D390" t="s">
         <v>1000</v>
-      </c>
-      <c r="C390" t="s">
-        <v>999</v>
-      </c>
-      <c r="D390" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -9485,13 +9496,13 @@
         <v>11</v>
       </c>
       <c r="B391" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C391" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D391" t="s">
         <v>1003</v>
-      </c>
-      <c r="C391" t="s">
-        <v>1002</v>
-      </c>
-      <c r="D391" t="s">
-        <v>1004</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -9499,13 +9510,13 @@
         <v>11</v>
       </c>
       <c r="B392" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C392" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D392" t="s">
         <v>1006</v>
-      </c>
-      <c r="C392" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D392" t="s">
-        <v>1007</v>
       </c>
     </row>
   </sheetData>

--- a/N5.xlsx
+++ b/N5.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sunsh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DDD6713-361A-4430-A021-3F2CF8BEBA93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -211,9 +210,6 @@
     <t>母親</t>
   </si>
   <si>
-    <t>子犬</t>
-  </si>
-  <si>
     <t>こいぬ</t>
   </si>
   <si>
@@ -3080,14 +3076,18 @@
   </si>
   <si>
     <t>之後、等一下、剩下</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>小犬</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3249,6 +3249,8 @@
     <font>
       <sz val="11"/>
       <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -3705,13 +3707,13 @@
     <cellStyle name="60% - 輔色5" xfId="36" builtinId="48" customBuiltin="1"/>
     <cellStyle name="60% - 輔色6" xfId="40" builtinId="52" customBuiltin="1"/>
     <cellStyle name="一般" xfId="0" builtinId="0"/>
-    <cellStyle name="一般 2" xfId="41" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="一般 2" xfId="41"/>
     <cellStyle name="中等" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="合計" xfId="16" builtinId="25" customBuiltin="1"/>
     <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="計算方式" xfId="11" builtinId="22" customBuiltin="1"/>
     <cellStyle name="連結的儲存格" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="備註 2" xfId="42" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="備註 2" xfId="42"/>
     <cellStyle name="說明文字" xfId="15" builtinId="53" customBuiltin="1"/>
     <cellStyle name="輔色1" xfId="17" builtinId="29" customBuiltin="1"/>
     <cellStyle name="輔色2" xfId="21" builtinId="33" customBuiltin="1"/>
@@ -4027,109 +4029,109 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D392"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5">
+    <row r="1" spans="1:4" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1008</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" t="s">
         <v>88</v>
       </c>
-      <c r="C2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" t="s">
         <v>91</v>
       </c>
-      <c r="C3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" t="s">
         <v>96</v>
       </c>
-      <c r="C5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" t="s">
         <v>99</v>
       </c>
-      <c r="C6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" t="s">
         <v>102</v>
       </c>
-      <c r="C7" t="s">
-        <v>101</v>
-      </c>
-      <c r="D7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -4143,105 +4145,105 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" t="s">
         <v>105</v>
       </c>
-      <c r="C9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1</v>
       </c>
       <c r="B12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" t="s">
         <v>112</v>
       </c>
-      <c r="C12" t="s">
-        <v>111</v>
-      </c>
-      <c r="D12" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1</v>
       </c>
       <c r="B13" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" t="s">
         <v>115</v>
       </c>
-      <c r="C13" t="s">
-        <v>114</v>
-      </c>
-      <c r="D13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1</v>
       </c>
       <c r="B14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" t="s">
         <v>118</v>
       </c>
-      <c r="C14" t="s">
-        <v>117</v>
-      </c>
-      <c r="D14" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1</v>
       </c>
       <c r="B15" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" t="s">
+        <v>119</v>
+      </c>
+      <c r="D15" t="s">
         <v>121</v>
       </c>
-      <c r="C15" t="s">
-        <v>120</v>
-      </c>
-      <c r="D15" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1</v>
       </c>
@@ -4255,91 +4257,91 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D17" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1</v>
       </c>
       <c r="B18" t="s">
+        <v>125</v>
+      </c>
+      <c r="C18" t="s">
+        <v>124</v>
+      </c>
+      <c r="D18" t="s">
         <v>126</v>
       </c>
-      <c r="C18" t="s">
-        <v>125</v>
-      </c>
-      <c r="D18" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1</v>
       </c>
       <c r="B19" t="s">
+        <v>128</v>
+      </c>
+      <c r="C19" t="s">
+        <v>127</v>
+      </c>
+      <c r="D19" t="s">
         <v>129</v>
       </c>
-      <c r="C19" t="s">
-        <v>128</v>
-      </c>
-      <c r="D19" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1</v>
       </c>
       <c r="B20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" t="s">
+        <v>130</v>
+      </c>
+      <c r="D20" t="s">
         <v>132</v>
       </c>
-      <c r="C20" t="s">
-        <v>131</v>
-      </c>
-      <c r="D20" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1</v>
       </c>
       <c r="B21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C21" t="s">
+        <v>133</v>
+      </c>
+      <c r="D21" t="s">
         <v>135</v>
       </c>
-      <c r="C21" t="s">
-        <v>134</v>
-      </c>
-      <c r="D21" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D22" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1</v>
       </c>
@@ -4353,63 +4355,63 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C24" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D24" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1</v>
       </c>
       <c r="B25" t="s">
+        <v>141</v>
+      </c>
+      <c r="C25" t="s">
+        <v>140</v>
+      </c>
+      <c r="D25" t="s">
         <v>142</v>
       </c>
-      <c r="C25" t="s">
-        <v>141</v>
-      </c>
-      <c r="D25" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C26" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D26" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D27" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1</v>
       </c>
@@ -4423,441 +4425,441 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C29" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D29" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1</v>
       </c>
       <c r="B30" t="s">
+        <v>149</v>
+      </c>
+      <c r="C30" t="s">
+        <v>148</v>
+      </c>
+      <c r="D30" t="s">
         <v>150</v>
       </c>
-      <c r="C30" t="s">
-        <v>149</v>
-      </c>
-      <c r="D30" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1</v>
       </c>
       <c r="B31" t="s">
+        <v>152</v>
+      </c>
+      <c r="C31" t="s">
+        <v>151</v>
+      </c>
+      <c r="D31" t="s">
         <v>153</v>
       </c>
-      <c r="C31" t="s">
-        <v>152</v>
-      </c>
-      <c r="D31" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D32" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1</v>
       </c>
       <c r="B33" t="s">
+        <v>157</v>
+      </c>
+      <c r="C33" t="s">
+        <v>156</v>
+      </c>
+      <c r="D33" t="s">
         <v>158</v>
       </c>
-      <c r="C33" t="s">
-        <v>157</v>
-      </c>
-      <c r="D33" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1</v>
       </c>
       <c r="B34" t="s">
+        <v>160</v>
+      </c>
+      <c r="C34" t="s">
+        <v>159</v>
+      </c>
+      <c r="D34" t="s">
         <v>161</v>
       </c>
-      <c r="C34" t="s">
-        <v>160</v>
-      </c>
-      <c r="D34" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>2</v>
       </c>
       <c r="B35" t="s">
+        <v>163</v>
+      </c>
+      <c r="C35" t="s">
+        <v>162</v>
+      </c>
+      <c r="D35" t="s">
         <v>164</v>
       </c>
-      <c r="C35" t="s">
-        <v>163</v>
-      </c>
-      <c r="D35" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>2</v>
       </c>
       <c r="B36" t="s">
+        <v>166</v>
+      </c>
+      <c r="C36" t="s">
+        <v>165</v>
+      </c>
+      <c r="D36" t="s">
         <v>167</v>
       </c>
-      <c r="C36" t="s">
-        <v>166</v>
-      </c>
-      <c r="D36" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>2</v>
       </c>
       <c r="B37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D37" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>2</v>
       </c>
       <c r="B38" t="s">
+        <v>169</v>
+      </c>
+      <c r="C38" t="s">
+        <v>168</v>
+      </c>
+      <c r="D38" t="s">
         <v>170</v>
       </c>
-      <c r="C38" t="s">
-        <v>169</v>
-      </c>
-      <c r="D38" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>2</v>
       </c>
       <c r="B39" t="s">
+        <v>172</v>
+      </c>
+      <c r="C39" t="s">
+        <v>171</v>
+      </c>
+      <c r="D39" t="s">
         <v>173</v>
       </c>
-      <c r="C39" t="s">
-        <v>172</v>
-      </c>
-      <c r="D39" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>2</v>
       </c>
       <c r="B40" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C40" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D40" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>2</v>
       </c>
       <c r="B41" t="s">
+        <v>177</v>
+      </c>
+      <c r="C41" t="s">
+        <v>176</v>
+      </c>
+      <c r="D41" t="s">
         <v>178</v>
       </c>
-      <c r="C41" t="s">
-        <v>177</v>
-      </c>
-      <c r="D41" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>2</v>
       </c>
       <c r="B42" t="s">
+        <v>180</v>
+      </c>
+      <c r="C42" t="s">
+        <v>179</v>
+      </c>
+      <c r="D42" t="s">
         <v>181</v>
       </c>
-      <c r="C42" t="s">
-        <v>180</v>
-      </c>
-      <c r="D42" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>2</v>
       </c>
       <c r="B43" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C43" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D43" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>2</v>
       </c>
       <c r="B44" t="s">
+        <v>185</v>
+      </c>
+      <c r="C44" t="s">
+        <v>184</v>
+      </c>
+      <c r="D44" t="s">
         <v>186</v>
       </c>
-      <c r="C44" t="s">
-        <v>185</v>
-      </c>
-      <c r="D44" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>2</v>
       </c>
       <c r="B45" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" t="s">
+        <v>187</v>
+      </c>
+      <c r="D45" t="s">
         <v>189</v>
       </c>
-      <c r="C45" t="s">
-        <v>188</v>
-      </c>
-      <c r="D45" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>2</v>
       </c>
       <c r="B46" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C46" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D46" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>2</v>
       </c>
       <c r="B47" t="s">
+        <v>193</v>
+      </c>
+      <c r="C47" t="s">
+        <v>192</v>
+      </c>
+      <c r="D47" t="s">
         <v>194</v>
       </c>
-      <c r="C47" t="s">
-        <v>193</v>
-      </c>
-      <c r="D47" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>2</v>
       </c>
       <c r="B48" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C48" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D48" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>2</v>
       </c>
       <c r="B49" t="s">
+        <v>198</v>
+      </c>
+      <c r="C49" t="s">
+        <v>197</v>
+      </c>
+      <c r="D49" t="s">
         <v>199</v>
       </c>
-      <c r="C49" t="s">
-        <v>198</v>
-      </c>
-      <c r="D49" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>2</v>
       </c>
       <c r="B50" t="s">
+        <v>201</v>
+      </c>
+      <c r="C50" t="s">
+        <v>200</v>
+      </c>
+      <c r="D50" t="s">
         <v>202</v>
       </c>
-      <c r="C50" t="s">
-        <v>201</v>
-      </c>
-      <c r="D50" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>2</v>
       </c>
       <c r="B51" t="s">
+        <v>204</v>
+      </c>
+      <c r="C51" t="s">
+        <v>203</v>
+      </c>
+      <c r="D51" t="s">
         <v>205</v>
       </c>
-      <c r="C51" t="s">
-        <v>204</v>
-      </c>
-      <c r="D51" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>2</v>
       </c>
       <c r="B52" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C52" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D52" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>2</v>
       </c>
       <c r="B53" t="s">
+        <v>209</v>
+      </c>
+      <c r="C53" t="s">
+        <v>208</v>
+      </c>
+      <c r="D53" t="s">
         <v>210</v>
       </c>
-      <c r="C53" t="s">
-        <v>209</v>
-      </c>
-      <c r="D53" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>2</v>
       </c>
       <c r="B54" t="s">
+        <v>212</v>
+      </c>
+      <c r="C54" t="s">
+        <v>211</v>
+      </c>
+      <c r="D54" t="s">
         <v>213</v>
       </c>
-      <c r="C54" t="s">
-        <v>212</v>
-      </c>
-      <c r="D54" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>2</v>
       </c>
       <c r="B55" t="s">
+        <v>215</v>
+      </c>
+      <c r="C55" t="s">
+        <v>214</v>
+      </c>
+      <c r="D55" t="s">
         <v>216</v>
       </c>
-      <c r="C55" t="s">
-        <v>215</v>
-      </c>
-      <c r="D55" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>2</v>
       </c>
       <c r="B56" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C56" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D56" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>2</v>
       </c>
       <c r="B57" t="s">
+        <v>220</v>
+      </c>
+      <c r="C57" t="s">
+        <v>219</v>
+      </c>
+      <c r="D57" t="s">
         <v>221</v>
       </c>
-      <c r="C57" t="s">
-        <v>220</v>
-      </c>
-      <c r="D57" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>2</v>
       </c>
       <c r="B58" t="s">
+        <v>223</v>
+      </c>
+      <c r="C58" t="s">
+        <v>222</v>
+      </c>
+      <c r="D58" t="s">
         <v>224</v>
       </c>
-      <c r="C58" t="s">
-        <v>223</v>
-      </c>
-      <c r="D58" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>2</v>
       </c>
       <c r="B59" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C59" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D59" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>2</v>
       </c>
@@ -4871,371 +4873,371 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>2</v>
       </c>
       <c r="B61" t="s">
+        <v>228</v>
+      </c>
+      <c r="C61" t="s">
+        <v>227</v>
+      </c>
+      <c r="D61" t="s">
         <v>229</v>
       </c>
-      <c r="C61" t="s">
-        <v>228</v>
-      </c>
-      <c r="D61" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>2</v>
       </c>
       <c r="B62" t="s">
+        <v>231</v>
+      </c>
+      <c r="C62" t="s">
+        <v>230</v>
+      </c>
+      <c r="D62" t="s">
         <v>232</v>
       </c>
-      <c r="C62" t="s">
-        <v>231</v>
-      </c>
-      <c r="D62" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>2</v>
       </c>
       <c r="B63" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C63" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D63" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>2</v>
       </c>
       <c r="B64" t="s">
+        <v>236</v>
+      </c>
+      <c r="C64" t="s">
+        <v>235</v>
+      </c>
+      <c r="D64" t="s">
         <v>237</v>
       </c>
-      <c r="C64" t="s">
-        <v>236</v>
-      </c>
-      <c r="D64" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>2</v>
       </c>
       <c r="B65" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C65" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D65" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>2</v>
       </c>
       <c r="B66" t="s">
+        <v>241</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D66" t="s">
         <v>242</v>
       </c>
-      <c r="C66" t="s">
-        <v>1011</v>
-      </c>
-      <c r="D66" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>2</v>
       </c>
       <c r="B67" t="s">
+        <v>244</v>
+      </c>
+      <c r="C67" t="s">
+        <v>243</v>
+      </c>
+      <c r="D67" t="s">
         <v>245</v>
       </c>
-      <c r="C67" t="s">
-        <v>244</v>
-      </c>
-      <c r="D67" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>2</v>
       </c>
       <c r="B68" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C68" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D68" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>2</v>
       </c>
       <c r="B69" t="s">
+        <v>249</v>
+      </c>
+      <c r="C69" t="s">
+        <v>248</v>
+      </c>
+      <c r="D69" t="s">
         <v>250</v>
       </c>
-      <c r="C69" t="s">
-        <v>249</v>
-      </c>
-      <c r="D69" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>2</v>
       </c>
       <c r="B70" t="s">
+        <v>252</v>
+      </c>
+      <c r="C70" t="s">
+        <v>251</v>
+      </c>
+      <c r="D70" t="s">
         <v>253</v>
       </c>
-      <c r="C70" t="s">
-        <v>252</v>
-      </c>
-      <c r="D70" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>2</v>
       </c>
       <c r="B71" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C71" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D71" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>3</v>
       </c>
       <c r="B72" t="s">
+        <v>257</v>
+      </c>
+      <c r="C72" t="s">
+        <v>256</v>
+      </c>
+      <c r="D72" t="s">
         <v>258</v>
       </c>
-      <c r="C72" t="s">
-        <v>257</v>
-      </c>
-      <c r="D72" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>3</v>
       </c>
       <c r="B73" t="s">
+        <v>260</v>
+      </c>
+      <c r="C73" t="s">
+        <v>259</v>
+      </c>
+      <c r="D73" t="s">
         <v>261</v>
       </c>
-      <c r="C73" t="s">
-        <v>260</v>
-      </c>
-      <c r="D73" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>3</v>
       </c>
       <c r="B74" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>3</v>
       </c>
       <c r="B75" t="s">
+        <v>265</v>
+      </c>
+      <c r="C75" t="s">
+        <v>264</v>
+      </c>
+      <c r="D75" t="s">
         <v>266</v>
       </c>
-      <c r="C75" t="s">
-        <v>265</v>
-      </c>
-      <c r="D75" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>3</v>
       </c>
       <c r="B76" t="s">
+        <v>268</v>
+      </c>
+      <c r="C76" t="s">
+        <v>267</v>
+      </c>
+      <c r="D76" t="s">
         <v>269</v>
       </c>
-      <c r="C76" t="s">
-        <v>268</v>
-      </c>
-      <c r="D76" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>3</v>
       </c>
       <c r="B77" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C77" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D77" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>3</v>
       </c>
       <c r="B78" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C78" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D78" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>3</v>
       </c>
       <c r="B79" t="s">
+        <v>275</v>
+      </c>
+      <c r="C79" t="s">
+        <v>274</v>
+      </c>
+      <c r="D79" t="s">
         <v>276</v>
       </c>
-      <c r="C79" t="s">
-        <v>275</v>
-      </c>
-      <c r="D79" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>3</v>
       </c>
       <c r="B80" t="s">
+        <v>278</v>
+      </c>
+      <c r="C80" t="s">
+        <v>277</v>
+      </c>
+      <c r="D80" t="s">
         <v>279</v>
       </c>
-      <c r="C80" t="s">
-        <v>278</v>
-      </c>
-      <c r="D80" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>3</v>
       </c>
       <c r="B81" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C81" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D81" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>3</v>
       </c>
       <c r="B82" t="s">
+        <v>283</v>
+      </c>
+      <c r="C82" t="s">
+        <v>282</v>
+      </c>
+      <c r="D82" t="s">
         <v>284</v>
       </c>
-      <c r="C82" t="s">
-        <v>283</v>
-      </c>
-      <c r="D82" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>3</v>
       </c>
       <c r="B83" t="s">
+        <v>286</v>
+      </c>
+      <c r="C83" t="s">
+        <v>285</v>
+      </c>
+      <c r="D83" t="s">
         <v>287</v>
       </c>
-      <c r="C83" t="s">
-        <v>286</v>
-      </c>
-      <c r="D83" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>3</v>
       </c>
       <c r="B84" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C84" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D84" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>3</v>
       </c>
       <c r="B85" t="s">
+        <v>291</v>
+      </c>
+      <c r="C85" t="s">
+        <v>290</v>
+      </c>
+      <c r="D85" t="s">
         <v>292</v>
       </c>
-      <c r="C85" t="s">
-        <v>291</v>
-      </c>
-      <c r="D85" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>3</v>
       </c>
       <c r="B86" t="s">
+        <v>294</v>
+      </c>
+      <c r="C86" t="s">
+        <v>293</v>
+      </c>
+      <c r="D86" t="s">
         <v>295</v>
       </c>
-      <c r="C86" t="s">
-        <v>294</v>
-      </c>
-      <c r="D86" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>3</v>
       </c>
@@ -5249,231 +5251,231 @@
         <v>40</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>3</v>
       </c>
       <c r="B88" t="s">
+        <v>297</v>
+      </c>
+      <c r="C88" t="s">
+        <v>296</v>
+      </c>
+      <c r="D88" t="s">
         <v>298</v>
       </c>
-      <c r="C88" t="s">
-        <v>297</v>
-      </c>
-      <c r="D88" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>3</v>
       </c>
       <c r="B89" t="s">
+        <v>300</v>
+      </c>
+      <c r="C89" t="s">
+        <v>299</v>
+      </c>
+      <c r="D89" t="s">
         <v>301</v>
       </c>
-      <c r="C89" t="s">
-        <v>300</v>
-      </c>
-      <c r="D89" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>3</v>
       </c>
       <c r="B90" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C90" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D90" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>3</v>
       </c>
       <c r="B91" t="s">
+        <v>305</v>
+      </c>
+      <c r="C91" t="s">
+        <v>304</v>
+      </c>
+      <c r="D91" t="s">
         <v>306</v>
       </c>
-      <c r="C91" t="s">
-        <v>305</v>
-      </c>
-      <c r="D91" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>3</v>
       </c>
       <c r="B92" t="s">
+        <v>308</v>
+      </c>
+      <c r="C92" t="s">
+        <v>307</v>
+      </c>
+      <c r="D92" t="s">
         <v>309</v>
       </c>
-      <c r="C92" t="s">
-        <v>308</v>
-      </c>
-      <c r="D92" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>3</v>
       </c>
       <c r="B93" t="s">
+        <v>311</v>
+      </c>
+      <c r="C93" t="s">
+        <v>310</v>
+      </c>
+      <c r="D93" t="s">
         <v>312</v>
       </c>
-      <c r="C93" t="s">
-        <v>311</v>
-      </c>
-      <c r="D93" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>3</v>
       </c>
       <c r="B94" t="s">
+        <v>314</v>
+      </c>
+      <c r="C94" t="s">
+        <v>313</v>
+      </c>
+      <c r="D94" t="s">
         <v>315</v>
       </c>
-      <c r="C94" t="s">
-        <v>314</v>
-      </c>
-      <c r="D94" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>3</v>
       </c>
       <c r="B95" t="s">
+        <v>316</v>
+      </c>
+      <c r="C95" t="s">
+        <v>240</v>
+      </c>
+      <c r="D95" t="s">
         <v>317</v>
       </c>
-      <c r="C95" t="s">
-        <v>241</v>
-      </c>
-      <c r="D95" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>3</v>
       </c>
       <c r="B96" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C96" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="D96" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>3</v>
       </c>
       <c r="B97" t="s">
+        <v>319</v>
+      </c>
+      <c r="C97" t="s">
+        <v>318</v>
+      </c>
+      <c r="D97" t="s">
         <v>320</v>
       </c>
-      <c r="C97" t="s">
-        <v>319</v>
-      </c>
-      <c r="D97" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>3</v>
       </c>
       <c r="B98" t="s">
+        <v>322</v>
+      </c>
+      <c r="C98" t="s">
+        <v>321</v>
+      </c>
+      <c r="D98" t="s">
         <v>323</v>
       </c>
-      <c r="C98" t="s">
-        <v>322</v>
-      </c>
-      <c r="D98" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>3</v>
       </c>
       <c r="B99" t="s">
+        <v>325</v>
+      </c>
+      <c r="C99" t="s">
+        <v>324</v>
+      </c>
+      <c r="D99" t="s">
         <v>326</v>
       </c>
-      <c r="C99" t="s">
-        <v>325</v>
-      </c>
-      <c r="D99" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4">
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>3</v>
       </c>
       <c r="B100" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C100" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D100" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>3</v>
       </c>
       <c r="B101" t="s">
+        <v>330</v>
+      </c>
+      <c r="C101" t="s">
+        <v>329</v>
+      </c>
+      <c r="D101" t="s">
         <v>331</v>
       </c>
-      <c r="C101" t="s">
-        <v>330</v>
-      </c>
-      <c r="D101" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>3</v>
       </c>
       <c r="B102" t="s">
+        <v>333</v>
+      </c>
+      <c r="C102" t="s">
+        <v>332</v>
+      </c>
+      <c r="D102" t="s">
         <v>334</v>
       </c>
-      <c r="C102" t="s">
-        <v>333</v>
-      </c>
-      <c r="D102" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>3</v>
       </c>
       <c r="B103" t="s">
+        <v>336</v>
+      </c>
+      <c r="C103" t="s">
+        <v>335</v>
+      </c>
+      <c r="D103" t="s">
         <v>337</v>
       </c>
-      <c r="C103" t="s">
-        <v>336</v>
-      </c>
-      <c r="D103" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4">
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>3</v>
       </c>
@@ -5487,203 +5489,203 @@
         <v>30</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>3</v>
       </c>
       <c r="B105" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C105" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D105" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>3</v>
       </c>
       <c r="B106" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C106" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D106" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>3</v>
       </c>
       <c r="B107" t="s">
+        <v>343</v>
+      </c>
+      <c r="C107" t="s">
+        <v>342</v>
+      </c>
+      <c r="D107" t="s">
         <v>344</v>
       </c>
-      <c r="C107" t="s">
-        <v>343</v>
-      </c>
-      <c r="D107" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4">
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>3</v>
       </c>
       <c r="B108" t="s">
+        <v>346</v>
+      </c>
+      <c r="C108" t="s">
+        <v>345</v>
+      </c>
+      <c r="D108" t="s">
         <v>347</v>
       </c>
-      <c r="C108" t="s">
-        <v>346</v>
-      </c>
-      <c r="D108" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>3</v>
       </c>
       <c r="B109" t="s">
+        <v>349</v>
+      </c>
+      <c r="C109" t="s">
+        <v>348</v>
+      </c>
+      <c r="D109" t="s">
         <v>350</v>
       </c>
-      <c r="C109" t="s">
-        <v>349</v>
-      </c>
-      <c r="D109" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4">
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>3</v>
       </c>
       <c r="B110" t="s">
+        <v>352</v>
+      </c>
+      <c r="C110" t="s">
+        <v>351</v>
+      </c>
+      <c r="D110" t="s">
         <v>353</v>
       </c>
-      <c r="C110" t="s">
-        <v>352</v>
-      </c>
-      <c r="D110" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4">
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>4</v>
       </c>
       <c r="B111" t="s">
+        <v>355</v>
+      </c>
+      <c r="C111" t="s">
+        <v>354</v>
+      </c>
+      <c r="D111" t="s">
         <v>356</v>
       </c>
-      <c r="C111" t="s">
-        <v>355</v>
-      </c>
-      <c r="D111" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4">
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>4</v>
       </c>
       <c r="B112" t="s">
+        <v>358</v>
+      </c>
+      <c r="C112" t="s">
+        <v>357</v>
+      </c>
+      <c r="D112" t="s">
         <v>359</v>
       </c>
-      <c r="C112" t="s">
-        <v>358</v>
-      </c>
-      <c r="D112" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4">
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>4</v>
       </c>
       <c r="B113" t="s">
+        <v>361</v>
+      </c>
+      <c r="C113" t="s">
+        <v>360</v>
+      </c>
+      <c r="D113" t="s">
         <v>362</v>
       </c>
-      <c r="C113" t="s">
-        <v>361</v>
-      </c>
-      <c r="D113" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4">
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>4</v>
       </c>
       <c r="B114" t="s">
+        <v>364</v>
+      </c>
+      <c r="C114" t="s">
+        <v>363</v>
+      </c>
+      <c r="D114" t="s">
         <v>365</v>
       </c>
-      <c r="C114" t="s">
-        <v>364</v>
-      </c>
-      <c r="D114" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4">
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>4</v>
       </c>
       <c r="B115" t="s">
+        <v>367</v>
+      </c>
+      <c r="C115" t="s">
+        <v>366</v>
+      </c>
+      <c r="D115" t="s">
         <v>368</v>
       </c>
-      <c r="C115" t="s">
-        <v>367</v>
-      </c>
-      <c r="D115" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4">
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>4</v>
       </c>
       <c r="B116" t="s">
+        <v>370</v>
+      </c>
+      <c r="C116" t="s">
+        <v>369</v>
+      </c>
+      <c r="D116" t="s">
         <v>371</v>
       </c>
-      <c r="C116" t="s">
-        <v>370</v>
-      </c>
-      <c r="D116" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4">
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>4</v>
       </c>
       <c r="B117" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C117" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D117" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>4</v>
       </c>
       <c r="B118" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C118" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D118" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>4</v>
       </c>
@@ -5697,259 +5699,259 @@
         <v>44</v>
       </c>
     </row>
-    <row r="120" spans="1:4">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>4</v>
       </c>
       <c r="B120" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C120" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D120" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>4</v>
       </c>
       <c r="B121" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C121" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D121" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>4</v>
       </c>
       <c r="B122" t="s">
+        <v>381</v>
+      </c>
+      <c r="C122" t="s">
+        <v>380</v>
+      </c>
+      <c r="D122" t="s">
         <v>382</v>
       </c>
-      <c r="C122" t="s">
-        <v>381</v>
-      </c>
-      <c r="D122" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4">
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>4</v>
       </c>
       <c r="B123" t="s">
+        <v>384</v>
+      </c>
+      <c r="C123" t="s">
+        <v>383</v>
+      </c>
+      <c r="D123" t="s">
         <v>385</v>
       </c>
-      <c r="C123" t="s">
-        <v>384</v>
-      </c>
-      <c r="D123" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4">
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>4</v>
       </c>
       <c r="B124" t="s">
+        <v>387</v>
+      </c>
+      <c r="C124" t="s">
+        <v>386</v>
+      </c>
+      <c r="D124" t="s">
         <v>388</v>
       </c>
-      <c r="C124" t="s">
-        <v>387</v>
-      </c>
-      <c r="D124" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4">
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>4</v>
       </c>
       <c r="B125" t="s">
+        <v>390</v>
+      </c>
+      <c r="C125" t="s">
+        <v>389</v>
+      </c>
+      <c r="D125" t="s">
         <v>391</v>
       </c>
-      <c r="C125" t="s">
-        <v>390</v>
-      </c>
-      <c r="D125" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4">
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>4</v>
       </c>
       <c r="B126" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C126" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D126" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>4</v>
       </c>
       <c r="B127" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C127" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D127" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>4</v>
       </c>
       <c r="B128" t="s">
+        <v>397</v>
+      </c>
+      <c r="C128" t="s">
+        <v>396</v>
+      </c>
+      <c r="D128" t="s">
         <v>398</v>
       </c>
-      <c r="C128" t="s">
-        <v>397</v>
-      </c>
-      <c r="D128" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4">
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>4</v>
       </c>
       <c r="B129" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C129" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D129" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>4</v>
       </c>
       <c r="B130" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C130" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D130" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>4</v>
       </c>
       <c r="B131" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C131" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D131" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>4</v>
       </c>
       <c r="B132" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C132" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D132" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>4</v>
       </c>
       <c r="B133" t="s">
+        <v>407</v>
+      </c>
+      <c r="C133" t="s">
+        <v>406</v>
+      </c>
+      <c r="D133" t="s">
         <v>408</v>
       </c>
-      <c r="C133" t="s">
-        <v>407</v>
-      </c>
-      <c r="D133" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4">
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>4</v>
       </c>
       <c r="B134" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C134" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D134" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>4</v>
       </c>
       <c r="B135" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C135" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D135" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>4</v>
       </c>
       <c r="B136" t="s">
+        <v>414</v>
+      </c>
+      <c r="C136" t="s">
+        <v>413</v>
+      </c>
+      <c r="D136" t="s">
         <v>415</v>
       </c>
-      <c r="C136" t="s">
-        <v>414</v>
-      </c>
-      <c r="D136" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4">
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>4</v>
       </c>
       <c r="B137" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C137" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D137" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>4</v>
       </c>
@@ -5960,94 +5962,94 @@
         <v>47</v>
       </c>
       <c r="D138" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>4</v>
       </c>
       <c r="B139" t="s">
+        <v>420</v>
+      </c>
+      <c r="C139" t="s">
+        <v>419</v>
+      </c>
+      <c r="D139" t="s">
         <v>421</v>
       </c>
-      <c r="C139" t="s">
-        <v>420</v>
-      </c>
-      <c r="D139" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4">
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>4</v>
       </c>
       <c r="B140" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C140" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D140" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>4</v>
       </c>
       <c r="B141" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C141" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D141" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>4</v>
       </c>
       <c r="B142" t="s">
+        <v>427</v>
+      </c>
+      <c r="C142" t="s">
+        <v>426</v>
+      </c>
+      <c r="D142" t="s">
         <v>428</v>
       </c>
-      <c r="C142" t="s">
-        <v>427</v>
-      </c>
-      <c r="D142" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4">
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>4</v>
       </c>
       <c r="B143" t="s">
+        <v>430</v>
+      </c>
+      <c r="C143" t="s">
+        <v>429</v>
+      </c>
+      <c r="D143" t="s">
         <v>431</v>
       </c>
-      <c r="C143" t="s">
-        <v>430</v>
-      </c>
-      <c r="D143" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4">
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>4</v>
       </c>
       <c r="B144" t="s">
+        <v>433</v>
+      </c>
+      <c r="C144" t="s">
+        <v>432</v>
+      </c>
+      <c r="D144" t="s">
         <v>434</v>
       </c>
-      <c r="C144" t="s">
-        <v>433</v>
-      </c>
-      <c r="D144" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4">
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>4</v>
       </c>
@@ -6061,175 +6063,175 @@
         <v>4</v>
       </c>
     </row>
-    <row r="146" spans="1:4">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>4</v>
       </c>
       <c r="B146" t="s">
+        <v>436</v>
+      </c>
+      <c r="C146" t="s">
+        <v>435</v>
+      </c>
+      <c r="D146" t="s">
         <v>437</v>
       </c>
-      <c r="C146" t="s">
-        <v>436</v>
-      </c>
-      <c r="D146" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4">
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>4</v>
       </c>
       <c r="B147" t="s">
+        <v>439</v>
+      </c>
+      <c r="C147" t="s">
+        <v>438</v>
+      </c>
+      <c r="D147" t="s">
         <v>440</v>
       </c>
-      <c r="C147" t="s">
-        <v>439</v>
-      </c>
-      <c r="D147" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4">
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>5</v>
       </c>
       <c r="B148" t="s">
+        <v>442</v>
+      </c>
+      <c r="C148" t="s">
+        <v>441</v>
+      </c>
+      <c r="D148" t="s">
         <v>443</v>
       </c>
-      <c r="C148" t="s">
-        <v>442</v>
-      </c>
-      <c r="D148" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4">
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>5</v>
       </c>
       <c r="B149" t="s">
+        <v>445</v>
+      </c>
+      <c r="C149" t="s">
+        <v>444</v>
+      </c>
+      <c r="D149" t="s">
         <v>446</v>
       </c>
-      <c r="C149" t="s">
-        <v>445</v>
-      </c>
-      <c r="D149" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4">
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>5</v>
       </c>
       <c r="B150" t="s">
+        <v>448</v>
+      </c>
+      <c r="C150" t="s">
+        <v>447</v>
+      </c>
+      <c r="D150" t="s">
         <v>449</v>
       </c>
-      <c r="C150" t="s">
-        <v>448</v>
-      </c>
-      <c r="D150" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4">
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>5</v>
       </c>
       <c r="B151" t="s">
+        <v>451</v>
+      </c>
+      <c r="C151" t="s">
+        <v>450</v>
+      </c>
+      <c r="D151" t="s">
         <v>452</v>
       </c>
-      <c r="C151" t="s">
-        <v>451</v>
-      </c>
-      <c r="D151" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4">
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>5</v>
       </c>
       <c r="B152" t="s">
+        <v>454</v>
+      </c>
+      <c r="C152" t="s">
+        <v>453</v>
+      </c>
+      <c r="D152" t="s">
         <v>455</v>
       </c>
-      <c r="C152" t="s">
-        <v>454</v>
-      </c>
-      <c r="D152" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4">
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>5</v>
       </c>
       <c r="B153" t="s">
+        <v>457</v>
+      </c>
+      <c r="C153" t="s">
+        <v>456</v>
+      </c>
+      <c r="D153" t="s">
         <v>458</v>
       </c>
-      <c r="C153" t="s">
-        <v>457</v>
-      </c>
-      <c r="D153" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4">
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>5</v>
       </c>
       <c r="B154" t="s">
+        <v>460</v>
+      </c>
+      <c r="C154" t="s">
+        <v>459</v>
+      </c>
+      <c r="D154" t="s">
         <v>461</v>
       </c>
-      <c r="C154" t="s">
-        <v>460</v>
-      </c>
-      <c r="D154" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4">
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>5</v>
       </c>
       <c r="B155" t="s">
+        <v>463</v>
+      </c>
+      <c r="C155" t="s">
+        <v>462</v>
+      </c>
+      <c r="D155" t="s">
         <v>464</v>
       </c>
-      <c r="C155" t="s">
-        <v>463</v>
-      </c>
-      <c r="D155" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4">
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>5</v>
       </c>
       <c r="B156" t="s">
+        <v>466</v>
+      </c>
+      <c r="C156" t="s">
+        <v>465</v>
+      </c>
+      <c r="D156" t="s">
         <v>467</v>
       </c>
-      <c r="C156" t="s">
-        <v>466</v>
-      </c>
-      <c r="D156" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4">
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>5</v>
       </c>
       <c r="B157" t="s">
+        <v>469</v>
+      </c>
+      <c r="C157" t="s">
+        <v>468</v>
+      </c>
+      <c r="D157" t="s">
         <v>470</v>
       </c>
-      <c r="C157" t="s">
-        <v>469</v>
-      </c>
-      <c r="D157" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4">
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>5</v>
       </c>
@@ -6237,139 +6239,139 @@
         <v>49</v>
       </c>
       <c r="C158" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D158" t="s">
         <v>1013</v>
       </c>
-      <c r="D158" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4">
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>5</v>
       </c>
       <c r="B159" t="s">
+        <v>472</v>
+      </c>
+      <c r="C159" t="s">
+        <v>471</v>
+      </c>
+      <c r="D159" t="s">
         <v>473</v>
       </c>
-      <c r="C159" t="s">
-        <v>472</v>
-      </c>
-      <c r="D159" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4">
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>5</v>
       </c>
       <c r="B160" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C160" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D160" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>5</v>
       </c>
       <c r="B161" t="s">
+        <v>477</v>
+      </c>
+      <c r="C161" t="s">
+        <v>476</v>
+      </c>
+      <c r="D161" t="s">
         <v>478</v>
       </c>
-      <c r="C161" t="s">
-        <v>477</v>
-      </c>
-      <c r="D161" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4">
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>5</v>
       </c>
       <c r="B162" t="s">
+        <v>480</v>
+      </c>
+      <c r="C162" t="s">
+        <v>479</v>
+      </c>
+      <c r="D162" t="s">
         <v>481</v>
       </c>
-      <c r="C162" t="s">
-        <v>480</v>
-      </c>
-      <c r="D162" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4">
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>5</v>
       </c>
       <c r="B163" t="s">
+        <v>483</v>
+      </c>
+      <c r="C163" t="s">
+        <v>482</v>
+      </c>
+      <c r="D163" t="s">
         <v>484</v>
       </c>
-      <c r="C163" t="s">
-        <v>483</v>
-      </c>
-      <c r="D163" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4">
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>5</v>
       </c>
       <c r="B164" t="s">
+        <v>486</v>
+      </c>
+      <c r="C164" t="s">
+        <v>485</v>
+      </c>
+      <c r="D164" t="s">
         <v>487</v>
       </c>
-      <c r="C164" t="s">
-        <v>486</v>
-      </c>
-      <c r="D164" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4">
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>5</v>
       </c>
       <c r="B165" t="s">
+        <v>489</v>
+      </c>
+      <c r="C165" t="s">
+        <v>488</v>
+      </c>
+      <c r="D165" t="s">
         <v>490</v>
       </c>
-      <c r="C165" t="s">
-        <v>489</v>
-      </c>
-      <c r="D165" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4">
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>5</v>
       </c>
       <c r="B166" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C166" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D166" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>5</v>
       </c>
       <c r="B167" t="s">
+        <v>492</v>
+      </c>
+      <c r="C167" t="s">
+        <v>491</v>
+      </c>
+      <c r="D167" t="s">
         <v>493</v>
       </c>
-      <c r="C167" t="s">
-        <v>492</v>
-      </c>
-      <c r="D167" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4">
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>5</v>
       </c>
@@ -6383,329 +6385,329 @@
         <v>18</v>
       </c>
     </row>
-    <row r="169" spans="1:4">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>5</v>
       </c>
       <c r="B169" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C169" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D169" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>5</v>
       </c>
       <c r="B170" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C170" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D170" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="171" spans="1:4">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>5</v>
       </c>
       <c r="B171" t="s">
+        <v>499</v>
+      </c>
+      <c r="C171" t="s">
+        <v>498</v>
+      </c>
+      <c r="D171" t="s">
         <v>500</v>
       </c>
-      <c r="C171" t="s">
-        <v>499</v>
-      </c>
-      <c r="D171" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4">
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>5</v>
       </c>
       <c r="B172" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C172" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D172" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>5</v>
       </c>
       <c r="B173" t="s">
+        <v>504</v>
+      </c>
+      <c r="C173" t="s">
+        <v>503</v>
+      </c>
+      <c r="D173" t="s">
         <v>505</v>
       </c>
-      <c r="C173" t="s">
-        <v>504</v>
-      </c>
-      <c r="D173" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4">
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>5</v>
       </c>
       <c r="B174" t="s">
+        <v>507</v>
+      </c>
+      <c r="C174" t="s">
+        <v>506</v>
+      </c>
+      <c r="D174" t="s">
         <v>508</v>
       </c>
-      <c r="C174" t="s">
-        <v>507</v>
-      </c>
-      <c r="D174" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4">
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>5</v>
       </c>
       <c r="B175" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C175" t="s">
+        <v>509</v>
+      </c>
+      <c r="D175" t="s">
         <v>510</v>
       </c>
-      <c r="D175" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4">
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>5</v>
       </c>
       <c r="B176" t="s">
+        <v>512</v>
+      </c>
+      <c r="C176" t="s">
+        <v>511</v>
+      </c>
+      <c r="D176" t="s">
         <v>513</v>
       </c>
-      <c r="C176" t="s">
-        <v>512</v>
-      </c>
-      <c r="D176" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4">
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>5</v>
       </c>
       <c r="B177" t="s">
+        <v>515</v>
+      </c>
+      <c r="C177" t="s">
+        <v>514</v>
+      </c>
+      <c r="D177" t="s">
         <v>516</v>
       </c>
-      <c r="C177" t="s">
-        <v>515</v>
-      </c>
-      <c r="D177" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4">
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>5</v>
       </c>
       <c r="B178" t="s">
+        <v>517</v>
+      </c>
+      <c r="C178" t="s">
+        <v>516</v>
+      </c>
+      <c r="D178" t="s">
         <v>518</v>
       </c>
-      <c r="C178" t="s">
-        <v>517</v>
-      </c>
-      <c r="D178" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4">
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>5</v>
       </c>
       <c r="B179" t="s">
+        <v>520</v>
+      </c>
+      <c r="C179" t="s">
+        <v>519</v>
+      </c>
+      <c r="D179" t="s">
         <v>521</v>
       </c>
-      <c r="C179" t="s">
-        <v>520</v>
-      </c>
-      <c r="D179" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4">
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>5</v>
       </c>
       <c r="B180" t="s">
+        <v>523</v>
+      </c>
+      <c r="C180" t="s">
+        <v>522</v>
+      </c>
+      <c r="D180" t="s">
         <v>524</v>
       </c>
-      <c r="C180" t="s">
-        <v>523</v>
-      </c>
-      <c r="D180" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4">
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>5</v>
       </c>
       <c r="B181" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C181" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D181" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>5</v>
       </c>
       <c r="B182" t="s">
+        <v>526</v>
+      </c>
+      <c r="C182" t="s">
+        <v>525</v>
+      </c>
+      <c r="D182" t="s">
         <v>527</v>
       </c>
-      <c r="C182" t="s">
-        <v>526</v>
-      </c>
-      <c r="D182" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4">
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>5</v>
       </c>
       <c r="B183" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C183" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D183" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>5</v>
       </c>
       <c r="B184" t="s">
+        <v>531</v>
+      </c>
+      <c r="C184" t="s">
+        <v>530</v>
+      </c>
+      <c r="D184" t="s">
         <v>532</v>
       </c>
-      <c r="C184" t="s">
-        <v>531</v>
-      </c>
-      <c r="D184" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4">
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>6</v>
       </c>
       <c r="B185" t="s">
+        <v>534</v>
+      </c>
+      <c r="C185" t="s">
+        <v>533</v>
+      </c>
+      <c r="D185" t="s">
         <v>535</v>
       </c>
-      <c r="C185" t="s">
-        <v>534</v>
-      </c>
-      <c r="D185" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4">
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>6</v>
       </c>
       <c r="B186" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C186" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D186" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>6</v>
       </c>
       <c r="B187" t="s">
+        <v>539</v>
+      </c>
+      <c r="C187" t="s">
+        <v>538</v>
+      </c>
+      <c r="D187" t="s">
         <v>540</v>
       </c>
-      <c r="C187" t="s">
-        <v>539</v>
-      </c>
-      <c r="D187" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4">
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>6</v>
       </c>
       <c r="B188" t="s">
+        <v>542</v>
+      </c>
+      <c r="C188" t="s">
+        <v>541</v>
+      </c>
+      <c r="D188" t="s">
         <v>543</v>
       </c>
-      <c r="C188" t="s">
-        <v>542</v>
-      </c>
-      <c r="D188" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4">
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>6</v>
       </c>
       <c r="B189" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C189" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D189" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>6</v>
       </c>
       <c r="B190" t="s">
+        <v>547</v>
+      </c>
+      <c r="C190" t="s">
+        <v>546</v>
+      </c>
+      <c r="D190" t="s">
         <v>548</v>
       </c>
-      <c r="C190" t="s">
-        <v>547</v>
-      </c>
-      <c r="D190" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4">
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>6</v>
       </c>
       <c r="B191" t="s">
+        <v>550</v>
+      </c>
+      <c r="C191" t="s">
+        <v>549</v>
+      </c>
+      <c r="D191" t="s">
         <v>551</v>
       </c>
-      <c r="C191" t="s">
-        <v>550</v>
-      </c>
-      <c r="D191" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4">
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>6</v>
       </c>
@@ -6719,287 +6721,287 @@
         <v>24</v>
       </c>
     </row>
-    <row r="193" spans="1:4">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>6</v>
       </c>
       <c r="B193" t="s">
+        <v>553</v>
+      </c>
+      <c r="C193" t="s">
+        <v>552</v>
+      </c>
+      <c r="D193" t="s">
         <v>554</v>
       </c>
-      <c r="C193" t="s">
-        <v>553</v>
-      </c>
-      <c r="D193" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4">
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>6</v>
       </c>
       <c r="B194" t="s">
+        <v>556</v>
+      </c>
+      <c r="C194" t="s">
+        <v>555</v>
+      </c>
+      <c r="D194" t="s">
         <v>557</v>
       </c>
-      <c r="C194" t="s">
-        <v>556</v>
-      </c>
-      <c r="D194" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4">
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>6</v>
       </c>
       <c r="B195" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C195" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D195" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>6</v>
       </c>
       <c r="B196" t="s">
+        <v>561</v>
+      </c>
+      <c r="C196" t="s">
+        <v>560</v>
+      </c>
+      <c r="D196" t="s">
         <v>562</v>
       </c>
-      <c r="C196" t="s">
-        <v>561</v>
-      </c>
-      <c r="D196" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4">
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>6</v>
       </c>
       <c r="B197" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C197" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D197" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>6</v>
       </c>
       <c r="B198" t="s">
+        <v>566</v>
+      </c>
+      <c r="C198" t="s">
+        <v>565</v>
+      </c>
+      <c r="D198" t="s">
         <v>567</v>
       </c>
-      <c r="C198" t="s">
-        <v>566</v>
-      </c>
-      <c r="D198" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4">
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>6</v>
       </c>
       <c r="B199" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C199" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D199" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>6</v>
       </c>
       <c r="B200" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C200" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D200" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>6</v>
       </c>
       <c r="B201" t="s">
+        <v>573</v>
+      </c>
+      <c r="C201" t="s">
+        <v>572</v>
+      </c>
+      <c r="D201" t="s">
         <v>574</v>
       </c>
-      <c r="C201" t="s">
-        <v>573</v>
-      </c>
-      <c r="D201" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4">
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>6</v>
       </c>
       <c r="B202" t="s">
+        <v>576</v>
+      </c>
+      <c r="C202" t="s">
+        <v>575</v>
+      </c>
+      <c r="D202" t="s">
         <v>577</v>
       </c>
-      <c r="C202" t="s">
-        <v>576</v>
-      </c>
-      <c r="D202" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4">
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>6</v>
       </c>
       <c r="B203" t="s">
+        <v>579</v>
+      </c>
+      <c r="C203" t="s">
+        <v>578</v>
+      </c>
+      <c r="D203" t="s">
         <v>580</v>
       </c>
-      <c r="C203" t="s">
-        <v>579</v>
-      </c>
-      <c r="D203" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4">
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>6</v>
       </c>
       <c r="B204" t="s">
+        <v>582</v>
+      </c>
+      <c r="C204" t="s">
+        <v>581</v>
+      </c>
+      <c r="D204" t="s">
         <v>583</v>
       </c>
-      <c r="C204" t="s">
-        <v>582</v>
-      </c>
-      <c r="D204" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4">
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>6</v>
       </c>
       <c r="B205" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C205" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D205" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>6</v>
       </c>
       <c r="B206" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C206" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D206" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>6</v>
       </c>
       <c r="B207" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C207" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D207" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>6</v>
       </c>
       <c r="B208" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C208" t="s">
+        <v>590</v>
+      </c>
+      <c r="D208" s="2" t="s">
         <v>1016</v>
       </c>
-      <c r="C208" t="s">
-        <v>591</v>
-      </c>
-      <c r="D208" s="2" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4">
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>6</v>
       </c>
       <c r="B209" t="s">
+        <v>591</v>
+      </c>
+      <c r="C209" t="s">
         <v>592</v>
       </c>
-      <c r="C209" t="s">
+      <c r="D209" t="s">
         <v>593</v>
       </c>
-      <c r="D209" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4">
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>6</v>
       </c>
       <c r="B210" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C210" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D210" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>6</v>
       </c>
       <c r="B211" t="s">
+        <v>597</v>
+      </c>
+      <c r="C211" t="s">
+        <v>596</v>
+      </c>
+      <c r="D211" t="s">
         <v>598</v>
       </c>
-      <c r="C211" t="s">
-        <v>597</v>
-      </c>
-      <c r="D211" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="212" spans="1:4">
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>6</v>
       </c>
       <c r="B212" t="s">
+        <v>600</v>
+      </c>
+      <c r="C212" t="s">
+        <v>599</v>
+      </c>
+      <c r="D212" t="s">
         <v>601</v>
       </c>
-      <c r="C212" t="s">
-        <v>600</v>
-      </c>
-      <c r="D212" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4">
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>6</v>
       </c>
@@ -7013,35 +7015,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:4">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>6</v>
       </c>
       <c r="B214" t="s">
+        <v>603</v>
+      </c>
+      <c r="C214" t="s">
+        <v>602</v>
+      </c>
+      <c r="D214" t="s">
         <v>604</v>
       </c>
-      <c r="C214" t="s">
-        <v>603</v>
-      </c>
-      <c r="D214" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4">
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>6</v>
       </c>
       <c r="B215" t="s">
+        <v>606</v>
+      </c>
+      <c r="C215" t="s">
+        <v>605</v>
+      </c>
+      <c r="D215" t="s">
         <v>607</v>
       </c>
-      <c r="C215" t="s">
-        <v>606</v>
-      </c>
-      <c r="D215" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4">
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>6</v>
       </c>
@@ -7052,52 +7054,52 @@
         <v>31</v>
       </c>
       <c r="D216" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>6</v>
       </c>
       <c r="B217" t="s">
+        <v>610</v>
+      </c>
+      <c r="C217" t="s">
+        <v>609</v>
+      </c>
+      <c r="D217" t="s">
         <v>611</v>
       </c>
-      <c r="C217" t="s">
-        <v>610</v>
-      </c>
-      <c r="D217" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="218" spans="1:4">
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>6</v>
       </c>
       <c r="B218" t="s">
+        <v>613</v>
+      </c>
+      <c r="C218" t="s">
+        <v>612</v>
+      </c>
+      <c r="D218" t="s">
         <v>614</v>
       </c>
-      <c r="C218" t="s">
-        <v>613</v>
-      </c>
-      <c r="D218" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4">
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>6</v>
       </c>
       <c r="B219" t="s">
+        <v>616</v>
+      </c>
+      <c r="C219" t="s">
+        <v>615</v>
+      </c>
+      <c r="D219" t="s">
         <v>617</v>
       </c>
-      <c r="C219" t="s">
-        <v>616</v>
-      </c>
-      <c r="D219" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="220" spans="1:4">
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>6</v>
       </c>
@@ -7111,161 +7113,161 @@
         <v>33</v>
       </c>
     </row>
-    <row r="221" spans="1:4">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>7</v>
       </c>
       <c r="B221" t="s">
+        <v>619</v>
+      </c>
+      <c r="C221" t="s">
+        <v>618</v>
+      </c>
+      <c r="D221" t="s">
         <v>620</v>
       </c>
-      <c r="C221" t="s">
-        <v>619</v>
-      </c>
-      <c r="D221" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="222" spans="1:4">
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>7</v>
       </c>
       <c r="B222" t="s">
+        <v>622</v>
+      </c>
+      <c r="C222" t="s">
+        <v>621</v>
+      </c>
+      <c r="D222" t="s">
         <v>623</v>
       </c>
-      <c r="C222" t="s">
-        <v>622</v>
-      </c>
-      <c r="D222" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4">
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>7</v>
       </c>
       <c r="B223" t="s">
+        <v>625</v>
+      </c>
+      <c r="C223" t="s">
+        <v>624</v>
+      </c>
+      <c r="D223" t="s">
         <v>626</v>
       </c>
-      <c r="C223" t="s">
-        <v>625</v>
-      </c>
-      <c r="D223" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4">
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>7</v>
       </c>
       <c r="B224" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C224" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D224" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="225" spans="1:4">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>7</v>
       </c>
       <c r="B225" t="s">
+        <v>630</v>
+      </c>
+      <c r="C225" t="s">
+        <v>629</v>
+      </c>
+      <c r="D225" t="s">
         <v>631</v>
       </c>
-      <c r="C225" t="s">
-        <v>630</v>
-      </c>
-      <c r="D225" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="226" spans="1:4">
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>7</v>
       </c>
       <c r="B226" t="s">
+        <v>633</v>
+      </c>
+      <c r="C226" t="s">
+        <v>632</v>
+      </c>
+      <c r="D226" t="s">
         <v>634</v>
       </c>
-      <c r="C226" t="s">
-        <v>633</v>
-      </c>
-      <c r="D226" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="227" spans="1:4">
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>7</v>
       </c>
       <c r="B227" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C227" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D227" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>7</v>
       </c>
       <c r="B228" t="s">
+        <v>638</v>
+      </c>
+      <c r="C228" t="s">
+        <v>637</v>
+      </c>
+      <c r="D228" t="s">
         <v>639</v>
       </c>
-      <c r="C228" t="s">
-        <v>638</v>
-      </c>
-      <c r="D228" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="229" spans="1:4">
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>7</v>
       </c>
       <c r="B229" t="s">
+        <v>641</v>
+      </c>
+      <c r="C229" t="s">
+        <v>640</v>
+      </c>
+      <c r="D229" t="s">
         <v>642</v>
       </c>
-      <c r="C229" t="s">
-        <v>641</v>
-      </c>
-      <c r="D229" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="230" spans="1:4">
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>7</v>
       </c>
       <c r="B230" t="s">
+        <v>644</v>
+      </c>
+      <c r="C230" t="s">
+        <v>643</v>
+      </c>
+      <c r="D230" t="s">
         <v>645</v>
       </c>
-      <c r="C230" t="s">
-        <v>644</v>
-      </c>
-      <c r="D230" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4">
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>7</v>
       </c>
       <c r="B231" t="s">
+        <v>647</v>
+      </c>
+      <c r="C231" t="s">
+        <v>646</v>
+      </c>
+      <c r="D231" t="s">
         <v>648</v>
       </c>
-      <c r="C231" t="s">
-        <v>647</v>
-      </c>
-      <c r="D231" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="232" spans="1:4">
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>7</v>
       </c>
@@ -7279,21 +7281,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="233" spans="1:4">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>7</v>
       </c>
       <c r="B233" t="s">
+        <v>650</v>
+      </c>
+      <c r="C233" t="s">
+        <v>649</v>
+      </c>
+      <c r="D233" t="s">
         <v>651</v>
       </c>
-      <c r="C233" t="s">
-        <v>650</v>
-      </c>
-      <c r="D233" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="234" spans="1:4">
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>7</v>
       </c>
@@ -7307,427 +7309,427 @@
         <v>61</v>
       </c>
     </row>
-    <row r="235" spans="1:4">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>7</v>
       </c>
       <c r="B235" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C235" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D235" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="236" spans="1:4">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>7</v>
       </c>
       <c r="B236" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C236" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D236" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="237" spans="1:4">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>7</v>
       </c>
       <c r="B237" t="s">
+        <v>657</v>
+      </c>
+      <c r="C237" t="s">
+        <v>656</v>
+      </c>
+      <c r="D237" t="s">
         <v>658</v>
       </c>
-      <c r="C237" t="s">
-        <v>657</v>
-      </c>
-      <c r="D237" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="238" spans="1:4">
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>7</v>
       </c>
       <c r="B238" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C238" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D238" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="239" spans="1:4">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>7</v>
       </c>
       <c r="B239" t="s">
+        <v>75</v>
+      </c>
+      <c r="C239" t="s">
+        <v>74</v>
+      </c>
+      <c r="D239" t="s">
         <v>76</v>
       </c>
-      <c r="C239" t="s">
-        <v>75</v>
-      </c>
-      <c r="D239" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="240" spans="1:4">
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>7</v>
       </c>
       <c r="B240" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C240" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D240" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="241" spans="1:4">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>7</v>
       </c>
       <c r="B241" t="s">
+        <v>662</v>
+      </c>
+      <c r="C241" t="s">
+        <v>661</v>
+      </c>
+      <c r="D241" t="s">
         <v>663</v>
       </c>
-      <c r="C241" t="s">
-        <v>662</v>
-      </c>
-      <c r="D241" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="242" spans="1:4">
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>7</v>
       </c>
       <c r="B242" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C242" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D242" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="243" spans="1:4">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>7</v>
       </c>
       <c r="B243" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C243" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D243" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="244" spans="1:4">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>7</v>
       </c>
       <c r="B244" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C244" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D244" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="245" spans="1:4">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>7</v>
       </c>
       <c r="B245" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C245" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D245" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="246" spans="1:4">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>7</v>
       </c>
       <c r="B246" t="s">
+        <v>673</v>
+      </c>
+      <c r="C246" t="s">
+        <v>672</v>
+      </c>
+      <c r="D246" t="s">
         <v>674</v>
       </c>
-      <c r="C246" t="s">
-        <v>673</v>
-      </c>
-      <c r="D246" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="247" spans="1:4">
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>7</v>
       </c>
       <c r="B247" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C247" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D247" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="248" spans="1:4">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>7</v>
       </c>
       <c r="B248" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C248" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D248" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="249" spans="1:4">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>7</v>
       </c>
       <c r="B249" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C249" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D249" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="250" spans="1:4">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>7</v>
       </c>
       <c r="B250" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C250" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D250" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="251" spans="1:4">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>8</v>
       </c>
       <c r="B251" t="s">
+        <v>684</v>
+      </c>
+      <c r="C251" t="s">
+        <v>683</v>
+      </c>
+      <c r="D251" t="s">
         <v>685</v>
       </c>
-      <c r="C251" t="s">
-        <v>684</v>
-      </c>
-      <c r="D251" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4">
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>8</v>
       </c>
       <c r="B252" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C252" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D252" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="253" spans="1:4">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>8</v>
       </c>
       <c r="B253" t="s">
+        <v>308</v>
+      </c>
+      <c r="C253" t="s">
+        <v>307</v>
+      </c>
+      <c r="D253" t="s">
         <v>309</v>
       </c>
-      <c r="C253" t="s">
-        <v>308</v>
-      </c>
-      <c r="D253" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="254" spans="1:4">
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>8</v>
       </c>
       <c r="B254" t="s">
+        <v>689</v>
+      </c>
+      <c r="C254" t="s">
+        <v>688</v>
+      </c>
+      <c r="D254" t="s">
         <v>690</v>
       </c>
-      <c r="C254" t="s">
-        <v>689</v>
-      </c>
-      <c r="D254" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="255" spans="1:4">
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>8</v>
       </c>
       <c r="B255" t="s">
+        <v>692</v>
+      </c>
+      <c r="C255" t="s">
+        <v>691</v>
+      </c>
+      <c r="D255" t="s">
         <v>693</v>
       </c>
-      <c r="C255" t="s">
-        <v>692</v>
-      </c>
-      <c r="D255" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="256" spans="1:4">
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>8</v>
       </c>
       <c r="B256" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C256" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D256" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="257" spans="1:4">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>8</v>
       </c>
       <c r="B257" t="s">
+        <v>697</v>
+      </c>
+      <c r="C257" t="s">
+        <v>696</v>
+      </c>
+      <c r="D257" t="s">
         <v>698</v>
       </c>
-      <c r="C257" t="s">
-        <v>697</v>
-      </c>
-      <c r="D257" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="258" spans="1:4">
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>8</v>
       </c>
       <c r="B258" t="s">
+        <v>700</v>
+      </c>
+      <c r="C258" t="s">
+        <v>699</v>
+      </c>
+      <c r="D258" t="s">
         <v>701</v>
       </c>
-      <c r="C258" t="s">
-        <v>700</v>
-      </c>
-      <c r="D258" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="259" spans="1:4">
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>8</v>
       </c>
       <c r="B259" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C259" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D259" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="260" spans="1:4">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>8</v>
       </c>
       <c r="B260" t="s">
+        <v>477</v>
+      </c>
+      <c r="C260" t="s">
+        <v>476</v>
+      </c>
+      <c r="D260" t="s">
         <v>478</v>
       </c>
-      <c r="C260" t="s">
-        <v>477</v>
-      </c>
-      <c r="D260" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="261" spans="1:4">
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>8</v>
       </c>
       <c r="B261" t="s">
+        <v>63</v>
+      </c>
+      <c r="C261" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D261" t="s">
         <v>64</v>
       </c>
-      <c r="C261" t="s">
-        <v>63</v>
-      </c>
-      <c r="D261" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="262" spans="1:4">
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>8</v>
       </c>
       <c r="B262" t="s">
+        <v>705</v>
+      </c>
+      <c r="C262" t="s">
+        <v>704</v>
+      </c>
+      <c r="D262" t="s">
         <v>706</v>
       </c>
-      <c r="C262" t="s">
-        <v>705</v>
-      </c>
-      <c r="D262" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="263" spans="1:4">
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>8</v>
       </c>
       <c r="B263" t="s">
+        <v>708</v>
+      </c>
+      <c r="C263" t="s">
+        <v>707</v>
+      </c>
+      <c r="D263" t="s">
         <v>709</v>
       </c>
-      <c r="C263" t="s">
-        <v>708</v>
-      </c>
-      <c r="D263" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="264" spans="1:4">
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>8</v>
       </c>
       <c r="B264" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C264" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D264" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="265" spans="1:4">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>8</v>
       </c>
@@ -7738,682 +7740,682 @@
         <v>45</v>
       </c>
       <c r="D265" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="266" spans="1:4">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>8</v>
       </c>
       <c r="B266" t="s">
+        <v>714</v>
+      </c>
+      <c r="C266" t="s">
+        <v>713</v>
+      </c>
+      <c r="D266" t="s">
         <v>715</v>
       </c>
-      <c r="C266" t="s">
-        <v>714</v>
-      </c>
-      <c r="D266" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="267" spans="1:4">
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>8</v>
       </c>
       <c r="B267" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C267" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D267" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="268" spans="1:4">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>8</v>
       </c>
       <c r="B268" t="s">
+        <v>718</v>
+      </c>
+      <c r="C268" t="s">
+        <v>717</v>
+      </c>
+      <c r="D268" t="s">
         <v>719</v>
       </c>
-      <c r="C268" t="s">
-        <v>718</v>
-      </c>
-      <c r="D268" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="269" spans="1:4">
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>8</v>
       </c>
       <c r="B269" t="s">
+        <v>721</v>
+      </c>
+      <c r="C269" t="s">
+        <v>720</v>
+      </c>
+      <c r="D269" t="s">
         <v>722</v>
       </c>
-      <c r="C269" t="s">
-        <v>721</v>
-      </c>
-      <c r="D269" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="270" spans="1:4">
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>8</v>
       </c>
       <c r="B270" t="s">
+        <v>724</v>
+      </c>
+      <c r="C270" t="s">
+        <v>723</v>
+      </c>
+      <c r="D270" t="s">
         <v>725</v>
       </c>
-      <c r="C270" t="s">
-        <v>724</v>
-      </c>
-      <c r="D270" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4">
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>8</v>
       </c>
       <c r="B271" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C271" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D271" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="272" spans="1:4">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>8</v>
       </c>
       <c r="B272" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C272" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D272" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="273" spans="1:4">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>8</v>
       </c>
       <c r="B273" t="s">
+        <v>731</v>
+      </c>
+      <c r="C273" t="s">
+        <v>730</v>
+      </c>
+      <c r="D273" t="s">
         <v>732</v>
       </c>
-      <c r="C273" t="s">
-        <v>731</v>
-      </c>
-      <c r="D273" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="274" spans="1:4">
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>8</v>
       </c>
       <c r="B274" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C274" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D274" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>8</v>
       </c>
       <c r="B275" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C275" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D275" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="276" spans="1:4">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>8</v>
       </c>
       <c r="B276" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C276" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D276" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="277" spans="1:4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>8</v>
       </c>
       <c r="B277" t="s">
+        <v>740</v>
+      </c>
+      <c r="C277" t="s">
+        <v>739</v>
+      </c>
+      <c r="D277" t="s">
         <v>741</v>
       </c>
-      <c r="C277" t="s">
-        <v>740</v>
-      </c>
-      <c r="D277" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="278" spans="1:4">
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>8</v>
       </c>
       <c r="B278" t="s">
+        <v>743</v>
+      </c>
+      <c r="C278" t="s">
+        <v>742</v>
+      </c>
+      <c r="D278" t="s">
         <v>744</v>
       </c>
-      <c r="C278" t="s">
-        <v>743</v>
-      </c>
-      <c r="D278" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="279" spans="1:4">
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>8</v>
       </c>
       <c r="B279" t="s">
+        <v>746</v>
+      </c>
+      <c r="C279" t="s">
+        <v>745</v>
+      </c>
+      <c r="D279" t="s">
         <v>747</v>
       </c>
-      <c r="C279" t="s">
-        <v>746</v>
-      </c>
-      <c r="D279" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4">
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>8</v>
       </c>
       <c r="B280" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C280" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D280" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>8</v>
       </c>
       <c r="B281" t="s">
+        <v>751</v>
+      </c>
+      <c r="C281" t="s">
+        <v>750</v>
+      </c>
+      <c r="D281" t="s">
         <v>752</v>
       </c>
-      <c r="C281" t="s">
-        <v>751</v>
-      </c>
-      <c r="D281" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4">
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>8</v>
       </c>
       <c r="B282" t="s">
+        <v>754</v>
+      </c>
+      <c r="C282" t="s">
+        <v>753</v>
+      </c>
+      <c r="D282" t="s">
         <v>755</v>
       </c>
-      <c r="C282" t="s">
-        <v>754</v>
-      </c>
-      <c r="D282" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="283" spans="1:4">
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>8</v>
       </c>
       <c r="B283" t="s">
+        <v>757</v>
+      </c>
+      <c r="C283" t="s">
+        <v>756</v>
+      </c>
+      <c r="D283" t="s">
         <v>758</v>
       </c>
-      <c r="C283" t="s">
-        <v>757</v>
-      </c>
-      <c r="D283" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="284" spans="1:4">
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>9</v>
       </c>
       <c r="B284" t="s">
+        <v>760</v>
+      </c>
+      <c r="C284" t="s">
+        <v>759</v>
+      </c>
+      <c r="D284" t="s">
         <v>761</v>
       </c>
-      <c r="C284" t="s">
-        <v>760</v>
-      </c>
-      <c r="D284" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="285" spans="1:4">
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>9</v>
       </c>
       <c r="B285" t="s">
+        <v>763</v>
+      </c>
+      <c r="C285" t="s">
+        <v>762</v>
+      </c>
+      <c r="D285" t="s">
         <v>764</v>
       </c>
-      <c r="C285" t="s">
-        <v>763</v>
-      </c>
-      <c r="D285" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="286" spans="1:4">
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>9</v>
       </c>
       <c r="B286" t="s">
+        <v>766</v>
+      </c>
+      <c r="C286" t="s">
+        <v>765</v>
+      </c>
+      <c r="D286" t="s">
         <v>767</v>
       </c>
-      <c r="C286" t="s">
-        <v>766</v>
-      </c>
-      <c r="D286" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="287" spans="1:4">
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>9</v>
       </c>
       <c r="B287" t="s">
+        <v>769</v>
+      </c>
+      <c r="C287" t="s">
+        <v>768</v>
+      </c>
+      <c r="D287" t="s">
         <v>770</v>
       </c>
-      <c r="C287" t="s">
-        <v>769</v>
-      </c>
-      <c r="D287" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="288" spans="1:4">
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>9</v>
       </c>
       <c r="B288" t="s">
+        <v>772</v>
+      </c>
+      <c r="C288" t="s">
+        <v>771</v>
+      </c>
+      <c r="D288" t="s">
         <v>773</v>
       </c>
-      <c r="C288" t="s">
-        <v>772</v>
-      </c>
-      <c r="D288" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="289" spans="1:4">
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>9</v>
       </c>
       <c r="B289" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C289" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D289" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="290" spans="1:4">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>9</v>
       </c>
       <c r="B290" t="s">
+        <v>775</v>
+      </c>
+      <c r="C290" t="s">
+        <v>774</v>
+      </c>
+      <c r="D290" t="s">
         <v>776</v>
       </c>
-      <c r="C290" t="s">
-        <v>775</v>
-      </c>
-      <c r="D290" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="291" spans="1:4">
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>9</v>
       </c>
       <c r="B291" t="s">
+        <v>778</v>
+      </c>
+      <c r="C291" t="s">
+        <v>777</v>
+      </c>
+      <c r="D291" t="s">
         <v>779</v>
       </c>
-      <c r="C291" t="s">
-        <v>778</v>
-      </c>
-      <c r="D291" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="292" spans="1:4">
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>9</v>
       </c>
       <c r="B292" t="s">
+        <v>781</v>
+      </c>
+      <c r="C292" t="s">
+        <v>780</v>
+      </c>
+      <c r="D292" t="s">
         <v>782</v>
       </c>
-      <c r="C292" t="s">
-        <v>781</v>
-      </c>
-      <c r="D292" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="293" spans="1:4">
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>9</v>
       </c>
       <c r="B293" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C293" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D293" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="294" spans="1:4">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>9</v>
       </c>
       <c r="B294" t="s">
+        <v>784</v>
+      </c>
+      <c r="C294" t="s">
+        <v>783</v>
+      </c>
+      <c r="D294" t="s">
         <v>785</v>
       </c>
-      <c r="C294" t="s">
-        <v>784</v>
-      </c>
-      <c r="D294" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="295" spans="1:4">
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>9</v>
       </c>
       <c r="B295" t="s">
+        <v>787</v>
+      </c>
+      <c r="C295" t="s">
+        <v>786</v>
+      </c>
+      <c r="D295" t="s">
         <v>788</v>
       </c>
-      <c r="C295" t="s">
-        <v>787</v>
-      </c>
-      <c r="D295" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="296" spans="1:4">
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>9</v>
       </c>
       <c r="B296" t="s">
+        <v>790</v>
+      </c>
+      <c r="C296" t="s">
+        <v>789</v>
+      </c>
+      <c r="D296" t="s">
         <v>791</v>
       </c>
-      <c r="C296" t="s">
-        <v>790</v>
-      </c>
-      <c r="D296" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="297" spans="1:4">
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>9</v>
       </c>
       <c r="B297" t="s">
+        <v>793</v>
+      </c>
+      <c r="C297" t="s">
+        <v>792</v>
+      </c>
+      <c r="D297" t="s">
         <v>794</v>
       </c>
-      <c r="C297" t="s">
-        <v>793</v>
-      </c>
-      <c r="D297" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="298" spans="1:4">
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>9</v>
       </c>
       <c r="B298" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C298" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D298" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="299" spans="1:4">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>9</v>
       </c>
       <c r="B299" t="s">
+        <v>796</v>
+      </c>
+      <c r="C299" t="s">
+        <v>795</v>
+      </c>
+      <c r="D299" t="s">
         <v>797</v>
       </c>
-      <c r="C299" t="s">
-        <v>796</v>
-      </c>
-      <c r="D299" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="300" spans="1:4">
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>9</v>
       </c>
       <c r="B300" t="s">
+        <v>799</v>
+      </c>
+      <c r="C300" t="s">
+        <v>798</v>
+      </c>
+      <c r="D300" t="s">
         <v>800</v>
       </c>
-      <c r="C300" t="s">
-        <v>799</v>
-      </c>
-      <c r="D300" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="301" spans="1:4">
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>9</v>
       </c>
       <c r="B301" t="s">
+        <v>343</v>
+      </c>
+      <c r="C301" t="s">
+        <v>342</v>
+      </c>
+      <c r="D301" t="s">
         <v>344</v>
       </c>
-      <c r="C301" t="s">
-        <v>343</v>
-      </c>
-      <c r="D301" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="302" spans="1:4">
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>9</v>
       </c>
       <c r="B302" t="s">
+        <v>802</v>
+      </c>
+      <c r="C302" t="s">
+        <v>801</v>
+      </c>
+      <c r="D302" t="s">
         <v>803</v>
       </c>
-      <c r="C302" t="s">
-        <v>802</v>
-      </c>
-      <c r="D302" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="303" spans="1:4">
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>9</v>
       </c>
       <c r="B303" t="s">
+        <v>805</v>
+      </c>
+      <c r="C303" t="s">
+        <v>804</v>
+      </c>
+      <c r="D303" t="s">
         <v>806</v>
       </c>
-      <c r="C303" t="s">
-        <v>805</v>
-      </c>
-      <c r="D303" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="304" spans="1:4">
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>9</v>
       </c>
       <c r="B304" t="s">
+        <v>808</v>
+      </c>
+      <c r="C304" t="s">
+        <v>807</v>
+      </c>
+      <c r="D304" t="s">
         <v>809</v>
       </c>
-      <c r="C304" t="s">
-        <v>808</v>
-      </c>
-      <c r="D304" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="305" spans="1:4">
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>9</v>
       </c>
       <c r="B305" t="s">
+        <v>811</v>
+      </c>
+      <c r="C305" t="s">
+        <v>810</v>
+      </c>
+      <c r="D305" t="s">
         <v>812</v>
       </c>
-      <c r="C305" t="s">
-        <v>811</v>
-      </c>
-      <c r="D305" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="306" spans="1:4">
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>9</v>
       </c>
       <c r="B306" t="s">
+        <v>814</v>
+      </c>
+      <c r="C306" t="s">
+        <v>813</v>
+      </c>
+      <c r="D306" t="s">
         <v>815</v>
       </c>
-      <c r="C306" t="s">
-        <v>814</v>
-      </c>
-      <c r="D306" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="307" spans="1:4">
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>9</v>
       </c>
       <c r="B307" t="s">
+        <v>817</v>
+      </c>
+      <c r="C307" t="s">
+        <v>816</v>
+      </c>
+      <c r="D307" t="s">
         <v>818</v>
       </c>
-      <c r="C307" t="s">
-        <v>817</v>
-      </c>
-      <c r="D307" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="308" spans="1:4">
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>9</v>
       </c>
       <c r="B308" t="s">
+        <v>820</v>
+      </c>
+      <c r="C308" t="s">
+        <v>819</v>
+      </c>
+      <c r="D308" t="s">
         <v>821</v>
       </c>
-      <c r="C308" t="s">
-        <v>820</v>
-      </c>
-      <c r="D308" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="309" spans="1:4">
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>9</v>
       </c>
       <c r="B309" t="s">
+        <v>823</v>
+      </c>
+      <c r="C309" t="s">
+        <v>822</v>
+      </c>
+      <c r="D309" t="s">
         <v>824</v>
       </c>
-      <c r="C309" t="s">
-        <v>823</v>
-      </c>
-      <c r="D309" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="310" spans="1:4">
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>9</v>
       </c>
       <c r="B310" t="s">
+        <v>826</v>
+      </c>
+      <c r="C310" t="s">
+        <v>825</v>
+      </c>
+      <c r="D310" t="s">
         <v>827</v>
       </c>
-      <c r="C310" t="s">
-        <v>826</v>
-      </c>
-      <c r="D310" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="311" spans="1:4">
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>9</v>
       </c>
       <c r="B311" t="s">
+        <v>829</v>
+      </c>
+      <c r="C311" t="s">
+        <v>828</v>
+      </c>
+      <c r="D311" t="s">
         <v>830</v>
       </c>
-      <c r="C311" t="s">
-        <v>829</v>
-      </c>
-      <c r="D311" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="312" spans="1:4">
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>9</v>
       </c>
       <c r="B312" t="s">
+        <v>832</v>
+      </c>
+      <c r="C312" t="s">
+        <v>831</v>
+      </c>
+      <c r="D312" t="s">
         <v>833</v>
       </c>
-      <c r="C312" t="s">
-        <v>832</v>
-      </c>
-      <c r="D312" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="313" spans="1:4">
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>9</v>
       </c>
       <c r="B313" t="s">
+        <v>835</v>
+      </c>
+      <c r="C313" t="s">
+        <v>834</v>
+      </c>
+      <c r="D313" t="s">
         <v>836</v>
       </c>
-      <c r="C313" t="s">
-        <v>835</v>
-      </c>
-      <c r="D313" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="314" spans="1:4">
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>9</v>
       </c>
@@ -8427,259 +8429,259 @@
         <v>22</v>
       </c>
     </row>
-    <row r="315" spans="1:4">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>9</v>
       </c>
       <c r="B315" t="s">
+        <v>838</v>
+      </c>
+      <c r="C315" t="s">
+        <v>837</v>
+      </c>
+      <c r="D315" t="s">
         <v>839</v>
       </c>
-      <c r="C315" t="s">
-        <v>838</v>
-      </c>
-      <c r="D315" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="316" spans="1:4">
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>9</v>
       </c>
       <c r="B316" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C316" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D316" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="317" spans="1:4">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>9</v>
       </c>
       <c r="B317" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C317" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D317" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="318" spans="1:4">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>9</v>
       </c>
       <c r="B318" t="s">
+        <v>842</v>
+      </c>
+      <c r="C318" t="s">
+        <v>841</v>
+      </c>
+      <c r="D318" t="s">
         <v>843</v>
       </c>
-      <c r="C318" t="s">
-        <v>842</v>
-      </c>
-      <c r="D318" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="319" spans="1:4">
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>9</v>
       </c>
       <c r="B319" t="s">
+        <v>845</v>
+      </c>
+      <c r="C319" t="s">
+        <v>844</v>
+      </c>
+      <c r="D319" t="s">
         <v>846</v>
       </c>
-      <c r="C319" t="s">
-        <v>845</v>
-      </c>
-      <c r="D319" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="320" spans="1:4">
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>9</v>
       </c>
       <c r="B320" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C320" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="D320" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="321" spans="1:4">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>10</v>
       </c>
       <c r="B321" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C321" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="D321" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="322" spans="1:4">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>10</v>
       </c>
       <c r="B322" t="s">
+        <v>852</v>
+      </c>
+      <c r="C322" t="s">
+        <v>851</v>
+      </c>
+      <c r="D322" t="s">
         <v>853</v>
       </c>
-      <c r="C322" t="s">
-        <v>852</v>
-      </c>
-      <c r="D322" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="323" spans="1:4">
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>10</v>
       </c>
       <c r="B323" t="s">
+        <v>855</v>
+      </c>
+      <c r="C323" t="s">
+        <v>854</v>
+      </c>
+      <c r="D323" t="s">
         <v>856</v>
       </c>
-      <c r="C323" t="s">
-        <v>855</v>
-      </c>
-      <c r="D323" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="324" spans="1:4">
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>10</v>
       </c>
       <c r="B324" t="s">
+        <v>858</v>
+      </c>
+      <c r="C324" t="s">
+        <v>857</v>
+      </c>
+      <c r="D324" t="s">
         <v>859</v>
       </c>
-      <c r="C324" t="s">
-        <v>858</v>
-      </c>
-      <c r="D324" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="325" spans="1:4">
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>10</v>
       </c>
       <c r="B325" t="s">
+        <v>861</v>
+      </c>
+      <c r="C325" t="s">
+        <v>860</v>
+      </c>
+      <c r="D325" t="s">
         <v>862</v>
       </c>
-      <c r="C325" t="s">
-        <v>861</v>
-      </c>
-      <c r="D325" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="326" spans="1:4">
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>10</v>
       </c>
       <c r="B326" t="s">
+        <v>864</v>
+      </c>
+      <c r="C326" t="s">
+        <v>863</v>
+      </c>
+      <c r="D326" t="s">
         <v>865</v>
       </c>
-      <c r="C326" t="s">
-        <v>864</v>
-      </c>
-      <c r="D326" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="327" spans="1:4">
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>10</v>
       </c>
       <c r="B327" t="s">
+        <v>867</v>
+      </c>
+      <c r="C327" t="s">
+        <v>866</v>
+      </c>
+      <c r="D327" t="s">
         <v>868</v>
       </c>
-      <c r="C327" t="s">
-        <v>867</v>
-      </c>
-      <c r="D327" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="328" spans="1:4">
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>10</v>
       </c>
       <c r="B328" t="s">
+        <v>98</v>
+      </c>
+      <c r="C328" t="s">
+        <v>97</v>
+      </c>
+      <c r="D328" t="s">
         <v>99</v>
       </c>
-      <c r="C328" t="s">
-        <v>98</v>
-      </c>
-      <c r="D328" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="329" spans="1:4">
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>10</v>
       </c>
       <c r="B329" t="s">
+        <v>870</v>
+      </c>
+      <c r="C329" t="s">
+        <v>869</v>
+      </c>
+      <c r="D329" t="s">
         <v>871</v>
       </c>
-      <c r="C329" t="s">
-        <v>870</v>
-      </c>
-      <c r="D329" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="330" spans="1:4">
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>10</v>
       </c>
       <c r="B330" t="s">
+        <v>873</v>
+      </c>
+      <c r="C330" t="s">
+        <v>872</v>
+      </c>
+      <c r="D330" t="s">
         <v>874</v>
       </c>
-      <c r="C330" t="s">
-        <v>873</v>
-      </c>
-      <c r="D330" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="331" spans="1:4">
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>10</v>
       </c>
       <c r="B331" t="s">
+        <v>876</v>
+      </c>
+      <c r="C331" t="s">
+        <v>875</v>
+      </c>
+      <c r="D331" t="s">
         <v>877</v>
       </c>
-      <c r="C331" t="s">
-        <v>876</v>
-      </c>
-      <c r="D331" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="332" spans="1:4">
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>10</v>
       </c>
       <c r="B332" t="s">
+        <v>879</v>
+      </c>
+      <c r="C332" t="s">
+        <v>878</v>
+      </c>
+      <c r="D332" t="s">
         <v>880</v>
       </c>
-      <c r="C332" t="s">
-        <v>879</v>
-      </c>
-      <c r="D332" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="333" spans="1:4">
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>10</v>
       </c>
@@ -8693,63 +8695,63 @@
         <v>39</v>
       </c>
     </row>
-    <row r="334" spans="1:4">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>10</v>
       </c>
       <c r="B334" t="s">
+        <v>882</v>
+      </c>
+      <c r="C334" t="s">
+        <v>881</v>
+      </c>
+      <c r="D334" t="s">
         <v>883</v>
       </c>
-      <c r="C334" t="s">
-        <v>882</v>
-      </c>
-      <c r="D334" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="335" spans="1:4">
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>10</v>
       </c>
       <c r="B335" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C335" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D335" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="336" spans="1:4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>10</v>
       </c>
       <c r="B336" t="s">
+        <v>885</v>
+      </c>
+      <c r="C336" t="s">
+        <v>884</v>
+      </c>
+      <c r="D336" t="s">
         <v>886</v>
       </c>
-      <c r="C336" t="s">
-        <v>885</v>
-      </c>
-      <c r="D336" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="337" spans="1:4">
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>10</v>
       </c>
       <c r="B337" t="s">
+        <v>888</v>
+      </c>
+      <c r="C337" t="s">
+        <v>887</v>
+      </c>
+      <c r="D337" t="s">
         <v>889</v>
       </c>
-      <c r="C337" t="s">
-        <v>888</v>
-      </c>
-      <c r="D337" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="338" spans="1:4">
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>10</v>
       </c>
@@ -8763,455 +8765,455 @@
         <v>55</v>
       </c>
     </row>
-    <row r="339" spans="1:4">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>10</v>
       </c>
       <c r="B339" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C339" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="D339" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="340" spans="1:4">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>10</v>
       </c>
       <c r="B340" t="s">
+        <v>893</v>
+      </c>
+      <c r="C340" t="s">
+        <v>892</v>
+      </c>
+      <c r="D340" t="s">
         <v>894</v>
       </c>
-      <c r="C340" t="s">
-        <v>893</v>
-      </c>
-      <c r="D340" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="341" spans="1:4">
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>10</v>
       </c>
       <c r="B341" t="s">
+        <v>802</v>
+      </c>
+      <c r="C341" t="s">
+        <v>801</v>
+      </c>
+      <c r="D341" t="s">
         <v>803</v>
       </c>
-      <c r="C341" t="s">
-        <v>802</v>
-      </c>
-      <c r="D341" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="342" spans="1:4">
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>10</v>
       </c>
       <c r="B342" t="s">
+        <v>141</v>
+      </c>
+      <c r="C342" t="s">
+        <v>140</v>
+      </c>
+      <c r="D342" t="s">
         <v>142</v>
       </c>
-      <c r="C342" t="s">
-        <v>141</v>
-      </c>
-      <c r="D342" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="343" spans="1:4">
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>10</v>
       </c>
       <c r="B343" t="s">
+        <v>896</v>
+      </c>
+      <c r="C343" t="s">
+        <v>895</v>
+      </c>
+      <c r="D343" t="s">
         <v>897</v>
       </c>
-      <c r="C343" t="s">
-        <v>896</v>
-      </c>
-      <c r="D343" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="344" spans="1:4">
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>10</v>
       </c>
       <c r="B344" t="s">
+        <v>899</v>
+      </c>
+      <c r="C344" t="s">
+        <v>898</v>
+      </c>
+      <c r="D344" t="s">
         <v>900</v>
       </c>
-      <c r="C344" t="s">
-        <v>899</v>
-      </c>
-      <c r="D344" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="345" spans="1:4">
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>10</v>
       </c>
       <c r="B345" t="s">
+        <v>902</v>
+      </c>
+      <c r="C345" t="s">
+        <v>901</v>
+      </c>
+      <c r="D345" t="s">
         <v>903</v>
       </c>
-      <c r="C345" t="s">
-        <v>902</v>
-      </c>
-      <c r="D345" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="346" spans="1:4">
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>10</v>
       </c>
       <c r="B346" t="s">
+        <v>905</v>
+      </c>
+      <c r="C346" t="s">
+        <v>904</v>
+      </c>
+      <c r="D346" t="s">
         <v>906</v>
       </c>
-      <c r="C346" t="s">
-        <v>905</v>
-      </c>
-      <c r="D346" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="347" spans="1:4">
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>10</v>
       </c>
       <c r="B347" t="s">
+        <v>908</v>
+      </c>
+      <c r="C347" t="s">
+        <v>907</v>
+      </c>
+      <c r="D347" t="s">
         <v>909</v>
       </c>
-      <c r="C347" t="s">
-        <v>908</v>
-      </c>
-      <c r="D347" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="348" spans="1:4">
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>10</v>
       </c>
       <c r="B348" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C348" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D348" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="349" spans="1:4">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>10</v>
       </c>
       <c r="B349" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C349" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D349" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="350" spans="1:4">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>10</v>
       </c>
       <c r="B350" t="s">
+        <v>914</v>
+      </c>
+      <c r="C350" t="s">
+        <v>913</v>
+      </c>
+      <c r="D350" t="s">
         <v>915</v>
       </c>
-      <c r="C350" t="s">
-        <v>914</v>
-      </c>
-      <c r="D350" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="351" spans="1:4">
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>10</v>
       </c>
       <c r="B351" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C351" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D351" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="352" spans="1:4">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>10</v>
       </c>
       <c r="B352" t="s">
+        <v>919</v>
+      </c>
+      <c r="C352" t="s">
+        <v>918</v>
+      </c>
+      <c r="D352" t="s">
         <v>920</v>
       </c>
-      <c r="C352" t="s">
-        <v>919</v>
-      </c>
-      <c r="D352" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="353" spans="1:4">
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>10</v>
       </c>
       <c r="B353" t="s">
+        <v>922</v>
+      </c>
+      <c r="C353" t="s">
+        <v>921</v>
+      </c>
+      <c r="D353" t="s">
         <v>923</v>
       </c>
-      <c r="C353" t="s">
-        <v>922</v>
-      </c>
-      <c r="D353" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="354" spans="1:4">
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>10</v>
       </c>
       <c r="B354" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C354" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D354" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="355" spans="1:4">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>10</v>
       </c>
       <c r="B355" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C355" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D355" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="356" spans="1:4">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>11</v>
       </c>
       <c r="B356" t="s">
+        <v>928</v>
+      </c>
+      <c r="C356" t="s">
+        <v>927</v>
+      </c>
+      <c r="D356" t="s">
         <v>929</v>
       </c>
-      <c r="C356" t="s">
-        <v>928</v>
-      </c>
-      <c r="D356" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="357" spans="1:4">
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>11</v>
       </c>
       <c r="B357" t="s">
+        <v>931</v>
+      </c>
+      <c r="C357" t="s">
+        <v>930</v>
+      </c>
+      <c r="D357" t="s">
         <v>932</v>
       </c>
-      <c r="C357" t="s">
-        <v>931</v>
-      </c>
-      <c r="D357" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="358" spans="1:4">
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>11</v>
       </c>
       <c r="B358" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C358" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="D358" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="359" spans="1:4">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>11</v>
       </c>
       <c r="B359" t="s">
+        <v>936</v>
+      </c>
+      <c r="C359" t="s">
+        <v>935</v>
+      </c>
+      <c r="D359" t="s">
         <v>937</v>
       </c>
-      <c r="C359" t="s">
-        <v>936</v>
-      </c>
-      <c r="D359" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="360" spans="1:4">
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>11</v>
       </c>
       <c r="B360" t="s">
+        <v>95</v>
+      </c>
+      <c r="C360" t="s">
+        <v>94</v>
+      </c>
+      <c r="D360" t="s">
         <v>96</v>
       </c>
-      <c r="C360" t="s">
-        <v>95</v>
-      </c>
-      <c r="D360" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="361" spans="1:4">
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>11</v>
       </c>
       <c r="B361" t="s">
+        <v>939</v>
+      </c>
+      <c r="C361" t="s">
+        <v>938</v>
+      </c>
+      <c r="D361" t="s">
         <v>940</v>
       </c>
-      <c r="C361" t="s">
-        <v>939</v>
-      </c>
-      <c r="D361" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="362" spans="1:4">
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>11</v>
       </c>
       <c r="B362" t="s">
+        <v>942</v>
+      </c>
+      <c r="C362" t="s">
+        <v>941</v>
+      </c>
+      <c r="D362" t="s">
         <v>943</v>
       </c>
-      <c r="C362" t="s">
-        <v>942</v>
-      </c>
-      <c r="D362" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="363" spans="1:4">
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>11</v>
       </c>
       <c r="B363" t="s">
+        <v>870</v>
+      </c>
+      <c r="C363" t="s">
+        <v>869</v>
+      </c>
+      <c r="D363" t="s">
         <v>871</v>
       </c>
-      <c r="C363" t="s">
-        <v>870</v>
-      </c>
-      <c r="D363" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="364" spans="1:4">
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>11</v>
       </c>
       <c r="B364" t="s">
+        <v>945</v>
+      </c>
+      <c r="C364" t="s">
+        <v>944</v>
+      </c>
+      <c r="D364" t="s">
         <v>946</v>
       </c>
-      <c r="C364" t="s">
-        <v>945</v>
-      </c>
-      <c r="D364" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="365" spans="1:4">
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>11</v>
       </c>
       <c r="B365" t="s">
+        <v>948</v>
+      </c>
+      <c r="C365" t="s">
+        <v>947</v>
+      </c>
+      <c r="D365" t="s">
         <v>949</v>
       </c>
-      <c r="C365" t="s">
-        <v>948</v>
-      </c>
-      <c r="D365" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="366" spans="1:4">
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>11</v>
       </c>
       <c r="B366" t="s">
+        <v>951</v>
+      </c>
+      <c r="C366" t="s">
+        <v>950</v>
+      </c>
+      <c r="D366" t="s">
         <v>952</v>
       </c>
-      <c r="C366" t="s">
-        <v>951</v>
-      </c>
-      <c r="D366" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="367" spans="1:4">
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>11</v>
       </c>
       <c r="B367" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C367" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D367" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="368" spans="1:4">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>11</v>
       </c>
       <c r="B368" t="s">
+        <v>579</v>
+      </c>
+      <c r="C368" t="s">
+        <v>578</v>
+      </c>
+      <c r="D368" t="s">
         <v>580</v>
       </c>
-      <c r="C368" t="s">
-        <v>579</v>
-      </c>
-      <c r="D368" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="369" spans="1:4">
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>11</v>
       </c>
       <c r="B369" t="s">
+        <v>955</v>
+      </c>
+      <c r="C369" t="s">
+        <v>954</v>
+      </c>
+      <c r="D369" t="s">
         <v>956</v>
       </c>
-      <c r="C369" t="s">
-        <v>955</v>
-      </c>
-      <c r="D369" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="370" spans="1:4">
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>11</v>
       </c>
       <c r="B370" t="s">
+        <v>958</v>
+      </c>
+      <c r="C370" t="s">
+        <v>957</v>
+      </c>
+      <c r="D370" t="s">
         <v>959</v>
       </c>
-      <c r="C370" t="s">
-        <v>958</v>
-      </c>
-      <c r="D370" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="371" spans="1:4">
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>11</v>
       </c>
@@ -9225,49 +9227,49 @@
         <v>14</v>
       </c>
     </row>
-    <row r="372" spans="1:4">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>11</v>
       </c>
       <c r="B372" t="s">
+        <v>961</v>
+      </c>
+      <c r="C372" t="s">
+        <v>960</v>
+      </c>
+      <c r="D372" t="s">
         <v>962</v>
       </c>
-      <c r="C372" t="s">
-        <v>961</v>
-      </c>
-      <c r="D372" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="373" spans="1:4">
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>11</v>
       </c>
       <c r="B373" t="s">
+        <v>964</v>
+      </c>
+      <c r="C373" t="s">
+        <v>963</v>
+      </c>
+      <c r="D373" t="s">
         <v>965</v>
       </c>
-      <c r="C373" t="s">
-        <v>964</v>
-      </c>
-      <c r="D373" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="374" spans="1:4">
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>11</v>
       </c>
       <c r="B374" t="s">
+        <v>967</v>
+      </c>
+      <c r="C374" t="s">
+        <v>966</v>
+      </c>
+      <c r="D374" t="s">
         <v>968</v>
       </c>
-      <c r="C374" t="s">
-        <v>967</v>
-      </c>
-      <c r="D374" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="375" spans="1:4">
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>11</v>
       </c>
@@ -9281,161 +9283,161 @@
         <v>10</v>
       </c>
     </row>
-    <row r="376" spans="1:4">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>11</v>
       </c>
       <c r="B376" t="s">
+        <v>970</v>
+      </c>
+      <c r="C376" t="s">
+        <v>969</v>
+      </c>
+      <c r="D376" t="s">
         <v>971</v>
       </c>
-      <c r="C376" t="s">
-        <v>970</v>
-      </c>
-      <c r="D376" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="377" spans="1:4">
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>11</v>
       </c>
       <c r="B377" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C377" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D377" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="378" spans="1:4">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>11</v>
       </c>
       <c r="B378" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="C378" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="D378" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="379" spans="1:4">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>11</v>
       </c>
       <c r="B379" t="s">
+        <v>975</v>
+      </c>
+      <c r="C379" t="s">
+        <v>974</v>
+      </c>
+      <c r="D379" t="s">
         <v>976</v>
       </c>
-      <c r="C379" t="s">
-        <v>975</v>
-      </c>
-      <c r="D379" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="380" spans="1:4">
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>11</v>
       </c>
       <c r="B380" t="s">
+        <v>978</v>
+      </c>
+      <c r="C380" t="s">
+        <v>977</v>
+      </c>
+      <c r="D380" t="s">
         <v>979</v>
       </c>
-      <c r="C380" t="s">
-        <v>978</v>
-      </c>
-      <c r="D380" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="381" spans="1:4">
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>11</v>
       </c>
       <c r="B381" t="s">
+        <v>981</v>
+      </c>
+      <c r="C381" t="s">
+        <v>980</v>
+      </c>
+      <c r="D381" t="s">
         <v>982</v>
       </c>
-      <c r="C381" t="s">
-        <v>981</v>
-      </c>
-      <c r="D381" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="382" spans="1:4">
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>11</v>
       </c>
       <c r="B382" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="C382" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="D382" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="383" spans="1:4">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>11</v>
       </c>
       <c r="B383" t="s">
+        <v>986</v>
+      </c>
+      <c r="C383" t="s">
+        <v>985</v>
+      </c>
+      <c r="D383" t="s">
         <v>987</v>
       </c>
-      <c r="C383" t="s">
-        <v>986</v>
-      </c>
-      <c r="D383" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="384" spans="1:4">
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>11</v>
       </c>
       <c r="B384" t="s">
+        <v>989</v>
+      </c>
+      <c r="C384" t="s">
+        <v>988</v>
+      </c>
+      <c r="D384" t="s">
         <v>990</v>
       </c>
-      <c r="C384" t="s">
-        <v>989</v>
-      </c>
-      <c r="D384" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="385" spans="1:4">
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>11</v>
       </c>
       <c r="B385" t="s">
+        <v>992</v>
+      </c>
+      <c r="C385" t="s">
+        <v>991</v>
+      </c>
+      <c r="D385" t="s">
         <v>993</v>
       </c>
-      <c r="C385" t="s">
-        <v>992</v>
-      </c>
-      <c r="D385" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="386" spans="1:4">
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>11</v>
       </c>
       <c r="B386" t="s">
+        <v>995</v>
+      </c>
+      <c r="C386" t="s">
+        <v>994</v>
+      </c>
+      <c r="D386" t="s">
         <v>996</v>
       </c>
-      <c r="C386" t="s">
-        <v>995</v>
-      </c>
-      <c r="D386" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="387" spans="1:4">
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>11</v>
       </c>
@@ -9449,74 +9451,74 @@
         <v>35</v>
       </c>
     </row>
-    <row r="388" spans="1:4">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>11</v>
       </c>
       <c r="B388" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C388" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D388" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="389" spans="1:4">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>11</v>
       </c>
       <c r="B389" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C389" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D389" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="390" spans="1:4">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>11</v>
       </c>
       <c r="B390" t="s">
+        <v>998</v>
+      </c>
+      <c r="C390" t="s">
+        <v>997</v>
+      </c>
+      <c r="D390" t="s">
         <v>999</v>
       </c>
-      <c r="C390" t="s">
-        <v>998</v>
-      </c>
-      <c r="D390" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="391" spans="1:4">
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>11</v>
       </c>
       <c r="B391" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C391" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D391" t="s">
         <v>1002</v>
       </c>
-      <c r="C391" t="s">
-        <v>1001</v>
-      </c>
-      <c r="D391" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="392" spans="1:4">
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>11</v>
       </c>
       <c r="B392" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C392" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D392" t="s">
         <v>1005</v>
-      </c>
-      <c r="C392" t="s">
-        <v>1004</v>
-      </c>
-      <c r="D392" t="s">
-        <v>1006</v>
       </c>
     </row>
   </sheetData>
